--- a/gSHAPE_SOC_Recommendations.xlsx
+++ b/gSHAPE_SOC_Recommendations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/moges_biru_ufl_edu/Documents/UFL/Research_Work/ETH SHAPE/Rerun for App/SMAF file and code for gSHAPE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAC026DD-74AB-4A5E-929D-E29221067CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADC9803A-D4F6-4B89-835D-44124134E52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="571" xr2:uid="{D96F18D4-8F79-4C09-94DE-D0B4E2D141DD}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5590" uniqueCount="1443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5590" uniqueCount="1568">
   <si>
     <t>Region</t>
   </si>
@@ -2718,7 +2718,7 @@
     <t>Florida</t>
   </si>
   <si>
-    <t>FL01-01-01-VL</t>
+    <t>FL-1</t>
   </si>
   <si>
     <t>Conventional Tillage</t>
@@ -2730,7 +2730,7 @@
     <t>Transition to strip-till or no-till immediately to halt severe carbon losses.</t>
   </si>
   <si>
-    <t>FL01-01-01-L</t>
+    <t>FL-2</t>
   </si>
   <si>
     <t>Continuous tillage breaks apart fragile micro-aggregates, leaving organic matter vulnerable to heat.</t>
@@ -2739,7 +2739,7 @@
     <t>Reduce soil disturbance to protect existing organic matter and allow biological glues to form.</t>
   </si>
   <si>
-    <t>FL01-01-01-M</t>
+    <t>FL-3</t>
   </si>
   <si>
     <t>Carbon inputs are currently fighting a losing battle against tillage-induced oxidation.</t>
@@ -2748,7 +2748,7 @@
     <t>Implement strip-till to minimize disturbance and provide the necessary catalyst to push SOC into the High zone.</t>
   </si>
   <si>
-    <t>FL01-01-01-H</t>
+    <t>FL-4</t>
   </si>
   <si>
     <t>Achieving high SOC with continuous tillage is rare and likely dependent on massive external organic inputs.</t>
@@ -2757,7 +2757,7 @@
     <t>Minimize tillage passes to lock in these volatile gains and reduce operational fuel costs.</t>
   </si>
   <si>
-    <t>FL01-01-01-VH</t>
+    <t>FL-5</t>
   </si>
   <si>
     <t>Elite SOC levels are present despite heavy disturbance, making these stocks highly volatile.</t>
@@ -2766,6 +2766,9 @@
     <t>Adopt reduced tillage to protect this massive carbon investment from rapid microbial mineralization.</t>
   </si>
   <si>
+    <t>FL-6</t>
+  </si>
+  <si>
     <t>No till (0-5)</t>
   </si>
   <si>
@@ -2775,30 +2778,45 @@
     <t>Protect the no-till transition by minimizing all disturbance and incorporating high-biomass cover crops.</t>
   </si>
   <si>
+    <t>FL-7</t>
+  </si>
+  <si>
     <t>The soil is currently in a transitional phase where biological glues are just beginning to bind sand particles.</t>
   </si>
   <si>
     <t>Continue strictly minimizing disturbance to support the formation of macro-aggregates.</t>
   </si>
   <si>
+    <t>FL-8</t>
+  </si>
+  <si>
     <t>Reduced disturbance has allowed soil structure to stabilize, representing significant progress in SOC retention.</t>
   </si>
   <si>
     <t>Maintain the no-till system to prevent the oxidation of the newly built particulate organic matter.</t>
   </si>
   <si>
+    <t>FL-9</t>
+  </si>
+  <si>
     <t>The reduced tillage system is effectively protecting stored carbon from extreme summer temperatures.</t>
   </si>
   <si>
     <t>Aim for continuous no-till or ultra-low disturbance planting to push into elite percentiles.</t>
   </si>
   <si>
+    <t>FL-10</t>
+  </si>
+  <si>
     <t>The soil possesses elite carbon stocks, indicating highly successful structural management.</t>
   </si>
   <si>
     <t>Ensure all planter setups can handle continuous high-residue planting to stop micro-aggregate breakdown entirely.</t>
   </si>
   <si>
+    <t>FL-11</t>
+  </si>
+  <si>
     <t>No till (5+ yrs)</t>
   </si>
   <si>
@@ -2808,31 +2826,43 @@
     <t>Aggressively increase root and residue biomass through cover crops to fill the empty carbon tank.</t>
   </si>
   <si>
+    <t>FL-12</t>
+  </si>
+  <si>
     <t>No-till is preserving the baseline, but sandy soils require massive organic inputs to actively build SOC.</t>
   </si>
   <si>
     <t>Maximize root exudates by optimizing cash crop yields and integrating heavy cover crops.</t>
   </si>
   <si>
+    <t>FL-13</t>
+  </si>
+  <si>
     <t>The continuous no-till framework is working perfectly to stabilize the biological cycling of nutrients.</t>
   </si>
   <si>
     <t>Focus on optimizing crop rotation diversity to push SOC accumulation higher.</t>
   </si>
   <si>
+    <t>FL-14</t>
+  </si>
+  <si>
     <t>The elimination of disturbance is successfully protecting carbon from intense heat and microbial oxidation.</t>
   </si>
   <si>
     <t>Maintain this continuous no-till system to protect high-functioning soil biology.</t>
   </si>
   <si>
+    <t>FL-15</t>
+  </si>
+  <si>
     <t>The continuous no-till system is perfectly preserving the soil's maximum carbon-holding capacity.</t>
   </si>
   <si>
     <t>Maintain this exact baseline management to sustain elite biological functioning.</t>
   </si>
   <si>
-    <t>FL01-01-02-VL</t>
+    <t>FL-16</t>
   </si>
   <si>
     <t>Cover Crop</t>
@@ -2844,7 +2874,7 @@
     <t>Implement a winter cover crop immediately to provide soil armor and start feeding the microbial community.</t>
   </si>
   <si>
-    <t>FL01-01-02-L</t>
+    <t>FL-17</t>
   </si>
   <si>
     <t>Bare fallows represent a massive missed opportunity for capturing carbon via root exudates.</t>
@@ -2853,7 +2883,7 @@
     <t>Add a high-biomass cover crop to jumpstart soil biology and cool the soil surface.</t>
   </si>
   <si>
-    <t>FL01-01-02-M</t>
+    <t>FL-18</t>
   </si>
   <si>
     <t>The soil maintains average SOC, but missing off-season biomass limits further accumulation.</t>
@@ -2862,7 +2892,7 @@
     <t>Integrate a cover crop to provide the soil armor needed to push performance into the High zone.</t>
   </si>
   <si>
-    <t>FL01-01-02-H</t>
+    <t>FL-19</t>
   </si>
   <si>
     <t>High SOC is present, but bare fallows leave it vulnerable to intense summer heat and oxidation.</t>
@@ -2871,7 +2901,7 @@
     <t>Utilize cover crops to provide critical armor and help cycle nutrients for the subsequent cash crop.</t>
   </si>
   <si>
-    <t>FL01-01-02-VH</t>
+    <t>FL-20</t>
   </si>
   <si>
     <t>Massive carbon investments are highly susceptible to leaching and oxidation during bare off-seasons.</t>
@@ -2880,36 +2910,54 @@
     <t>Keep a living root in the soil year-round to protect and sustain elite carbon stocks.</t>
   </si>
   <si>
+    <t>FL-21</t>
+  </si>
+  <si>
     <t>Legumes fix nitrogen, but their low C:N ratio causes residue to decompose too quickly to build long-term SOC.</t>
   </si>
   <si>
     <t>Mix legumes with a high-carbon grass species to leave a more persistent surface mulch.</t>
   </si>
   <si>
+    <t>FL-22</t>
+  </si>
+  <si>
     <t>Legumes provide excellent nitrogen credits, but the resulting biomass vaporizes quickly in hot climates.</t>
   </si>
   <si>
     <t>Integrate recalcitrant carbon from winter grasses to build lasting particulate organic matter.</t>
   </si>
   <si>
+    <t>FL-23</t>
+  </si>
+  <si>
     <t>Legumes are effective for fertility, but a low C:N ratio limits aggregate formation in sandy soils.</t>
   </si>
   <si>
     <t>Add a high-carbon grass to the mix to provide a balanced food source for soil fungi.</t>
   </si>
   <si>
+    <t>FL-24</t>
+  </si>
+  <si>
     <t>Legume cover crops efficiently offset synthetic nitrogen costs while supporting high biological activity.</t>
   </si>
   <si>
     <t>Continue use, but monitor residue breakdown rates to ensure the soil remains armored.</t>
   </si>
   <si>
+    <t>FL-25</t>
+  </si>
+  <si>
     <t>The system is biologically hyper-active, and legumes feed this system perfectly without tying up nitrogen.</t>
   </si>
   <si>
     <t>Maintain current legume integration to support elite microbial populations.</t>
   </si>
   <si>
+    <t>FL-26</t>
+  </si>
+  <si>
     <t>Winter Grass</t>
   </si>
   <si>
@@ -2919,30 +2967,45 @@
     <t>Utilize heavy seeding rates of rye or oats to rapidly build surface residue.</t>
   </si>
   <si>
+    <t>FL-27</t>
+  </si>
+  <si>
     <t>Winter grasses provide excellent carbon bulk, acting as a blanket that protects moisture and cools the soil.</t>
   </si>
   <si>
     <t>Terminate carefully to maximize surface mulch retention going into the spring planting season.</t>
   </si>
   <si>
+    <t>FL-28</t>
+  </si>
+  <si>
     <t>Persistent grass residue is a strong driver of the current average SOC accumulation.</t>
   </si>
   <si>
     <t>Monitor for potential nitrogen immobilization during cash crop planting, or consider adding a legume next season.</t>
   </si>
   <si>
+    <t>FL-29</t>
+  </si>
+  <si>
     <t>High-biomass winter grass inputs actively protect elite carbon pools from degrading during dormant periods.</t>
   </si>
   <si>
     <t>Continue utilizing high-biomass grasses to maintain structural integrity.</t>
   </si>
   <si>
+    <t>FL-30</t>
+  </si>
+  <si>
     <t>The massive root systems of winter grasses perfectly maintain deep-soil carbon stocks year-round.</t>
   </si>
   <si>
     <t>Maintain this strategy to ensure constant carbon exudation into the soil profile.</t>
   </si>
   <si>
+    <t>FL-31</t>
+  </si>
+  <si>
     <t>Summer Grass</t>
   </si>
   <si>
@@ -2952,61 +3015,88 @@
     <t>Plant sorghum-sudangrass to rapidly generate necessary carbon bulk and soil shading.</t>
   </si>
   <si>
+    <t>FL-32</t>
+  </si>
+  <si>
     <t>Deep-rooting summer grasses break through compaction layers while injecting immense amounts of carbon.</t>
   </si>
   <si>
     <t>Utilize summer grasses to improve water infiltration and expand the rooting zone.</t>
   </si>
   <si>
+    <t>FL-33</t>
+  </si>
+  <si>
     <t>Summer grasses provide exceptional armor against extreme heat and intense rainfall while suppressing nematodes.</t>
   </si>
   <si>
     <t>Implement this highly effective strategy to push SOC into the High zone.</t>
   </si>
   <si>
+    <t>FL-34</t>
+  </si>
+  <si>
     <t>Heavy summer biomass maintains high SOC and protects the soil matrix from the physical impact of thunderstorms.</t>
   </si>
   <si>
     <t>Continue utilizing heavy summer grasses to sustain high carbon retention.</t>
   </si>
   <si>
+    <t>FL-35</t>
+  </si>
+  <si>
     <t>Maximum biomass generation perfectly sustains biological capacity during extremely hot summer fallows.</t>
   </si>
   <si>
     <t>Maintain summer grass fallows to feed elite microbial populations.</t>
   </si>
   <si>
+    <t>FL-36</t>
+  </si>
+  <si>
     <t>Multispecies mixes offer diverse exudates, but degraded sands require significant persistent biomass.</t>
   </si>
   <si>
     <t>Ensure the grass component of the mix is dominant enough to leave lasting surface armor.</t>
   </si>
   <si>
+    <t>FL-37</t>
+  </si>
+  <si>
     <t>A balanced C:N ratio from a mix optimizes microbial efficiency and initiates stable humus formation.</t>
   </si>
   <si>
     <t>Utilize a balanced mix to maximize both root diversity and surface residue persistence.</t>
   </si>
   <si>
+    <t>FL-38</t>
+  </si>
+  <si>
     <t>Diverse root exudates and balanced C:N ratios represent the gold standard for humification.</t>
   </si>
   <si>
     <t>Maintain this diverse mix to accelerate the climb into the High zone without sacrificing cash crop fertility.</t>
   </si>
   <si>
+    <t>FL-39</t>
+  </si>
+  <si>
     <t>Diverse root systems are feeding a highly efficient microbial food web, locking in high carbon stocks.</t>
   </si>
   <si>
     <t>Continue utilizing multispecies mixes to maintain this resilient biological system.</t>
   </si>
   <si>
+    <t>FL-40</t>
+  </si>
+  <si>
     <t>Peak biological management is achieved through the diversity of root architectures and exudates.</t>
   </si>
   <si>
     <t>Maintain high-diversity mixes to effortlessly sustain elite soil microbiomes.</t>
   </si>
   <si>
-    <t>FL01-01-03-VL</t>
+    <t>FL-41</t>
   </si>
   <si>
     <t>Residue</t>
@@ -3018,7 +3108,7 @@
     <t>Stop residue removal immediately and return all biomass to the soil surface.</t>
   </si>
   <si>
-    <t>FL01-01-03-L</t>
+    <t>FL-42</t>
   </si>
   <si>
     <t>Surface residue is the only shield against extreme heat; removing it guarantees rapid carbon oxidation.</t>
@@ -3027,7 +3117,7 @@
     <t>Cease exporting stover and leave all harvest residue in the field to cool the soil.</t>
   </si>
   <si>
-    <t>FL01-01-03-M</t>
+    <t>FL-43</t>
   </si>
   <si>
     <t>Residue removal acts as a hard ceiling on SOC potential, stalling progress despite other good practices.</t>
@@ -3036,7 +3126,7 @@
     <t>Retain at least 50-75% of cash crop stover to push the soil into the High zone.</t>
   </si>
   <si>
-    <t>FL01-01-03-H</t>
+    <t>FL-44</t>
   </si>
   <si>
     <t>High SOC levels are at severe risk of rapid depletion if surface residue export continues.</t>
@@ -3045,7 +3135,7 @@
     <t>Stop mining the soil's carbon bank and return biomass to protect the biological baseline.</t>
   </si>
   <si>
-    <t>FL01-01-03-VH</t>
+    <t>FL-45</t>
   </si>
   <si>
     <t>Exporting residue from an elite soil sustainably starves the microbial population of required energy.</t>
@@ -3054,6 +3144,9 @@
     <t>Halt all residue export to maintain the biological demand of this top-tier soil.</t>
   </si>
   <si>
+    <t>FL-46</t>
+  </si>
+  <si>
     <t>Yes 50%</t>
   </si>
   <si>
@@ -3063,30 +3156,45 @@
     <t>Increase retention to 75%+ to adequately cool the soil surface and protect moisture.</t>
   </si>
   <si>
+    <t>FL-47</t>
+  </si>
+  <si>
     <t>Leaving 50% residue maintains the baseline, but sandy soils require maximum organic return to build carbon.</t>
   </si>
   <si>
     <t>Maximize stover retention to actively build particulate organic matter.</t>
   </si>
   <si>
+    <t>FL-48</t>
+  </si>
+  <si>
     <t>Partial retention provides adequate management, but limits the total carbon available for humification.</t>
   </si>
   <si>
     <t>Consider leaving more residue to fully armor the soil against heavy summer rains and crusting.</t>
   </si>
   <si>
+    <t>FL-49</t>
+  </si>
+  <si>
     <t>High SOC is maintained, but elite soils benefit from maximizing carbon return to the biological cycle.</t>
   </si>
   <si>
     <t>Ensure the amount of residue removed does not exceed what the biological system can replace.</t>
   </si>
   <si>
+    <t>FL-50</t>
+  </si>
+  <si>
     <t>Maintaining an elite tier demands massive and continuous carbon returns to the soil.</t>
   </si>
   <si>
     <t>Push toward 100% residue retention where planting equipment allows.</t>
   </si>
   <si>
+    <t>FL-51</t>
+  </si>
+  <si>
     <t>Yes 75%</t>
   </si>
   <si>
@@ -3096,30 +3204,45 @@
     <t>Focus on reducing tillage passes or introducing winter cover crops to utilize this residue.</t>
   </si>
   <si>
+    <t>FL-52</t>
+  </si>
+  <si>
     <t>Residue management is strong; low SOC may be stalled by pH or fertility issues limiting total crop biomass.</t>
   </si>
   <si>
     <t>Investigate and correct chemical limitations to maximize the total volume of retained stover.</t>
   </si>
   <si>
+    <t>FL-53</t>
+  </si>
+  <si>
     <t>Retaining 75% residue provides excellent armor and returns significant carbon to the biological cycle.</t>
   </si>
   <si>
     <t>Maintain this retention level to continuously build stable particulate organic carbon.</t>
   </si>
   <si>
+    <t>FL-54</t>
+  </si>
+  <si>
     <t>This high level of residue retention is a primary driver sustaining the current high soil health status.</t>
   </si>
   <si>
     <t>Continue this practice to protect biological activity from environmental extremes.</t>
   </si>
   <si>
+    <t>FL-55</t>
+  </si>
+  <si>
     <t>Leaving the vast majority of residue is a highly sustainable method for feeding massive microbial populations.</t>
   </si>
   <si>
     <t>Maintain current retention levels to support elite biological demands.</t>
   </si>
   <si>
+    <t>FL-56</t>
+  </si>
+  <si>
     <t>Yes 100%</t>
   </si>
   <si>
@@ -3129,31 +3252,43 @@
     <t>Focus on optimizing crop fertility to ensure the 100% retention actually provides enough bulk.</t>
   </si>
   <si>
+    <t>FL-57</t>
+  </si>
+  <si>
     <t>Complete residue retention provides perfect soil armor to moderate extreme Florida temperatures.</t>
   </si>
   <si>
     <t>With residue optimized, prioritize reducing tillage passes to jumpstart aggregate formation.</t>
   </si>
   <si>
+    <t>FL-58</t>
+  </si>
+  <si>
     <t>Maximum carbon return ensures the microbial system is constantly fed and protected from the elements.</t>
   </si>
   <si>
     <t>Maintain 100% retention to reliably push SOC into the High functioning zone.</t>
   </si>
   <si>
+    <t>FL-59</t>
+  </si>
+  <si>
     <t>Returning all residue is exactly how high-functioning soils sustain structural integrity and biological capacity.</t>
   </si>
   <si>
     <t>Continue flawless residue retention to protect this valuable carbon stock.</t>
   </si>
   <si>
+    <t>FL-60</t>
+  </si>
+  <si>
     <t>100% retention is absolutely mandatory to meet the massive biological carbon demand of an elite soil.</t>
   </si>
   <si>
     <t>Maintain this practice indefinitely to sustain peak soil health.</t>
   </si>
   <si>
-    <t>FL02-01-01-VL</t>
+    <t>FL-61</t>
   </si>
   <si>
     <t>sugarcane</t>
@@ -3171,7 +3306,7 @@
     <t>Transition to green cane harvesting to cease carbon hemorrhaging and begin rebuilding.</t>
   </si>
   <si>
-    <t>FL02-01-01-L</t>
+    <t>FL-62</t>
   </si>
   <si>
     <t>Immense amounts of potential soil carbon are being exported into the atmosphere as smoke.</t>
@@ -3180,7 +3315,7 @@
     <t>Retain harvest biomass as a trash blanket to build biological structure and SOC.</t>
   </si>
   <si>
-    <t>FL02-01-01-M</t>
+    <t>FL-63</t>
   </si>
   <si>
     <t>Burning acts as a hard ceiling on carbon accumulation, sacrificing long-term particulate organic matter for short-term ash nutrients.</t>
@@ -3189,7 +3324,7 @@
     <t>Cease burning to push SOC into the High zone.</t>
   </si>
   <si>
-    <t>FL02-01-01-H</t>
+    <t>FL-64</t>
   </si>
   <si>
     <t>High SOC exists despite burning, but the lack of a trash blanket leaves the soil surface vulnerable to rapid oxidation.</t>
@@ -3198,7 +3333,7 @@
     <t>Cease burning to protect elite carbon stocks from intense summer sun.</t>
   </si>
   <si>
-    <t>FL02-01-01-VH</t>
+    <t>FL-65</t>
   </si>
   <si>
     <t>An elite carbon baseline is present, but routine burning puts it at severe risk of degradation.</t>
@@ -3207,6 +3342,9 @@
     <t>Transition to green cane harvesting to protect the soil surface from moisture loss and oxidation.</t>
   </si>
   <si>
+    <t>FL-66</t>
+  </si>
+  <si>
     <t>Green Cane (Trash Blanket)</t>
   </si>
   <si>
@@ -3216,31 +3354,43 @@
     <t>Utilize the trash blanket to cool the soil, conserve moisture, and slowly feed the microbial web.</t>
   </si>
   <si>
+    <t>FL-67</t>
+  </si>
+  <si>
     <t>A thick trash blanket serves as the best defense against intense heat and microbial burnout.</t>
   </si>
   <si>
     <t>Ensure residue is distributed evenly to maximize soil contact and humification rates.</t>
   </si>
   <si>
+    <t>FL-68</t>
+  </si>
+  <si>
     <t>Retained biomass is actively cycling nutrients and building particulate organic carbon.</t>
   </si>
   <si>
     <t>Maintain the green cane trash blanket as the primary driver pushing SOC toward the High zone.</t>
   </si>
   <si>
+    <t>FL-69</t>
+  </si>
+  <si>
     <t>The trash blanket is perfectly shielding soil biology, suppressing weeds, and returning massive carbon amounts.</t>
   </si>
   <si>
     <t>Continue green cane harvesting to sustain high biological cycling.</t>
   </si>
   <si>
+    <t>FL-70</t>
+  </si>
+  <si>
     <t>Immense carbon return from the trash blanket feeds a hyper-efficient biological community year-round.</t>
   </si>
   <si>
     <t>Mandatory maintenance of green cane harvesting is required to sustain this elite SOC.</t>
   </si>
   <si>
-    <t>FL02-01-02-VL</t>
+    <t>FL-71</t>
   </si>
   <si>
     <t>Bare Fallow (Dry)</t>
@@ -3252,7 +3402,7 @@
     <t>Implement a cover crop or flood fallow immediately to stop rapid carbon loss.</t>
   </si>
   <si>
-    <t>FL02-01-02-L</t>
+    <t>FL-72</t>
   </si>
   <si>
     <t>A dry, bare fallow allows intense heat to oxidize remaining soil organic matter, actively working against SOC building efforts.</t>
@@ -3261,7 +3411,7 @@
     <t>Cover the soil during the fallow window to protect existing structure.</t>
   </si>
   <si>
-    <t>FL02-01-02-M</t>
+    <t>FL-73</t>
   </si>
   <si>
     <t>Ratoon crops build carbon, but a bare fallow erases much of that progress during the transition.</t>
@@ -3270,7 +3420,7 @@
     <t>Cover the soil between cycles as the easiest way to jump into the High zone.</t>
   </si>
   <si>
-    <t>FL02-01-02-H</t>
+    <t>FL-74</t>
   </si>
   <si>
     <t>Bare fallows will rapidly burn through elite carbon stocks built during the multi-year cane cycle.</t>
@@ -3279,7 +3429,7 @@
     <t>Keep the soil covered or flooded during the vulnerable replant transition.</t>
   </si>
   <si>
-    <t>FL02-01-02-VH</t>
+    <t>FL-75</t>
   </si>
   <si>
     <t>Leaving an elite soil bare mines the soil's carbon bank and crashes microbial populations.</t>
@@ -3288,6 +3438,9 @@
     <t>Protect the soil surface entirely between cane cycles to maintain this top tier.</t>
   </si>
   <si>
+    <t>FL-76</t>
+  </si>
+  <si>
     <t>Flooded Fallow</t>
   </si>
   <si>
@@ -3297,30 +3450,45 @@
     <t>Utilize this defensive strategy to halt carbon loss, and integrate cover crops post-flood to build SOC.</t>
   </si>
   <si>
+    <t>FL-77</t>
+  </si>
+  <si>
     <t>Flooding effectively resets pest cycles and halts oxidation before replanting.</t>
   </si>
   <si>
     <t>Consider a flooded rice rotation to actively build carbon rather than just preserving it.</t>
   </si>
   <si>
+    <t>FL-78</t>
+  </si>
+  <si>
     <t>Flooding effectively protects average SOC from intense summer heat during the transition.</t>
   </si>
   <si>
     <t>Maintain this highly sustainable practice for sugarcane cycle transitions.</t>
   </si>
   <si>
+    <t>FL-79</t>
+  </si>
+  <si>
     <t>Creating an anaerobic environment perfectly preserves high carbon stocks from oxidizing during the replant window.</t>
   </si>
   <si>
     <t>Continue utilizing flooded fallows to protect elite biological investments.</t>
   </si>
   <si>
+    <t>FL-80</t>
+  </si>
+  <si>
     <t>Flooding ensures zero oxidative loss of elite carbon pools while the field is out of cane production.</t>
   </si>
   <si>
     <t>Maintain this excellent defensive maneuver to sustain peak SOC.</t>
   </si>
   <si>
+    <t>FL-81</t>
+  </si>
+  <si>
     <t>Cover Crop (Sunn Hemp / Sorghum)</t>
   </si>
   <si>
@@ -3330,30 +3498,45 @@
     <t>Plant high-biomass cover crops to accelerate biological recovery before the next cane cycle.</t>
   </si>
   <si>
+    <t>FL-82</t>
+  </si>
+  <si>
     <t>Cover crop biomass effectively replaces the carbon lost during the heavy tillage required to destroy old cane stools.</t>
   </si>
   <si>
     <t>Maximize cover crop biomass production during the fallow window.</t>
   </si>
   <si>
+    <t>FL-83</t>
+  </si>
+  <si>
     <t>High-biomass cover crops diversify the food web and pump carbon deep into the profile.</t>
   </si>
   <si>
     <t>Utilize this practice as the primary method to push SOC into the High zone.</t>
   </si>
   <si>
+    <t>FL-84</t>
+  </si>
+  <si>
     <t>Cover crops maintain living roots and diverse exudates between cane cycles, perfectly protecting high SOC.</t>
   </si>
   <si>
     <t>Continue this management to sustain active biological populations.</t>
   </si>
   <si>
+    <t>FL-85</t>
+  </si>
+  <si>
     <t>Intense biological diversity ensures microbial populations remain hyper-active during the fallow transition.</t>
   </si>
   <si>
     <t>Maintain elite rotational management with diverse cover crops.</t>
   </si>
   <si>
+    <t>FL-86</t>
+  </si>
+  <si>
     <t>Flooded Rice Rotation</t>
   </si>
   <si>
@@ -3363,31 +3546,43 @@
     <t>Utilize this premier strategy to rapidly rebuild carbon in depleted cane soils.</t>
   </si>
   <si>
+    <t>FL-87</t>
+  </si>
+  <si>
     <t>Highly recalcitrant rice straw breaks down slowly, building lasting particulate organic matter.</t>
   </si>
   <si>
     <t>Incorporate rice rotations to maximize stable carbon retention.</t>
   </si>
   <si>
+    <t>FL-88</t>
+  </si>
+  <si>
     <t>This powerful rotation halts oxidation, controls nematodes, and leaves persistent carbon behind.</t>
   </si>
   <si>
     <t>Maintain rice rotations to actively push the SOC baseline higher.</t>
   </si>
   <si>
+    <t>FL-89</t>
+  </si>
+  <si>
     <t>Cash-crop rice rotations diversify economics while perfectly preserving and building high carbon stocks.</t>
   </si>
   <si>
     <t>Continue this highly sustainable practice to protect elite soil health.</t>
   </si>
   <si>
+    <t>FL-90</t>
+  </si>
+  <si>
     <t>Flooded rice represents the ultimate sustainable sugarcane rotation, maximizing land use while protecting biology.</t>
   </si>
   <si>
     <t>Maintain this flawless rotational system.</t>
   </si>
   <si>
-    <t>FL02-01-03-VL</t>
+    <t>FL-91</t>
   </si>
   <si>
     <t>Replant Tillage</t>
@@ -3402,7 +3597,7 @@
     <t>Try to chemically terminate and use minimum-till planting where possible.</t>
   </si>
   <si>
-    <t>FL02-01-03-L</t>
+    <t>FL-92</t>
   </si>
   <si>
     <t>Heavy replant tillage burns off the organic matter accumulated during the ratoon years.</t>
@@ -3411,7 +3606,7 @@
     <t>Look for ways to reduce equipment passes during this vulnerable window.</t>
   </si>
   <si>
-    <t>FL02-01-03-M</t>
+    <t>FL-93</t>
   </si>
   <si>
     <t>This intensive tillage event sets your carbon progress back every replant cycle.</t>
@@ -3420,7 +3615,7 @@
     <t>Minimize disturbance here as the key to breaking through to the High zone.</t>
   </si>
   <si>
-    <t>FL02-01-03-H</t>
+    <t>FL-94</t>
   </si>
   <si>
     <t>Heavy disturbance required to prepare the seedbed can oxidize years of carbon accumulation rapidly if left bare.</t>
@@ -3429,7 +3624,7 @@
     <t>Proceed with extreme caution during the replant year to protect the baseline.</t>
   </si>
   <si>
-    <t>FL02-01-03-VH</t>
+    <t>FL-95</t>
   </si>
   <si>
     <t>This level of disturbance severely threatens the structural integrity of your elite baseline.</t>
@@ -3438,6 +3633,9 @@
     <t>Compensate for this mandatory disturbance with massive biomass retention during the rest of the cycle.</t>
   </si>
   <si>
+    <t>FL-96</t>
+  </si>
+  <si>
     <t>Minimum-Till (Zonal)</t>
   </si>
   <si>
@@ -3447,31 +3645,43 @@
     <t>Combine zonal tillage with high-biomass cover crops to start rebuilding.</t>
   </si>
   <si>
+    <t>FL-97</t>
+  </si>
+  <si>
     <t>Restricting tillage to the planting zone preserves fungal networks and aggregate stability in the row middles.</t>
   </si>
   <si>
     <t>Keep refining this practice to accelerate recovery.</t>
   </si>
   <si>
+    <t>FL-98</t>
+  </si>
+  <si>
     <t>This targeted tillage prevents the massive carbon loss typically associated with cane replanting.</t>
   </si>
   <si>
     <t>Maintain excellent structural preservation by limiting the tillage footprint.</t>
   </si>
   <si>
+    <t>FL-99</t>
+  </si>
+  <si>
     <t>Preserved row middles act as biological reservoirs to carry the field through the destructive replant phase.</t>
   </si>
   <si>
     <t>Continue minimum-till practices to effortlessly maintain high SOC.</t>
   </si>
   <si>
+    <t>FL-100</t>
+  </si>
+  <si>
     <t>Limiting disturbance exclusively to the furrow perfectly maintains elite SOC during the replant year.</t>
   </si>
   <si>
     <t>Maintain flawless execution of zonal tillage.</t>
   </si>
   <si>
-    <t>FL03-01-01-VL</t>
+    <t>FL-101</t>
   </si>
   <si>
     <t>Bed Management &amp; Tillage</t>
@@ -3486,7 +3696,7 @@
     <t>Maximize biomass inputs during the off-season to offset this mandatory disturbance.</t>
   </si>
   <si>
-    <t>FL03-01-01-L</t>
+    <t>FL-102</t>
   </si>
   <si>
     <t>Aggressive tillage destroys macro-aggregates and exposes protected carbon to intense heat.</t>
@@ -3495,7 +3705,7 @@
     <t>Aggressively apply organic amendments or cover crops to overcome this bottleneck.</t>
   </si>
   <si>
-    <t>FL03-01-01-M</t>
+    <t>FL-103</t>
   </si>
   <si>
     <t>Average SOC is maintained despite extreme disturbance, likely through heavy residue return.</t>
@@ -3504,7 +3714,7 @@
     <t>Recognize that plasticulture acts as a hard ceiling preventing progression to higher tiers.</t>
   </si>
   <si>
-    <t>FL03-01-01-H</t>
+    <t>FL-104</t>
   </si>
   <si>
     <t>High SOC under intensive plasticulture suggests massive continuous inputs of compost or litter.</t>
@@ -3513,7 +3723,7 @@
     <t>Monitor for phosphorus overloading while maintaining organic inputs.</t>
   </si>
   <si>
-    <t>FL03-01-01-VH</t>
+    <t>FL-105</t>
   </si>
   <si>
     <t>Maintaining elite SOC under annual plasticulture is virtually impossible without unsustainable imports.</t>
@@ -3522,6 +3732,9 @@
     <t>Reevaluate management to ensure carbon oxidation isn't outpacing organic amendments.</t>
   </si>
   <si>
+    <t>FL-106</t>
+  </si>
+  <si>
     <t>Bare Ground / Reduced Bedding</t>
   </si>
   <si>
@@ -3531,31 +3744,43 @@
     <t>Integrate high-residue cover crops into the rotation to begin rebuilding structure.</t>
   </si>
   <si>
+    <t>FL-107</t>
+  </si>
+  <si>
     <t>Reducing plastic use and bed height lowers soil temperatures and slows mineralization.</t>
   </si>
   <si>
     <t>Continue minimizing tillage passes to allow fungal networks to establish.</t>
   </si>
   <si>
+    <t>FL-108</t>
+  </si>
+  <si>
     <t>Soil biology is stabilizing and efficiently cycling crop residues without the extreme heat of plastic mulch.</t>
   </si>
   <si>
     <t>Maintain this excellent structural management to protect carbon stocks.</t>
   </si>
   <si>
+    <t>FL-109</t>
+  </si>
+  <si>
     <t>Lower-disturbance approaches allow vegetable systems to accumulate meaningful carbon.</t>
   </si>
   <si>
     <t>Protect the soil surface from heavy rains to maintain this high baseline.</t>
   </si>
   <si>
+    <t>FL-110</t>
+  </si>
+  <si>
     <t>Flawless minimal-disturbance practices and constant living roots have achieved elite status.</t>
   </si>
   <si>
     <t>Maintain current practices to protect this highly unusual and impressive vegetable soil.</t>
   </si>
   <si>
-    <t>FL03-01-02-VL</t>
+    <t>FL-111</t>
   </si>
   <si>
     <t>Fumigation Practices</t>
@@ -3570,7 +3795,7 @@
     <t>Transition to targeted applications or biological alternatives to allow microbial recovery.</t>
   </si>
   <si>
-    <t>FL03-01-02-L</t>
+    <t>FL-112</t>
   </si>
   <si>
     <t>Fumigation resets the biological clock, preventing plant residues from converting into stable SOC.</t>
@@ -3579,7 +3804,7 @@
     <t>Reduce fumigation frequency to allow the active microbiome to establish.</t>
   </si>
   <si>
-    <t>FL03-01-02-M</t>
+    <t>FL-113</t>
   </si>
   <si>
     <t>The soil holds physical carbon, but frequent fumigation renders it biologically dead.</t>
@@ -3588,7 +3813,7 @@
     <t>Implement bio-fumigants to push the soil health score into the High zone.</t>
   </si>
   <si>
-    <t>FL03-01-02-H</t>
+    <t>FL-114</t>
   </si>
   <si>
     <t>Routine fumigation prevents high carbon baselines from cycling nutrients efficiently.</t>
@@ -3597,7 +3822,7 @@
     <t>Stop utilizing broad-spectrum fumigants to unlock this massive biological battery.</t>
   </si>
   <si>
-    <t>FL03-01-02-VH</t>
+    <t>FL-115</t>
   </si>
   <si>
     <t>Routine fumigation inevitably crashes the complex microbial webs required for elite SOC.</t>
@@ -3606,6 +3831,9 @@
     <t>Eliminate broad-spectrum fumigants immediately to protect biological capacity.</t>
   </si>
   <si>
+    <t>FL-116</t>
+  </si>
+  <si>
     <t>In-Bed Only / Biological Alternatives</t>
   </si>
   <si>
@@ -3615,31 +3843,43 @@
     <t>Maintain targeted applications to jumpstart soil recovery.</t>
   </si>
   <si>
+    <t>FL-117</t>
+  </si>
+  <si>
     <t>Preserving fungal populations in row middles ensures off-season cover crops decompose into stable carbon.</t>
   </si>
   <si>
     <t>Continue this excellent transitional step.</t>
   </si>
   <si>
+    <t>FL-118</t>
+  </si>
+  <si>
     <t>Preserved biology in the middles actively breaks down residues and builds aggregate stability.</t>
   </si>
   <si>
     <t>Maintain this targeted approach as the primary driver of your SOC.</t>
   </si>
   <si>
+    <t>FL-119</t>
+  </si>
+  <si>
     <t>Utilizing bio-fumigants or solarization protects the massive microbial populations sustaining high carbon.</t>
   </si>
   <si>
     <t>Continue excellent biological management.</t>
   </si>
   <si>
+    <t>FL-120</t>
+  </si>
+  <si>
     <t>Eliminating broad-spectrum fumigants is mandatory to protect the delicate microbiome of elite vegetable soils.</t>
   </si>
   <si>
     <t>Maintain flawless execution of biological alternatives.</t>
   </si>
   <si>
-    <t>FL03-01-03-VL</t>
+    <t>FL-121</t>
   </si>
   <si>
     <t>Off-Season Fallow Management</t>
@@ -3654,7 +3894,7 @@
     <t>Plant a scavenger cover crop immediately to stabilize the soil.</t>
   </si>
   <si>
-    <t>FL03-01-03-L</t>
+    <t>FL-122</t>
   </si>
   <si>
     <t>Bare summer fallows act as an incinerator for soil carbon, destroying necessary organic matter.</t>
@@ -3663,7 +3903,7 @@
     <t>Eliminate bare fallows to hold water and nutrients for the next cash crop.</t>
   </si>
   <si>
-    <t>FL03-01-03-M</t>
+    <t>FL-123</t>
   </si>
   <si>
     <t>Good in-season practices are being held back by off-season bare fallows.</t>
@@ -3672,7 +3912,7 @@
     <t>Implement a summer cover crop as the most effective tool to reach the High zone.</t>
   </si>
   <si>
-    <t>FL03-01-03-H</t>
+    <t>FL-124</t>
   </si>
   <si>
     <t>Bare summer fallows put high SOC at severe risk of rapid oxidation.</t>
@@ -3681,7 +3921,7 @@
     <t>Protect this elite investment by keeping the soil covered year-round.</t>
   </si>
   <si>
-    <t>FL03-01-03-VH</t>
+    <t>FL-125</t>
   </si>
   <si>
     <t>Leaving an elite soil bare during summer mines the carbon bank and starves microbes.</t>
@@ -3690,6 +3930,9 @@
     <t>Maintain a living root to feed this massive microbial population.</t>
   </si>
   <si>
+    <t>FL-126</t>
+  </si>
+  <si>
     <t>High-Biomass Summer Cover (e.g., Sorghum-Sudangrass)</t>
   </si>
   <si>
@@ -3699,31 +3942,43 @@
     <t>Utilize sorghum-sudangrass to rapidly cool the soil before the next planting.</t>
   </si>
   <si>
+    <t>FL-127</t>
+  </si>
+  <si>
     <t>High biomass adds carbon bulk while deep roots break up compaction pans from bed-forming equipment.</t>
   </si>
   <si>
     <t>Continue this excellent strategy to improve physical structure.</t>
   </si>
   <si>
+    <t>FL-128</t>
+  </si>
+  <si>
     <t>High biomass protects against thunderstorms while naturally suppressing nematodes through bio-fumigation.</t>
   </si>
   <si>
     <t>Maintain this practice to build resilient vegetable soils.</t>
   </si>
   <si>
+    <t>FL-129</t>
+  </si>
+  <si>
     <t>Summer cover crops perfectly armor high carbon stocks while simultaneously starving out disease cycles.</t>
   </si>
   <si>
     <t>Continue utilizing high-biomass covers to protect the soil surface.</t>
   </si>
   <si>
+    <t>FL-130</t>
+  </si>
+  <si>
     <t>Maximum biological return sustains carbon levels despite the extreme disturbance of the cash crop season.</t>
   </si>
   <si>
     <t>Maintain high-biomass summer covers to feed elite microbial populations.</t>
   </si>
   <si>
-    <t>FL04-01-01-VL</t>
+    <t>FL-131</t>
   </si>
   <si>
     <t>Orchard Floor Management</t>
@@ -3738,7 +3993,7 @@
     <t>Allow native vegetation to establish between rows to stop carbon hemorrhaging.</t>
   </si>
   <si>
-    <t>FL04-01-01-L</t>
+    <t>FL-132</t>
   </si>
   <si>
     <t>Clean orchard floors expose soil to wind erosion and high summer temperatures.</t>
@@ -3747,7 +4002,7 @@
     <t>Introduce living roots in the row middles to accelerate microbial recovery.</t>
   </si>
   <si>
-    <t>FL04-01-01-M</t>
+    <t>FL-133</t>
   </si>
   <si>
     <t>Canopy litter maintains a baseline, but bare row middles act as a hard ceiling on SOC.</t>
@@ -3756,7 +4011,7 @@
     <t>Allow ground cover to grow to significantly lower soil temperatures and push SOC higher.</t>
   </si>
   <si>
-    <t>FL04-01-01-H</t>
+    <t>FL-134</t>
   </si>
   <si>
     <t>Exposed middles are highly vulnerable to rapid oxidation if canopy cover declines.</t>
@@ -3765,7 +4020,7 @@
     <t>Establish ground cover to protect high SOC from extreme weather events.</t>
   </si>
   <si>
-    <t>FL04-01-01-VH</t>
+    <t>FL-135</t>
   </si>
   <si>
     <t>Maintaining elite SOC is nearly impossible long-term without active root exudates in the middles.</t>
@@ -3774,6 +4029,9 @@
     <t>Establish permanent ground cover to prevent microbes from mining the existing carbon bank.</t>
   </si>
   <si>
+    <t>FL-136</t>
+  </si>
+  <si>
     <t>Mowed Sod / Native Vegetation</t>
   </si>
   <si>
@@ -3783,30 +4041,45 @@
     <t>Reduce mowing frequency to allow deeper root expansion and greater exudate release.</t>
   </si>
   <si>
+    <t>FL-137</t>
+  </si>
+  <si>
     <t>Sod provides a solid defensive baseline that protects against wind and water erosion.</t>
   </si>
   <si>
     <t>Diversify the sward or manage mowing heights to maximize root sloughing and build carbon.</t>
   </si>
   <si>
+    <t>FL-138</t>
+  </si>
+  <si>
     <t>Permanent ground cover maintains a stable biological cycle and buffers soil temperatures.</t>
   </si>
   <si>
     <t>Overseed the sod with a winter legume to balance the C:N ratio and push SOC higher.</t>
   </si>
   <si>
+    <t>FL-139</t>
+  </si>
+  <si>
     <t>Permanent root systems effectively protect carbon from oxidation in mature groves.</t>
   </si>
   <si>
     <t>Maintain this highly sustainable practice to lock in high carbon stocks.</t>
   </si>
   <si>
+    <t>FL-140</t>
+  </si>
+  <si>
     <t>Permanent, year-round ground cover is essential to maintaining high biological activity.</t>
   </si>
   <si>
     <t>Continue protecting the structural integrity of elite row middles with mowed sod.</t>
   </si>
   <si>
+    <t>FL-141</t>
+  </si>
+  <si>
     <t>Planted Cover Crop (Row Middles)</t>
   </si>
   <si>
@@ -3816,31 +4089,43 @@
     <t>Utilize deep-rooted mixes to jumpstart the recovery of the soil food web.</t>
   </si>
   <si>
+    <t>FL-142</t>
+  </si>
+  <si>
     <t>Planted covers are the fastest agronomic lever to build soil structure in an orchard.</t>
   </si>
   <si>
     <t>Ensure the mix contains deep-rooted grasses to break compaction and leave lasting surface biomass.</t>
   </si>
   <si>
+    <t>FL-143</t>
+  </si>
+  <si>
     <t>Diverse root exudates optimize humification, building resilient soils that buffer trees against drought.</t>
   </si>
   <si>
     <t>Maintain this active management to push your baseline higher.</t>
   </si>
   <si>
+    <t>FL-144</t>
+  </si>
+  <si>
     <t>Diverse living roots lock in high carbon stocks and cycle nutrients highly efficiently.</t>
   </si>
   <si>
     <t>Continue feeding the microbial food web with dedicated cover crop plantings.</t>
   </si>
   <si>
+    <t>FL-145</t>
+  </si>
+  <si>
     <t>Diverse, year-round living roots effortlessly sustain the massive biological demand of top-tier soil.</t>
   </si>
   <si>
     <t>Maintain elite management by ensuring continuous cover crop presence.</t>
   </si>
   <si>
-    <t>FL04-01-02-VL</t>
+    <t>FL-146</t>
   </si>
   <si>
     <t>Pruning &amp; Canopy Residue</t>
@@ -3855,7 +4140,7 @@
     <t>Stop removing woody biomass and mulch it in place to rebuild SOC.</t>
   </si>
   <si>
-    <t>FL04-01-02-L</t>
+    <t>FL-147</t>
   </si>
   <si>
     <t>Removing woody biomass actively starves the fungal networks required to build stable macro-aggregates.</t>
@@ -3864,7 +4149,7 @@
     <t>Retain all prunings to provide the ultimate fungal food source.</t>
   </si>
   <si>
-    <t>FL04-01-02-M</t>
+    <t>FL-148</t>
   </si>
   <si>
     <t>Burning prunings sacrifices the long-term particulate organic matter needed to reach the High zone.</t>
@@ -3873,7 +4158,7 @@
     <t>Retain prunings as your best source of slow-release carbon.</t>
   </si>
   <si>
-    <t>FL04-01-02-H</t>
+    <t>FL-149</t>
   </si>
   <si>
     <t>Exporting woody debris mines the carbon bank and will eventually degrade the high SOC baseline.</t>
@@ -3882,7 +4167,7 @@
     <t>Return all pruning biomass to protect the biological system.</t>
   </si>
   <si>
-    <t>FL04-01-02-VH</t>
+    <t>FL-150</t>
   </si>
   <si>
     <t>Burning or removing prunings is highly unsustainable for elite soils requiring massive carbon returns.</t>
@@ -3891,6 +4176,9 @@
     <t>Retain 100% of woody biomass to sustain elite biological populations.</t>
   </si>
   <si>
+    <t>FL-151</t>
+  </si>
+  <si>
     <t>Chipped &amp; Mulched in Place</t>
   </si>
   <si>
@@ -3900,31 +4188,43 @@
     <t>Continue chipping prunings to protect soil moisture and jumpstart degraded sands.</t>
   </si>
   <si>
+    <t>FL-152</t>
+  </si>
+  <si>
     <t>Mulching prunings under the canopy creates a fantastic fungal-dominant environment.</t>
   </si>
   <si>
     <t>Maintain this critical step to rebuild structural aggregates in sandy soils.</t>
   </si>
   <si>
+    <t>FL-153</t>
+  </si>
+  <si>
     <t>Chipped wood provides a slow, steady drip of carbon that buffers soil temperatures.</t>
   </si>
   <si>
     <t>Continue this excellent practice to push the baseline higher.</t>
   </si>
   <si>
+    <t>FL-154</t>
+  </si>
+  <si>
     <t>Returning woody biomass to the surface perfectly mimics natural forest systems to protect carbon stocks.</t>
   </si>
   <si>
     <t>Maintain this practice to sustain high biological activity.</t>
   </si>
   <si>
+    <t>FL-155</t>
+  </si>
+  <si>
     <t>Chipping and leaving all woody debris perfectly feeds massive microbial populations.</t>
   </si>
   <si>
     <t>Continue maximum carbon return to maintain elite SOC levels indefinitely.</t>
   </si>
   <si>
-    <t>FL05-01-01-VL</t>
+    <t>FL-156</t>
   </si>
   <si>
     <t>Site Preparation</t>
@@ -3939,7 +4239,7 @@
     <t>Avoid root raking entirely and transition to chemical site prep to stop the hemorrhage.</t>
   </si>
   <si>
-    <t>FL05-01-01-L</t>
+    <t>FL-157</t>
   </si>
   <si>
     <t>Bedding exposes mineral soil and accelerates microbial burnout, sacrificing long-term SOC.</t>
@@ -3948,7 +4248,7 @@
     <t>Keep beds as low and undisturbed as physically possible to maintain drainage.</t>
   </si>
   <si>
-    <t>FL05-01-01-M</t>
+    <t>FL-158</t>
   </si>
   <si>
     <t>Heavy disturbance burns off surface organic gains early in the rotation, acting as a ceiling on SOC.</t>
@@ -3957,7 +4257,7 @@
     <t>Reduce mechanical prep intensity to break through to the High zone.</t>
   </si>
   <si>
-    <t>FL05-01-01-H</t>
+    <t>FL-159</t>
   </si>
   <si>
     <t>Disrupting established fungal networks with heavy mechanical prep puts high SOC at severe risk.</t>
@@ -3966,7 +4266,7 @@
     <t>Transition away from intensive tillage to protect soil health gains.</t>
   </si>
   <si>
-    <t>FL05-01-01-VH</t>
+    <t>FL-160</t>
   </si>
   <si>
     <t>Intensive mechanical site prep is highly destructive to elite biological structures.</t>
@@ -3975,6 +4275,9 @@
     <t>Move strictly to minimal disturbance to preserve the physical integrity of the forest floor.</t>
   </si>
   <si>
+    <t>FL-161</t>
+  </si>
+  <si>
     <t>Minimal / Chemical Prep Only</t>
   </si>
   <si>
@@ -3984,31 +4287,43 @@
     <t>Continue minimal prep to improve water infiltration and rebuild degraded structure.</t>
   </si>
   <si>
+    <t>FL-162</t>
+  </si>
+  <si>
     <t>Avoiding tillage protects the fragile O-horizon from extreme heat.</t>
   </si>
   <si>
     <t>Maintain this critical first step to rebuild particulate organic matter.</t>
   </si>
   <si>
+    <t>FL-163</t>
+  </si>
+  <si>
     <t>Bypassing heavy tillage preserves established fungal networks and the surface organic layer.</t>
   </si>
   <si>
     <t>Continue minimal prep to push the SOC baseline higher right from planting.</t>
   </si>
   <si>
+    <t>FL-164</t>
+  </si>
+  <si>
     <t>This low-disturbance approach perfectly mimics natural forest succession to protect carbon stocks.</t>
   </si>
   <si>
     <t>Maintain this excellent strategy to sustain high SOC.</t>
   </si>
   <si>
+    <t>FL-165</t>
+  </si>
+  <si>
     <t>Minimal site prep perfectly preserves the massive biological investment of the previous rotation.</t>
   </si>
   <si>
     <t>Mandatory maintenance of this practice is required to keep elite status.</t>
   </si>
   <si>
-    <t>FL05-01-02-VL</t>
+    <t>FL-166</t>
   </si>
   <si>
     <t>Understory &amp; Residue Management</t>
@@ -4023,7 +4338,7 @@
     <t>Lengthen burn intervals to allow organic matter accumulation on depleted soils.</t>
   </si>
   <si>
-    <t>FL05-01-02-L</t>
+    <t>FL-167</t>
   </si>
   <si>
     <t>Frequent burning consumes surface biomass before it can humify into stable soil carbon.</t>
@@ -4032,7 +4347,7 @@
     <t>Utilize cooler, patchier burns to leave unburned residue.</t>
   </si>
   <si>
-    <t>FL05-01-02-M</t>
+    <t>FL-168</t>
   </si>
   <si>
     <t>Regular burning acts as a bottleneck on SOC, sacrificing slow-release carbon for quick ash nutrients.</t>
@@ -4041,7 +4356,7 @@
     <t>Reduce fire frequency or intensity to push into the High zone.</t>
   </si>
   <si>
-    <t>FL05-01-02-H</t>
+    <t>FL-169</t>
   </si>
   <si>
     <t>High SOC is at risk if fires consume the protective duff layer.</t>
@@ -4050,7 +4365,7 @@
     <t>Ensure fires are lit only under high soil-moisture conditions to preserve organic horizons.</t>
   </si>
   <si>
-    <t>FL05-01-02-VH</t>
+    <t>FL-170</t>
   </si>
   <si>
     <t>A fire that burns too hot will instantly erase decades of carbon sequestration.</t>
@@ -4059,6 +4374,9 @@
     <t>Manage fire extremely carefully to prevent consumption of the organic duff layer.</t>
   </si>
   <si>
+    <t>FL-171</t>
+  </si>
+  <si>
     <t>Roller Chopping / Cool Patchy Burns</t>
   </si>
   <si>
@@ -4068,31 +4386,43 @@
     <t>Continue this practice to jumpstart biological recovery in degraded sands.</t>
   </si>
   <si>
+    <t>FL-172</t>
+  </si>
+  <si>
     <t>Crushing brush manages competition while retaining organic armor to cool the soil surface.</t>
   </si>
   <si>
     <t>Maintain this great balance of hazard reduction and carbon retention.</t>
   </si>
   <si>
+    <t>FL-173</t>
+  </si>
+  <si>
     <t>Returning crushed, recalcitrant carbon builds particulate organic matter without wildfire risk.</t>
   </si>
   <si>
     <t>Continue this excellent management to feed the fungal web.</t>
   </si>
   <si>
+    <t>FL-174</t>
+  </si>
+  <si>
     <t>Slow decomposition of woody debris provides a steady drip of carbon into the mineral soil.</t>
   </si>
   <si>
     <t>Maintain this practice to perfectly sustain high biological activity.</t>
   </si>
   <si>
+    <t>FL-175</t>
+  </si>
+  <si>
     <t>Leaving unburned woody debris feeds massive fungal populations that sustain structural integrity.</t>
   </si>
   <si>
     <t>Continue flawless execution of mechanical understory management.</t>
   </si>
   <si>
-    <t>FL05-01-03-VL</t>
+    <t>FL-176</t>
   </si>
   <si>
     <t>Rotation Length</t>
@@ -4107,7 +4437,7 @@
     <t>Minimize harvest traffic and heavy equipment use to protect what little structure remains.</t>
   </si>
   <si>
-    <t>FL05-01-03-L</t>
+    <t>FL-177</t>
   </si>
   <si>
     <t>Short cycles limit the amount of deep, stable carbon pine roots can sequester before resetting.</t>
@@ -4116,7 +4446,7 @@
     <t>Ensure logging equipment stays strictly on designated skid trails to limit compaction.</t>
   </si>
   <si>
-    <t>FL05-01-03-M</t>
+    <t>FL-178</t>
   </si>
   <si>
     <t>A 15-year cycle resets the biological clock before peak carbon sequestration occurs.</t>
@@ -4125,7 +4455,7 @@
     <t>Focus heavily on minimizing site prep disturbance to offset frequent canopy loss.</t>
   </si>
   <si>
-    <t>FL05-01-03-H</t>
+    <t>FL-179</t>
   </si>
   <si>
     <t>Maintaining high SOC on short rotations requires flawless, zero-disturbance harvesting.</t>
@@ -4134,7 +4464,7 @@
     <t>Strictly enforce harvest traffic controls to protect soil structure.</t>
   </si>
   <si>
-    <t>FL05-01-03-VH</t>
+    <t>FL-180</t>
   </si>
   <si>
     <t>Maintaining elite SOC with frequent harvest cycles is incredibly rare.</t>
@@ -4143,6 +4473,9 @@
     <t>Management of harvest residue and soil compaction must be absolutely perfect to sustain this tier.</t>
   </si>
   <si>
+    <t>FL-181</t>
+  </si>
+  <si>
     <t>Long Rotation Sawtimber (20+ Years)</t>
   </si>
   <si>
@@ -4152,31 +4485,43 @@
     <t>Protect the forest floor during thinning operations to allow rebuilding.</t>
   </si>
   <si>
+    <t>FL-182</t>
+  </si>
+  <si>
     <t>Extended periods of undisturbed growth naturally restore broken fungal networks.</t>
   </si>
   <si>
     <t>Ensure thinning operations do not cause excessive rutting or compaction.</t>
   </si>
   <si>
+    <t>FL-183</t>
+  </si>
+  <si>
     <t>The lack of major soil disturbance for two decades allows biological glues to stabilize the sand.</t>
   </si>
   <si>
     <t>Maintain this long rotation as the primary driver of your current SOC.</t>
   </si>
   <si>
+    <t>FL-184</t>
+  </si>
+  <si>
     <t>Massive, undisturbed root systems are locking in carbon gains and driving high SOC.</t>
   </si>
   <si>
     <t>Continue long rotation strategies to maintain extended biological stability.</t>
   </si>
   <si>
+    <t>FL-185</t>
+  </si>
+  <si>
     <t>Decades of undisturbed canopy cover and root expansion have created a premier carbon sink.</t>
   </si>
   <si>
     <t>Protect the soil during final harvest at all costs to maintain elite forestry management.</t>
   </si>
   <si>
-    <t>FL06-01-01-VL</t>
+    <t>FL-186</t>
   </si>
   <si>
     <t>Biomass Utilization</t>
@@ -4191,7 +4536,7 @@
     <t>Apply manure, compost, or biosolids to offset this export and rebuild the baseline.</t>
   </si>
   <si>
-    <t>FL06-01-01-L</t>
+    <t>FL-187</t>
   </si>
   <si>
     <t>Mining the soil's organic matter to produce hay prevents SOC recovery.</t>
@@ -4200,7 +4545,7 @@
     <t>Return carbon via grazing animals or heavy organic amendments to reverse degradation.</t>
   </si>
   <si>
-    <t>FL06-01-01-M</t>
+    <t>FL-188</t>
   </si>
   <si>
     <t>Continuous haying acts as a hard ceiling on average carbon stocks.</t>
@@ -4209,7 +4554,7 @@
     <t>Integrate grazing to cycle nutrients and biomass back into the soil and push into the High zone.</t>
   </si>
   <si>
-    <t>FL06-01-01-H</t>
+    <t>FL-189</t>
   </si>
   <si>
     <t>Continuous haying puts the elite carbon bank at risk of slow depletion over time.</t>
@@ -4218,7 +4563,7 @@
     <t>Monitor SOC closely and introduce nutrient cycling to protect the baseline.</t>
   </si>
   <si>
-    <t>FL06-01-01-VH</t>
+    <t>FL-190</t>
   </si>
   <si>
     <t>Maintaining elite SOC under continuous hay export is impossible without massive imported amendments.</t>
@@ -4227,6 +4572,9 @@
     <t>Return carbon to the soil organically to meet the massive biological demand.</t>
   </si>
   <si>
+    <t>FL-191</t>
+  </si>
+  <si>
     <t>Grazed (Nutrient Cycling)</t>
   </si>
   <si>
@@ -4236,31 +4584,43 @@
     <t>Utilize hoof action and manure to jumpstart biological recovery in degraded pastures.</t>
   </si>
   <si>
+    <t>FL-192</t>
+  </si>
+  <si>
     <t>Manure feeds the microbial food web while hoof action incorporates litter.</t>
   </si>
   <si>
     <t>Ensure grazing pressure isn't too high so the grass can produce enough biomass to cycle.</t>
   </si>
   <si>
+    <t>FL-193</t>
+  </si>
+  <si>
     <t>Biological cycling of returned carbon actively builds aggregate stability.</t>
   </si>
   <si>
     <t>Maintain grazing integration as the foundation of your pasture's health.</t>
   </si>
   <si>
+    <t>FL-194</t>
+  </si>
+  <si>
     <t>Constant return of organic matter from livestock sustains high soil carbon levels.</t>
   </si>
   <si>
     <t>Continue perfect management of the nutrient cycle.</t>
   </si>
   <si>
+    <t>FL-195</t>
+  </si>
+  <si>
     <t>The grazing system has created a hyper-efficient, closed-loop nutrient cycle.</t>
   </si>
   <si>
     <t>Maintain elite biological management to effortlessly sustain peak carbon capacity.</t>
   </si>
   <si>
-    <t>FL06-01-02-VL</t>
+    <t>FL-196</t>
   </si>
   <si>
     <t>Grazing Pressure &amp; Rotation</t>
@@ -4275,7 +4635,7 @@
     <t>Reduce stocking rates or implement rest periods immediately to allow recovery.</t>
   </si>
   <si>
-    <t>FL06-01-02-L</t>
+    <t>FL-197</t>
   </si>
   <si>
     <t>Heavy grazing creates bare spots that expose sand to intense heat, accelerating oxidation.</t>
@@ -4284,7 +4644,7 @@
     <t>Implement rest periods to give the pasture time to recover and armor the soil.</t>
   </si>
   <si>
-    <t>FL06-01-02-M</t>
+    <t>FL-198</t>
   </si>
   <si>
     <t>Constant grazing pressure prevents the deep root expansion needed to push into the High zone.</t>
@@ -4293,7 +4653,7 @@
     <t>Adopt rotational grazing to encourage deep root exudation.</t>
   </si>
   <si>
-    <t>FL06-01-02-H</t>
+    <t>FL-199</t>
   </si>
   <si>
     <t>Continuous heavy grazing threatens high SOC by compacting the soil and reducing root biomass.</t>
@@ -4302,7 +4662,7 @@
     <t>Prevent overgrazing to protect the structural integrity of the soil.</t>
   </si>
   <si>
-    <t>FL06-01-02-VH</t>
+    <t>FL-200</t>
   </si>
   <si>
     <t>Compaction and shallow rooting will inevitably crash the biological capacity of elite pastures.</t>
@@ -4311,6 +4671,9 @@
     <t>Strictly prevent overgrazing to protect this massive carbon stock.</t>
   </si>
   <si>
+    <t>FL-201</t>
+  </si>
+  <si>
     <t>Rotational Grazing (With Rest Periods)</t>
   </si>
   <si>
@@ -4320,31 +4683,43 @@
     <t>Utilize strict rest periods to slowly rebuild the depleted baseline.</t>
   </si>
   <si>
+    <t>FL-202</t>
+  </si>
+  <si>
     <t>Rotational grazing prevents bare spots, cools the surface, and encourages deeper rooting.</t>
   </si>
   <si>
     <t>Continue this great defensive strategy to build particulate organic matter.</t>
   </si>
   <si>
+    <t>FL-203</t>
+  </si>
+  <si>
     <t>Pulse-grazing causes root sloughing, providing immediate fungal food to build stable aggregates.</t>
   </si>
   <si>
     <t>Maintain rotational grazing to push the score into the High zone.</t>
   </si>
   <si>
+    <t>FL-204</t>
+  </si>
+  <si>
     <t>Even distribution of manure and deep root recovery locks in high carbon stocks.</t>
   </si>
   <si>
     <t>Continue active management to perfectly feed the microbial food web.</t>
   </si>
   <si>
+    <t>FL-205</t>
+  </si>
+  <si>
     <t>Intensive rotational grazing perfectly sustains the massive biological carbon demand of top-tier soil.</t>
   </si>
   <si>
     <t>Maintain flawless execution of rotational rest periods.</t>
   </si>
   <si>
-    <t>FL06-01-03-VL</t>
+    <t>FL-206</t>
   </si>
   <si>
     <t>Winter Management</t>
@@ -4359,7 +4734,7 @@
     <t>Plant winter rye, oats, or clover to accelerate biological recovery year-round.</t>
   </si>
   <si>
-    <t>FL06-01-03-L</t>
+    <t>FL-207</t>
   </si>
   <si>
     <t>Winter biomass prevents carbon oxidation during dormancy and provides critical surface armor.</t>
@@ -4368,7 +4743,7 @@
     <t>Continue overseeding to protect the soil surface.</t>
   </si>
   <si>
-    <t>FL06-01-03-M</t>
+    <t>FL-208</t>
   </si>
   <si>
     <t>Integrating a winter legume provides a nitrogen credit while maximizing year-round root exudates.</t>
@@ -4377,7 +4752,7 @@
     <t>Maintain this excellent strategy to push SOC higher.</t>
   </si>
   <si>
-    <t>FL06-01-03-H</t>
+    <t>FL-209</t>
   </si>
   <si>
     <t>Overseeding prevents the microbial die-off that typically occurs during winter dormancy.</t>
@@ -4386,7 +4761,7 @@
     <t>Continue maintaining the biological momentum of the pasture year-round.</t>
   </si>
   <si>
-    <t>FL06-01-03-VH</t>
+    <t>FL-210</t>
   </si>
   <si>
     <t>Maintaining year-round active root exudates perfectly sustains hyper-active microbial populations.</t>
@@ -19115,7 +19490,7 @@
         <v>883</v>
       </c>
       <c r="B392" s="31" t="s">
-        <v>884</v>
+        <v>900</v>
       </c>
       <c r="C392" s="31" t="s">
         <v>11</v>
@@ -19130,16 +19505,16 @@
         <v>14</v>
       </c>
       <c r="G392" s="31" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H392" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I392" s="31" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="J392" s="31" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="393" spans="1:10" ht="15.75">
@@ -19147,7 +19522,7 @@
         <v>883</v>
       </c>
       <c r="B393" s="31" t="s">
-        <v>888</v>
+        <v>904</v>
       </c>
       <c r="C393" s="31" t="s">
         <v>11</v>
@@ -19162,16 +19537,16 @@
         <v>14</v>
       </c>
       <c r="G393" s="31" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H393" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I393" s="31" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="J393" s="31" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="394" spans="1:10" ht="15.75">
@@ -19179,7 +19554,7 @@
         <v>883</v>
       </c>
       <c r="B394" s="31" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="C394" s="31" t="s">
         <v>11</v>
@@ -19194,16 +19569,16 @@
         <v>14</v>
       </c>
       <c r="G394" s="31" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H394" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I394" s="31" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="J394" s="31" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
     </row>
     <row r="395" spans="1:10" ht="15.75">
@@ -19211,7 +19586,7 @@
         <v>883</v>
       </c>
       <c r="B395" s="31" t="s">
-        <v>894</v>
+        <v>910</v>
       </c>
       <c r="C395" s="31" t="s">
         <v>11</v>
@@ -19226,16 +19601,16 @@
         <v>14</v>
       </c>
       <c r="G395" s="31" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H395" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I395" s="31" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="J395" s="31" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
     </row>
     <row r="396" spans="1:10" ht="15.75">
@@ -19243,7 +19618,7 @@
         <v>883</v>
       </c>
       <c r="B396" s="31" t="s">
-        <v>897</v>
+        <v>913</v>
       </c>
       <c r="C396" s="31" t="s">
         <v>11</v>
@@ -19258,16 +19633,16 @@
         <v>14</v>
       </c>
       <c r="G396" s="31" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H396" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I396" s="31" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="J396" s="31" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="397" spans="1:10" ht="15.75">
@@ -19275,7 +19650,7 @@
         <v>883</v>
       </c>
       <c r="B397" s="31" t="s">
-        <v>884</v>
+        <v>916</v>
       </c>
       <c r="C397" s="31" t="s">
         <v>11</v>
@@ -19290,16 +19665,16 @@
         <v>14</v>
       </c>
       <c r="G397" s="31" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="H397" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I397" s="31" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="J397" s="31" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
     </row>
     <row r="398" spans="1:10" ht="15.75">
@@ -19307,7 +19682,7 @@
         <v>883</v>
       </c>
       <c r="B398" s="31" t="s">
-        <v>888</v>
+        <v>920</v>
       </c>
       <c r="C398" s="31" t="s">
         <v>11</v>
@@ -19322,16 +19697,16 @@
         <v>14</v>
       </c>
       <c r="G398" s="31" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="H398" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I398" s="31" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="J398" s="31" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
     </row>
     <row r="399" spans="1:10" ht="15.75">
@@ -19339,7 +19714,7 @@
         <v>883</v>
       </c>
       <c r="B399" s="31" t="s">
-        <v>891</v>
+        <v>923</v>
       </c>
       <c r="C399" s="31" t="s">
         <v>11</v>
@@ -19354,16 +19729,16 @@
         <v>14</v>
       </c>
       <c r="G399" s="31" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="H399" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I399" s="31" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="J399" s="31" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
     </row>
     <row r="400" spans="1:10" ht="15.75">
@@ -19371,7 +19746,7 @@
         <v>883</v>
       </c>
       <c r="B400" s="31" t="s">
-        <v>894</v>
+        <v>926</v>
       </c>
       <c r="C400" s="31" t="s">
         <v>11</v>
@@ -19386,16 +19761,16 @@
         <v>14</v>
       </c>
       <c r="G400" s="31" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="H400" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I400" s="31" t="s">
-        <v>918</v>
+        <v>927</v>
       </c>
       <c r="J400" s="31" t="s">
-        <v>919</v>
+        <v>928</v>
       </c>
     </row>
     <row r="401" spans="1:10" ht="15.75">
@@ -19403,7 +19778,7 @@
         <v>883</v>
       </c>
       <c r="B401" s="31" t="s">
-        <v>897</v>
+        <v>929</v>
       </c>
       <c r="C401" s="31" t="s">
         <v>11</v>
@@ -19418,16 +19793,16 @@
         <v>14</v>
       </c>
       <c r="G401" s="31" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="H401" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I401" s="31" t="s">
-        <v>920</v>
+        <v>930</v>
       </c>
       <c r="J401" s="31" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
     </row>
     <row r="402" spans="1:10" ht="15.75">
@@ -19435,7 +19810,7 @@
         <v>883</v>
       </c>
       <c r="B402" s="31" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="C402" s="31" t="s">
         <v>11</v>
@@ -19447,7 +19822,7 @@
         <v>13</v>
       </c>
       <c r="F402" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G402" s="31" t="s">
         <v>122</v>
@@ -19456,10 +19831,10 @@
         <v>16</v>
       </c>
       <c r="I402" s="31" t="s">
-        <v>924</v>
+        <v>934</v>
       </c>
       <c r="J402" s="31" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
     </row>
     <row r="403" spans="1:10" ht="15.75">
@@ -19467,7 +19842,7 @@
         <v>883</v>
       </c>
       <c r="B403" s="31" t="s">
-        <v>926</v>
+        <v>936</v>
       </c>
       <c r="C403" s="31" t="s">
         <v>11</v>
@@ -19479,7 +19854,7 @@
         <v>13</v>
       </c>
       <c r="F403" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G403" s="31" t="s">
         <v>122</v>
@@ -19488,10 +19863,10 @@
         <v>19</v>
       </c>
       <c r="I403" s="31" t="s">
-        <v>927</v>
+        <v>937</v>
       </c>
       <c r="J403" s="31" t="s">
-        <v>928</v>
+        <v>938</v>
       </c>
     </row>
     <row r="404" spans="1:10" ht="15.75">
@@ -19499,7 +19874,7 @@
         <v>883</v>
       </c>
       <c r="B404" s="31" t="s">
-        <v>929</v>
+        <v>939</v>
       </c>
       <c r="C404" s="31" t="s">
         <v>11</v>
@@ -19511,7 +19886,7 @@
         <v>13</v>
       </c>
       <c r="F404" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G404" s="31" t="s">
         <v>122</v>
@@ -19520,10 +19895,10 @@
         <v>22</v>
       </c>
       <c r="I404" s="31" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="J404" s="31" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
     </row>
     <row r="405" spans="1:10" ht="15.75">
@@ -19531,7 +19906,7 @@
         <v>883</v>
       </c>
       <c r="B405" s="31" t="s">
-        <v>932</v>
+        <v>942</v>
       </c>
       <c r="C405" s="31" t="s">
         <v>11</v>
@@ -19543,7 +19918,7 @@
         <v>13</v>
       </c>
       <c r="F405" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G405" s="31" t="s">
         <v>122</v>
@@ -19552,10 +19927,10 @@
         <v>25</v>
       </c>
       <c r="I405" s="31" t="s">
-        <v>933</v>
+        <v>943</v>
       </c>
       <c r="J405" s="31" t="s">
-        <v>934</v>
+        <v>944</v>
       </c>
     </row>
     <row r="406" spans="1:10" ht="15.75">
@@ -19563,7 +19938,7 @@
         <v>883</v>
       </c>
       <c r="B406" s="31" t="s">
-        <v>935</v>
+        <v>945</v>
       </c>
       <c r="C406" s="31" t="s">
         <v>11</v>
@@ -19575,7 +19950,7 @@
         <v>13</v>
       </c>
       <c r="F406" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G406" s="31" t="s">
         <v>122</v>
@@ -19584,10 +19959,10 @@
         <v>28</v>
       </c>
       <c r="I406" s="31" t="s">
-        <v>936</v>
+        <v>946</v>
       </c>
       <c r="J406" s="31" t="s">
-        <v>937</v>
+        <v>947</v>
       </c>
     </row>
     <row r="407" spans="1:10" ht="15.75">
@@ -19595,7 +19970,7 @@
         <v>883</v>
       </c>
       <c r="B407" s="31" t="s">
-        <v>922</v>
+        <v>948</v>
       </c>
       <c r="C407" s="31" t="s">
         <v>11</v>
@@ -19607,7 +19982,7 @@
         <v>13</v>
       </c>
       <c r="F407" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G407" s="31" t="s">
         <v>448</v>
@@ -19616,10 +19991,10 @@
         <v>16</v>
       </c>
       <c r="I407" s="31" t="s">
-        <v>938</v>
+        <v>949</v>
       </c>
       <c r="J407" s="31" t="s">
-        <v>939</v>
+        <v>950</v>
       </c>
     </row>
     <row r="408" spans="1:10" ht="15.75">
@@ -19627,7 +20002,7 @@
         <v>883</v>
       </c>
       <c r="B408" s="31" t="s">
-        <v>926</v>
+        <v>951</v>
       </c>
       <c r="C408" s="31" t="s">
         <v>11</v>
@@ -19639,7 +20014,7 @@
         <v>13</v>
       </c>
       <c r="F408" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G408" s="31" t="s">
         <v>448</v>
@@ -19648,10 +20023,10 @@
         <v>19</v>
       </c>
       <c r="I408" s="31" t="s">
-        <v>940</v>
+        <v>952</v>
       </c>
       <c r="J408" s="31" t="s">
-        <v>941</v>
+        <v>953</v>
       </c>
     </row>
     <row r="409" spans="1:10" ht="15.75">
@@ -19659,7 +20034,7 @@
         <v>883</v>
       </c>
       <c r="B409" s="31" t="s">
-        <v>929</v>
+        <v>954</v>
       </c>
       <c r="C409" s="31" t="s">
         <v>11</v>
@@ -19671,7 +20046,7 @@
         <v>13</v>
       </c>
       <c r="F409" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G409" s="31" t="s">
         <v>448</v>
@@ -19680,10 +20055,10 @@
         <v>22</v>
       </c>
       <c r="I409" s="31" t="s">
-        <v>942</v>
+        <v>955</v>
       </c>
       <c r="J409" s="31" t="s">
-        <v>943</v>
+        <v>956</v>
       </c>
     </row>
     <row r="410" spans="1:10" ht="15.75">
@@ -19691,7 +20066,7 @@
         <v>883</v>
       </c>
       <c r="B410" s="31" t="s">
-        <v>932</v>
+        <v>957</v>
       </c>
       <c r="C410" s="31" t="s">
         <v>11</v>
@@ -19703,7 +20078,7 @@
         <v>13</v>
       </c>
       <c r="F410" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G410" s="31" t="s">
         <v>448</v>
@@ -19712,10 +20087,10 @@
         <v>25</v>
       </c>
       <c r="I410" s="31" t="s">
-        <v>944</v>
+        <v>958</v>
       </c>
       <c r="J410" s="31" t="s">
-        <v>945</v>
+        <v>959</v>
       </c>
     </row>
     <row r="411" spans="1:10" ht="15.75">
@@ -19723,7 +20098,7 @@
         <v>883</v>
       </c>
       <c r="B411" s="31" t="s">
-        <v>935</v>
+        <v>960</v>
       </c>
       <c r="C411" s="31" t="s">
         <v>11</v>
@@ -19735,7 +20110,7 @@
         <v>13</v>
       </c>
       <c r="F411" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G411" s="31" t="s">
         <v>448</v>
@@ -19744,10 +20119,10 @@
         <v>28</v>
       </c>
       <c r="I411" s="31" t="s">
-        <v>946</v>
+        <v>961</v>
       </c>
       <c r="J411" s="31" t="s">
-        <v>947</v>
+        <v>962</v>
       </c>
     </row>
     <row r="412" spans="1:10" ht="15.75">
@@ -19755,7 +20130,7 @@
         <v>883</v>
       </c>
       <c r="B412" s="31" t="s">
-        <v>922</v>
+        <v>963</v>
       </c>
       <c r="C412" s="31" t="s">
         <v>11</v>
@@ -19767,19 +20142,19 @@
         <v>13</v>
       </c>
       <c r="F412" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G412" s="31" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="H412" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I412" s="31" t="s">
-        <v>949</v>
+        <v>965</v>
       </c>
       <c r="J412" s="31" t="s">
-        <v>950</v>
+        <v>966</v>
       </c>
     </row>
     <row r="413" spans="1:10" ht="15.75">
@@ -19787,7 +20162,7 @@
         <v>883</v>
       </c>
       <c r="B413" s="31" t="s">
-        <v>926</v>
+        <v>967</v>
       </c>
       <c r="C413" s="31" t="s">
         <v>11</v>
@@ -19799,19 +20174,19 @@
         <v>13</v>
       </c>
       <c r="F413" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G413" s="31" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="H413" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I413" s="31" t="s">
-        <v>951</v>
+        <v>968</v>
       </c>
       <c r="J413" s="31" t="s">
-        <v>952</v>
+        <v>969</v>
       </c>
     </row>
     <row r="414" spans="1:10" ht="15.75">
@@ -19819,7 +20194,7 @@
         <v>883</v>
       </c>
       <c r="B414" s="31" t="s">
-        <v>929</v>
+        <v>970</v>
       </c>
       <c r="C414" s="31" t="s">
         <v>11</v>
@@ -19831,19 +20206,19 @@
         <v>13</v>
       </c>
       <c r="F414" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G414" s="31" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="H414" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I414" s="31" t="s">
-        <v>953</v>
+        <v>971</v>
       </c>
       <c r="J414" s="31" t="s">
-        <v>954</v>
+        <v>972</v>
       </c>
     </row>
     <row r="415" spans="1:10" ht="15.75">
@@ -19851,7 +20226,7 @@
         <v>883</v>
       </c>
       <c r="B415" s="31" t="s">
-        <v>932</v>
+        <v>973</v>
       </c>
       <c r="C415" s="31" t="s">
         <v>11</v>
@@ -19863,19 +20238,19 @@
         <v>13</v>
       </c>
       <c r="F415" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G415" s="31" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="H415" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I415" s="31" t="s">
-        <v>955</v>
+        <v>974</v>
       </c>
       <c r="J415" s="31" t="s">
-        <v>956</v>
+        <v>975</v>
       </c>
     </row>
     <row r="416" spans="1:10" ht="15.75">
@@ -19883,7 +20258,7 @@
         <v>883</v>
       </c>
       <c r="B416" s="31" t="s">
-        <v>935</v>
+        <v>976</v>
       </c>
       <c r="C416" s="31" t="s">
         <v>11</v>
@@ -19895,19 +20270,19 @@
         <v>13</v>
       </c>
       <c r="F416" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G416" s="31" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="H416" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I416" s="31" t="s">
-        <v>957</v>
+        <v>977</v>
       </c>
       <c r="J416" s="31" t="s">
-        <v>958</v>
+        <v>978</v>
       </c>
     </row>
     <row r="417" spans="1:10" ht="15.75">
@@ -19915,7 +20290,7 @@
         <v>883</v>
       </c>
       <c r="B417" s="31" t="s">
-        <v>922</v>
+        <v>979</v>
       </c>
       <c r="C417" s="31" t="s">
         <v>11</v>
@@ -19927,19 +20302,19 @@
         <v>13</v>
       </c>
       <c r="F417" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G417" s="31" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
       <c r="H417" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I417" s="31" t="s">
-        <v>960</v>
+        <v>981</v>
       </c>
       <c r="J417" s="31" t="s">
-        <v>961</v>
+        <v>982</v>
       </c>
     </row>
     <row r="418" spans="1:10" ht="15.75">
@@ -19947,7 +20322,7 @@
         <v>883</v>
       </c>
       <c r="B418" s="31" t="s">
-        <v>926</v>
+        <v>983</v>
       </c>
       <c r="C418" s="31" t="s">
         <v>11</v>
@@ -19959,19 +20334,19 @@
         <v>13</v>
       </c>
       <c r="F418" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G418" s="31" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
       <c r="H418" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I418" s="31" t="s">
-        <v>962</v>
+        <v>984</v>
       </c>
       <c r="J418" s="31" t="s">
-        <v>963</v>
+        <v>985</v>
       </c>
     </row>
     <row r="419" spans="1:10" ht="15.75">
@@ -19979,7 +20354,7 @@
         <v>883</v>
       </c>
       <c r="B419" s="31" t="s">
-        <v>929</v>
+        <v>986</v>
       </c>
       <c r="C419" s="31" t="s">
         <v>11</v>
@@ -19991,19 +20366,19 @@
         <v>13</v>
       </c>
       <c r="F419" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G419" s="31" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
       <c r="H419" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I419" s="31" t="s">
-        <v>964</v>
+        <v>987</v>
       </c>
       <c r="J419" s="31" t="s">
-        <v>965</v>
+        <v>988</v>
       </c>
     </row>
     <row r="420" spans="1:10" ht="15.75">
@@ -20011,7 +20386,7 @@
         <v>883</v>
       </c>
       <c r="B420" s="31" t="s">
-        <v>932</v>
+        <v>989</v>
       </c>
       <c r="C420" s="31" t="s">
         <v>11</v>
@@ -20023,19 +20398,19 @@
         <v>13</v>
       </c>
       <c r="F420" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G420" s="31" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
       <c r="H420" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I420" s="31" t="s">
-        <v>966</v>
+        <v>990</v>
       </c>
       <c r="J420" s="31" t="s">
-        <v>967</v>
+        <v>991</v>
       </c>
     </row>
     <row r="421" spans="1:10" ht="15.75">
@@ -20043,7 +20418,7 @@
         <v>883</v>
       </c>
       <c r="B421" s="31" t="s">
-        <v>935</v>
+        <v>992</v>
       </c>
       <c r="C421" s="31" t="s">
         <v>11</v>
@@ -20055,19 +20430,19 @@
         <v>13</v>
       </c>
       <c r="F421" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G421" s="31" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
       <c r="H421" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I421" s="31" t="s">
-        <v>968</v>
+        <v>993</v>
       </c>
       <c r="J421" s="31" t="s">
-        <v>969</v>
+        <v>994</v>
       </c>
     </row>
     <row r="422" spans="1:10" ht="15.75">
@@ -20075,7 +20450,7 @@
         <v>883</v>
       </c>
       <c r="B422" s="31" t="s">
-        <v>922</v>
+        <v>995</v>
       </c>
       <c r="C422" s="31" t="s">
         <v>11</v>
@@ -20087,7 +20462,7 @@
         <v>13</v>
       </c>
       <c r="F422" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G422" s="31" t="s">
         <v>799</v>
@@ -20096,10 +20471,10 @@
         <v>16</v>
       </c>
       <c r="I422" s="31" t="s">
-        <v>970</v>
+        <v>996</v>
       </c>
       <c r="J422" s="31" t="s">
-        <v>971</v>
+        <v>997</v>
       </c>
     </row>
     <row r="423" spans="1:10" ht="15.75">
@@ -20107,7 +20482,7 @@
         <v>883</v>
       </c>
       <c r="B423" s="31" t="s">
-        <v>926</v>
+        <v>998</v>
       </c>
       <c r="C423" s="31" t="s">
         <v>11</v>
@@ -20119,7 +20494,7 @@
         <v>13</v>
       </c>
       <c r="F423" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G423" s="31" t="s">
         <v>799</v>
@@ -20128,10 +20503,10 @@
         <v>19</v>
       </c>
       <c r="I423" s="31" t="s">
-        <v>972</v>
+        <v>999</v>
       </c>
       <c r="J423" s="31" t="s">
-        <v>973</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="424" spans="1:10" ht="15.75">
@@ -20139,7 +20514,7 @@
         <v>883</v>
       </c>
       <c r="B424" s="31" t="s">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="C424" s="31" t="s">
         <v>11</v>
@@ -20151,7 +20526,7 @@
         <v>13</v>
       </c>
       <c r="F424" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G424" s="31" t="s">
         <v>799</v>
@@ -20160,10 +20535,10 @@
         <v>22</v>
       </c>
       <c r="I424" s="31" t="s">
-        <v>974</v>
+        <v>1002</v>
       </c>
       <c r="J424" s="31" t="s">
-        <v>975</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="425" spans="1:10" ht="15.75">
@@ -20171,7 +20546,7 @@
         <v>883</v>
       </c>
       <c r="B425" s="31" t="s">
-        <v>932</v>
+        <v>1004</v>
       </c>
       <c r="C425" s="31" t="s">
         <v>11</v>
@@ -20183,7 +20558,7 @@
         <v>13</v>
       </c>
       <c r="F425" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G425" s="31" t="s">
         <v>799</v>
@@ -20192,10 +20567,10 @@
         <v>25</v>
       </c>
       <c r="I425" s="31" t="s">
-        <v>976</v>
+        <v>1005</v>
       </c>
       <c r="J425" s="31" t="s">
-        <v>977</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="426" spans="1:10" ht="15.75">
@@ -20203,7 +20578,7 @@
         <v>883</v>
       </c>
       <c r="B426" s="31" t="s">
-        <v>935</v>
+        <v>1007</v>
       </c>
       <c r="C426" s="31" t="s">
         <v>11</v>
@@ -20215,7 +20590,7 @@
         <v>13</v>
       </c>
       <c r="F426" s="31" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="G426" s="31" t="s">
         <v>799</v>
@@ -20224,10 +20599,10 @@
         <v>28</v>
       </c>
       <c r="I426" s="31" t="s">
-        <v>978</v>
+        <v>1008</v>
       </c>
       <c r="J426" s="31" t="s">
-        <v>979</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="427" spans="1:10" ht="15.75">
@@ -20235,7 +20610,7 @@
         <v>883</v>
       </c>
       <c r="B427" s="31" t="s">
-        <v>980</v>
+        <v>1010</v>
       </c>
       <c r="C427" s="31" t="s">
         <v>11</v>
@@ -20247,7 +20622,7 @@
         <v>13</v>
       </c>
       <c r="F427" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G427" s="31" t="s">
         <v>122</v>
@@ -20256,10 +20631,10 @@
         <v>16</v>
       </c>
       <c r="I427" s="31" t="s">
-        <v>982</v>
+        <v>1012</v>
       </c>
       <c r="J427" s="31" t="s">
-        <v>983</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="428" spans="1:10" ht="15.75">
@@ -20267,7 +20642,7 @@
         <v>883</v>
       </c>
       <c r="B428" s="31" t="s">
-        <v>984</v>
+        <v>1014</v>
       </c>
       <c r="C428" s="31" t="s">
         <v>11</v>
@@ -20279,7 +20654,7 @@
         <v>13</v>
       </c>
       <c r="F428" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G428" s="31" t="s">
         <v>122</v>
@@ -20288,10 +20663,10 @@
         <v>19</v>
       </c>
       <c r="I428" s="31" t="s">
-        <v>985</v>
+        <v>1015</v>
       </c>
       <c r="J428" s="31" t="s">
-        <v>986</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="429" spans="1:10" ht="15.75">
@@ -20299,7 +20674,7 @@
         <v>883</v>
       </c>
       <c r="B429" s="31" t="s">
-        <v>987</v>
+        <v>1017</v>
       </c>
       <c r="C429" s="31" t="s">
         <v>11</v>
@@ -20311,7 +20686,7 @@
         <v>13</v>
       </c>
       <c r="F429" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G429" s="31" t="s">
         <v>122</v>
@@ -20320,10 +20695,10 @@
         <v>22</v>
       </c>
       <c r="I429" s="31" t="s">
-        <v>988</v>
+        <v>1018</v>
       </c>
       <c r="J429" s="31" t="s">
-        <v>989</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="430" spans="1:10" ht="15.75">
@@ -20331,7 +20706,7 @@
         <v>883</v>
       </c>
       <c r="B430" s="31" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="C430" s="31" t="s">
         <v>11</v>
@@ -20343,7 +20718,7 @@
         <v>13</v>
       </c>
       <c r="F430" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G430" s="31" t="s">
         <v>122</v>
@@ -20352,10 +20727,10 @@
         <v>25</v>
       </c>
       <c r="I430" s="31" t="s">
-        <v>991</v>
+        <v>1021</v>
       </c>
       <c r="J430" s="31" t="s">
-        <v>992</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="431" spans="1:10" ht="15.75">
@@ -20363,7 +20738,7 @@
         <v>883</v>
       </c>
       <c r="B431" s="31" t="s">
-        <v>993</v>
+        <v>1023</v>
       </c>
       <c r="C431" s="31" t="s">
         <v>11</v>
@@ -20375,7 +20750,7 @@
         <v>13</v>
       </c>
       <c r="F431" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G431" s="31" t="s">
         <v>122</v>
@@ -20384,10 +20759,10 @@
         <v>28</v>
       </c>
       <c r="I431" s="31" t="s">
-        <v>994</v>
+        <v>1024</v>
       </c>
       <c r="J431" s="31" t="s">
-        <v>995</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="432" spans="1:10" ht="15.75">
@@ -20395,7 +20770,7 @@
         <v>883</v>
       </c>
       <c r="B432" s="31" t="s">
-        <v>980</v>
+        <v>1026</v>
       </c>
       <c r="C432" s="31" t="s">
         <v>11</v>
@@ -20407,19 +20782,19 @@
         <v>13</v>
       </c>
       <c r="F432" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G432" s="31" t="s">
-        <v>996</v>
+        <v>1027</v>
       </c>
       <c r="H432" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I432" s="31" t="s">
-        <v>997</v>
+        <v>1028</v>
       </c>
       <c r="J432" s="31" t="s">
-        <v>998</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="433" spans="1:10" ht="15.75">
@@ -20427,7 +20802,7 @@
         <v>883</v>
       </c>
       <c r="B433" s="31" t="s">
-        <v>984</v>
+        <v>1030</v>
       </c>
       <c r="C433" s="31" t="s">
         <v>11</v>
@@ -20439,19 +20814,19 @@
         <v>13</v>
       </c>
       <c r="F433" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G433" s="31" t="s">
-        <v>996</v>
+        <v>1027</v>
       </c>
       <c r="H433" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I433" s="31" t="s">
-        <v>999</v>
+        <v>1031</v>
       </c>
       <c r="J433" s="31" t="s">
-        <v>1000</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="434" spans="1:10" ht="15.75">
@@ -20459,7 +20834,7 @@
         <v>883</v>
       </c>
       <c r="B434" s="31" t="s">
-        <v>987</v>
+        <v>1033</v>
       </c>
       <c r="C434" s="31" t="s">
         <v>11</v>
@@ -20471,19 +20846,19 @@
         <v>13</v>
       </c>
       <c r="F434" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G434" s="31" t="s">
-        <v>996</v>
+        <v>1027</v>
       </c>
       <c r="H434" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I434" s="31" t="s">
-        <v>1001</v>
+        <v>1034</v>
       </c>
       <c r="J434" s="31" t="s">
-        <v>1002</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="435" spans="1:10" ht="15.75">
@@ -20491,7 +20866,7 @@
         <v>883</v>
       </c>
       <c r="B435" s="31" t="s">
-        <v>990</v>
+        <v>1036</v>
       </c>
       <c r="C435" s="31" t="s">
         <v>11</v>
@@ -20503,19 +20878,19 @@
         <v>13</v>
       </c>
       <c r="F435" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G435" s="31" t="s">
-        <v>996</v>
+        <v>1027</v>
       </c>
       <c r="H435" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I435" s="31" t="s">
-        <v>1003</v>
+        <v>1037</v>
       </c>
       <c r="J435" s="31" t="s">
-        <v>1004</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="436" spans="1:10" ht="15.75">
@@ -20523,7 +20898,7 @@
         <v>883</v>
       </c>
       <c r="B436" s="31" t="s">
-        <v>993</v>
+        <v>1039</v>
       </c>
       <c r="C436" s="31" t="s">
         <v>11</v>
@@ -20535,19 +20910,19 @@
         <v>13</v>
       </c>
       <c r="F436" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G436" s="31" t="s">
-        <v>996</v>
+        <v>1027</v>
       </c>
       <c r="H436" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I436" s="31" t="s">
-        <v>1005</v>
+        <v>1040</v>
       </c>
       <c r="J436" s="31" t="s">
-        <v>1006</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="437" spans="1:10" ht="15.75">
@@ -20555,7 +20930,7 @@
         <v>883</v>
       </c>
       <c r="B437" s="31" t="s">
-        <v>980</v>
+        <v>1042</v>
       </c>
       <c r="C437" s="31" t="s">
         <v>11</v>
@@ -20567,19 +20942,19 @@
         <v>13</v>
       </c>
       <c r="F437" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G437" s="31" t="s">
-        <v>1007</v>
+        <v>1043</v>
       </c>
       <c r="H437" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I437" s="31" t="s">
-        <v>1008</v>
+        <v>1044</v>
       </c>
       <c r="J437" s="31" t="s">
-        <v>1009</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="438" spans="1:10" ht="15.75">
@@ -20587,7 +20962,7 @@
         <v>883</v>
       </c>
       <c r="B438" s="31" t="s">
-        <v>984</v>
+        <v>1046</v>
       </c>
       <c r="C438" s="31" t="s">
         <v>11</v>
@@ -20599,19 +20974,19 @@
         <v>13</v>
       </c>
       <c r="F438" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G438" s="31" t="s">
-        <v>1007</v>
+        <v>1043</v>
       </c>
       <c r="H438" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I438" s="31" t="s">
-        <v>1010</v>
+        <v>1047</v>
       </c>
       <c r="J438" s="31" t="s">
-        <v>1011</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="439" spans="1:10" ht="15.75">
@@ -20619,7 +20994,7 @@
         <v>883</v>
       </c>
       <c r="B439" s="31" t="s">
-        <v>987</v>
+        <v>1049</v>
       </c>
       <c r="C439" s="31" t="s">
         <v>11</v>
@@ -20631,19 +21006,19 @@
         <v>13</v>
       </c>
       <c r="F439" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G439" s="31" t="s">
-        <v>1007</v>
+        <v>1043</v>
       </c>
       <c r="H439" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I439" s="31" t="s">
-        <v>1012</v>
+        <v>1050</v>
       </c>
       <c r="J439" s="31" t="s">
-        <v>1013</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="440" spans="1:10" ht="15.75">
@@ -20651,7 +21026,7 @@
         <v>883</v>
       </c>
       <c r="B440" s="31" t="s">
-        <v>990</v>
+        <v>1052</v>
       </c>
       <c r="C440" s="31" t="s">
         <v>11</v>
@@ -20663,19 +21038,19 @@
         <v>13</v>
       </c>
       <c r="F440" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G440" s="31" t="s">
-        <v>1007</v>
+        <v>1043</v>
       </c>
       <c r="H440" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I440" s="31" t="s">
-        <v>1014</v>
+        <v>1053</v>
       </c>
       <c r="J440" s="31" t="s">
-        <v>1015</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="441" spans="1:10" ht="15.75">
@@ -20683,7 +21058,7 @@
         <v>883</v>
       </c>
       <c r="B441" s="31" t="s">
-        <v>993</v>
+        <v>1055</v>
       </c>
       <c r="C441" s="31" t="s">
         <v>11</v>
@@ -20695,19 +21070,19 @@
         <v>13</v>
       </c>
       <c r="F441" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G441" s="31" t="s">
-        <v>1007</v>
+        <v>1043</v>
       </c>
       <c r="H441" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I441" s="31" t="s">
-        <v>1016</v>
+        <v>1056</v>
       </c>
       <c r="J441" s="31" t="s">
-        <v>1017</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="442" spans="1:10" ht="15.75">
@@ -20715,7 +21090,7 @@
         <v>883</v>
       </c>
       <c r="B442" s="31" t="s">
-        <v>980</v>
+        <v>1058</v>
       </c>
       <c r="C442" s="31" t="s">
         <v>11</v>
@@ -20727,19 +21102,19 @@
         <v>13</v>
       </c>
       <c r="F442" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G442" s="31" t="s">
-        <v>1018</v>
+        <v>1059</v>
       </c>
       <c r="H442" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I442" s="31" t="s">
-        <v>1019</v>
+        <v>1060</v>
       </c>
       <c r="J442" s="31" t="s">
-        <v>1020</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="443" spans="1:10" ht="15.75">
@@ -20747,7 +21122,7 @@
         <v>883</v>
       </c>
       <c r="B443" s="31" t="s">
-        <v>984</v>
+        <v>1062</v>
       </c>
       <c r="C443" s="31" t="s">
         <v>11</v>
@@ -20759,19 +21134,19 @@
         <v>13</v>
       </c>
       <c r="F443" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G443" s="31" t="s">
-        <v>1018</v>
+        <v>1059</v>
       </c>
       <c r="H443" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I443" s="31" t="s">
-        <v>1021</v>
+        <v>1063</v>
       </c>
       <c r="J443" s="31" t="s">
-        <v>1022</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="444" spans="1:10" ht="15.75">
@@ -20779,7 +21154,7 @@
         <v>883</v>
       </c>
       <c r="B444" s="31" t="s">
-        <v>987</v>
+        <v>1065</v>
       </c>
       <c r="C444" s="31" t="s">
         <v>11</v>
@@ -20791,19 +21166,19 @@
         <v>13</v>
       </c>
       <c r="F444" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G444" s="31" t="s">
-        <v>1018</v>
+        <v>1059</v>
       </c>
       <c r="H444" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I444" s="31" t="s">
-        <v>1023</v>
+        <v>1066</v>
       </c>
       <c r="J444" s="31" t="s">
-        <v>1024</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="445" spans="1:10" ht="15.75">
@@ -20811,7 +21186,7 @@
         <v>883</v>
       </c>
       <c r="B445" s="31" t="s">
-        <v>990</v>
+        <v>1068</v>
       </c>
       <c r="C445" s="31" t="s">
         <v>11</v>
@@ -20823,19 +21198,19 @@
         <v>13</v>
       </c>
       <c r="F445" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G445" s="31" t="s">
-        <v>1018</v>
+        <v>1059</v>
       </c>
       <c r="H445" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I445" s="31" t="s">
-        <v>1025</v>
+        <v>1069</v>
       </c>
       <c r="J445" s="31" t="s">
-        <v>1026</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="446" spans="1:10" ht="15.75">
@@ -20843,7 +21218,7 @@
         <v>883</v>
       </c>
       <c r="B446" s="31" t="s">
-        <v>993</v>
+        <v>1071</v>
       </c>
       <c r="C446" s="31" t="s">
         <v>11</v>
@@ -20855,19 +21230,19 @@
         <v>13</v>
       </c>
       <c r="F446" s="31" t="s">
-        <v>981</v>
+        <v>1011</v>
       </c>
       <c r="G446" s="31" t="s">
-        <v>1018</v>
+        <v>1059</v>
       </c>
       <c r="H446" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I446" s="31" t="s">
-        <v>1027</v>
+        <v>1072</v>
       </c>
       <c r="J446" s="31" t="s">
-        <v>1028</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="447" spans="1:10" ht="15.75">
@@ -20875,7 +21250,7 @@
         <v>883</v>
       </c>
       <c r="B447" s="31" t="s">
-        <v>1029</v>
+        <v>1074</v>
       </c>
       <c r="C447" s="31" t="s">
         <v>604</v>
@@ -20884,22 +21259,22 @@
         <v>605</v>
       </c>
       <c r="E447" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F447" s="31" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="G447" s="31" t="s">
-        <v>1032</v>
+        <v>1077</v>
       </c>
       <c r="H447" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I447" s="31" t="s">
-        <v>1033</v>
+        <v>1078</v>
       </c>
       <c r="J447" s="31" t="s">
-        <v>1034</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="448" spans="1:10" ht="15.75">
@@ -20907,7 +21282,7 @@
         <v>883</v>
       </c>
       <c r="B448" s="31" t="s">
-        <v>1035</v>
+        <v>1080</v>
       </c>
       <c r="C448" s="31" t="s">
         <v>604</v>
@@ -20916,22 +21291,22 @@
         <v>605</v>
       </c>
       <c r="E448" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F448" s="31" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="G448" s="31" t="s">
-        <v>1032</v>
+        <v>1077</v>
       </c>
       <c r="H448" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I448" s="31" t="s">
-        <v>1036</v>
+        <v>1081</v>
       </c>
       <c r="J448" s="31" t="s">
-        <v>1037</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="449" spans="1:10" ht="15.75">
@@ -20939,7 +21314,7 @@
         <v>883</v>
       </c>
       <c r="B449" s="31" t="s">
-        <v>1038</v>
+        <v>1083</v>
       </c>
       <c r="C449" s="31" t="s">
         <v>604</v>
@@ -20948,22 +21323,22 @@
         <v>605</v>
       </c>
       <c r="E449" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F449" s="31" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="G449" s="31" t="s">
-        <v>1032</v>
+        <v>1077</v>
       </c>
       <c r="H449" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I449" s="31" t="s">
-        <v>1039</v>
+        <v>1084</v>
       </c>
       <c r="J449" s="31" t="s">
-        <v>1040</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="450" spans="1:10" ht="15.75">
@@ -20971,7 +21346,7 @@
         <v>883</v>
       </c>
       <c r="B450" s="31" t="s">
-        <v>1041</v>
+        <v>1086</v>
       </c>
       <c r="C450" s="31" t="s">
         <v>604</v>
@@ -20980,22 +21355,22 @@
         <v>605</v>
       </c>
       <c r="E450" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F450" s="31" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="G450" s="31" t="s">
-        <v>1032</v>
+        <v>1077</v>
       </c>
       <c r="H450" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I450" s="31" t="s">
-        <v>1042</v>
+        <v>1087</v>
       </c>
       <c r="J450" s="31" t="s">
-        <v>1043</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="451" spans="1:10" ht="15.75">
@@ -21003,7 +21378,7 @@
         <v>883</v>
       </c>
       <c r="B451" s="31" t="s">
-        <v>1044</v>
+        <v>1089</v>
       </c>
       <c r="C451" s="31" t="s">
         <v>604</v>
@@ -21012,22 +21387,22 @@
         <v>605</v>
       </c>
       <c r="E451" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F451" s="31" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="G451" s="31" t="s">
-        <v>1032</v>
+        <v>1077</v>
       </c>
       <c r="H451" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I451" s="31" t="s">
-        <v>1045</v>
+        <v>1090</v>
       </c>
       <c r="J451" s="31" t="s">
-        <v>1046</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="452" spans="1:10" ht="15.75">
@@ -21035,7 +21410,7 @@
         <v>883</v>
       </c>
       <c r="B452" s="31" t="s">
-        <v>1029</v>
+        <v>1092</v>
       </c>
       <c r="C452" s="31" t="s">
         <v>604</v>
@@ -21044,22 +21419,22 @@
         <v>605</v>
       </c>
       <c r="E452" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F452" s="31" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="G452" s="31" t="s">
-        <v>1047</v>
+        <v>1093</v>
       </c>
       <c r="H452" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I452" s="31" t="s">
-        <v>1048</v>
+        <v>1094</v>
       </c>
       <c r="J452" s="31" t="s">
-        <v>1049</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="453" spans="1:10" ht="15.75">
@@ -21067,7 +21442,7 @@
         <v>883</v>
       </c>
       <c r="B453" s="31" t="s">
-        <v>1035</v>
+        <v>1096</v>
       </c>
       <c r="C453" s="31" t="s">
         <v>604</v>
@@ -21076,22 +21451,22 @@
         <v>605</v>
       </c>
       <c r="E453" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F453" s="31" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="G453" s="31" t="s">
-        <v>1047</v>
+        <v>1093</v>
       </c>
       <c r="H453" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I453" s="31" t="s">
-        <v>1050</v>
+        <v>1097</v>
       </c>
       <c r="J453" s="31" t="s">
-        <v>1051</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="454" spans="1:10" ht="15.75">
@@ -21099,7 +21474,7 @@
         <v>883</v>
       </c>
       <c r="B454" s="31" t="s">
-        <v>1038</v>
+        <v>1099</v>
       </c>
       <c r="C454" s="31" t="s">
         <v>604</v>
@@ -21108,22 +21483,22 @@
         <v>605</v>
       </c>
       <c r="E454" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F454" s="31" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="G454" s="31" t="s">
-        <v>1047</v>
+        <v>1093</v>
       </c>
       <c r="H454" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I454" s="31" t="s">
-        <v>1052</v>
+        <v>1100</v>
       </c>
       <c r="J454" s="31" t="s">
-        <v>1053</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="455" spans="1:10" ht="15.75">
@@ -21131,7 +21506,7 @@
         <v>883</v>
       </c>
       <c r="B455" s="31" t="s">
-        <v>1041</v>
+        <v>1102</v>
       </c>
       <c r="C455" s="31" t="s">
         <v>604</v>
@@ -21140,22 +21515,22 @@
         <v>605</v>
       </c>
       <c r="E455" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F455" s="31" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="G455" s="31" t="s">
-        <v>1047</v>
+        <v>1093</v>
       </c>
       <c r="H455" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I455" s="31" t="s">
-        <v>1054</v>
+        <v>1103</v>
       </c>
       <c r="J455" s="31" t="s">
-        <v>1055</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="456" spans="1:10" ht="15.75">
@@ -21163,7 +21538,7 @@
         <v>883</v>
       </c>
       <c r="B456" s="31" t="s">
-        <v>1044</v>
+        <v>1105</v>
       </c>
       <c r="C456" s="31" t="s">
         <v>604</v>
@@ -21172,22 +21547,22 @@
         <v>605</v>
       </c>
       <c r="E456" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F456" s="31" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="G456" s="31" t="s">
-        <v>1047</v>
+        <v>1093</v>
       </c>
       <c r="H456" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I456" s="31" t="s">
-        <v>1056</v>
+        <v>1106</v>
       </c>
       <c r="J456" s="31" t="s">
-        <v>1057</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="457" spans="1:10" ht="15.75">
@@ -21195,7 +21570,7 @@
         <v>883</v>
       </c>
       <c r="B457" s="31" t="s">
-        <v>1058</v>
+        <v>1108</v>
       </c>
       <c r="C457" s="31" t="s">
         <v>604</v>
@@ -21204,22 +21579,22 @@
         <v>605</v>
       </c>
       <c r="E457" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F457" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G457" s="31" t="s">
-        <v>1059</v>
+        <v>1109</v>
       </c>
       <c r="H457" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I457" s="31" t="s">
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="J457" s="31" t="s">
-        <v>1061</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="458" spans="1:10" ht="15.75">
@@ -21227,7 +21602,7 @@
         <v>883</v>
       </c>
       <c r="B458" s="31" t="s">
-        <v>1062</v>
+        <v>1112</v>
       </c>
       <c r="C458" s="31" t="s">
         <v>604</v>
@@ -21236,22 +21611,22 @@
         <v>605</v>
       </c>
       <c r="E458" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F458" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G458" s="31" t="s">
-        <v>1059</v>
+        <v>1109</v>
       </c>
       <c r="H458" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I458" s="31" t="s">
-        <v>1063</v>
+        <v>1113</v>
       </c>
       <c r="J458" s="31" t="s">
-        <v>1064</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="459" spans="1:10" ht="15.75">
@@ -21259,7 +21634,7 @@
         <v>883</v>
       </c>
       <c r="B459" s="31" t="s">
-        <v>1065</v>
+        <v>1115</v>
       </c>
       <c r="C459" s="31" t="s">
         <v>604</v>
@@ -21268,22 +21643,22 @@
         <v>605</v>
       </c>
       <c r="E459" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F459" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G459" s="31" t="s">
-        <v>1059</v>
+        <v>1109</v>
       </c>
       <c r="H459" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I459" s="31" t="s">
-        <v>1066</v>
+        <v>1116</v>
       </c>
       <c r="J459" s="31" t="s">
-        <v>1067</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="460" spans="1:10" ht="15.75">
@@ -21291,7 +21666,7 @@
         <v>883</v>
       </c>
       <c r="B460" s="31" t="s">
-        <v>1068</v>
+        <v>1118</v>
       </c>
       <c r="C460" s="31" t="s">
         <v>604</v>
@@ -21300,22 +21675,22 @@
         <v>605</v>
       </c>
       <c r="E460" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F460" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G460" s="31" t="s">
-        <v>1059</v>
+        <v>1109</v>
       </c>
       <c r="H460" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I460" s="31" t="s">
-        <v>1069</v>
+        <v>1119</v>
       </c>
       <c r="J460" s="31" t="s">
-        <v>1070</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="461" spans="1:10" ht="15.75">
@@ -21323,7 +21698,7 @@
         <v>883</v>
       </c>
       <c r="B461" s="31" t="s">
-        <v>1071</v>
+        <v>1121</v>
       </c>
       <c r="C461" s="31" t="s">
         <v>604</v>
@@ -21332,22 +21707,22 @@
         <v>605</v>
       </c>
       <c r="E461" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F461" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G461" s="31" t="s">
-        <v>1059</v>
+        <v>1109</v>
       </c>
       <c r="H461" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I461" s="31" t="s">
-        <v>1072</v>
+        <v>1122</v>
       </c>
       <c r="J461" s="31" t="s">
-        <v>1073</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="462" spans="1:10" ht="15.75">
@@ -21355,7 +21730,7 @@
         <v>883</v>
       </c>
       <c r="B462" s="31" t="s">
-        <v>1058</v>
+        <v>1124</v>
       </c>
       <c r="C462" s="31" t="s">
         <v>604</v>
@@ -21364,22 +21739,22 @@
         <v>605</v>
       </c>
       <c r="E462" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F462" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G462" s="31" t="s">
-        <v>1074</v>
+        <v>1125</v>
       </c>
       <c r="H462" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I462" s="31" t="s">
-        <v>1075</v>
+        <v>1126</v>
       </c>
       <c r="J462" s="31" t="s">
-        <v>1076</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="463" spans="1:10" ht="15.75">
@@ -21387,7 +21762,7 @@
         <v>883</v>
       </c>
       <c r="B463" s="31" t="s">
-        <v>1062</v>
+        <v>1128</v>
       </c>
       <c r="C463" s="31" t="s">
         <v>604</v>
@@ -21396,22 +21771,22 @@
         <v>605</v>
       </c>
       <c r="E463" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F463" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G463" s="31" t="s">
-        <v>1074</v>
+        <v>1125</v>
       </c>
       <c r="H463" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I463" s="31" t="s">
-        <v>1077</v>
+        <v>1129</v>
       </c>
       <c r="J463" s="31" t="s">
-        <v>1078</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="464" spans="1:10" ht="15.75">
@@ -21419,7 +21794,7 @@
         <v>883</v>
       </c>
       <c r="B464" s="31" t="s">
-        <v>1065</v>
+        <v>1131</v>
       </c>
       <c r="C464" s="31" t="s">
         <v>604</v>
@@ -21428,22 +21803,22 @@
         <v>605</v>
       </c>
       <c r="E464" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F464" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G464" s="31" t="s">
-        <v>1074</v>
+        <v>1125</v>
       </c>
       <c r="H464" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I464" s="31" t="s">
-        <v>1079</v>
+        <v>1132</v>
       </c>
       <c r="J464" s="31" t="s">
-        <v>1080</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="465" spans="1:10" ht="15.75">
@@ -21451,7 +21826,7 @@
         <v>883</v>
       </c>
       <c r="B465" s="31" t="s">
-        <v>1068</v>
+        <v>1134</v>
       </c>
       <c r="C465" s="31" t="s">
         <v>604</v>
@@ -21460,22 +21835,22 @@
         <v>605</v>
       </c>
       <c r="E465" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F465" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G465" s="31" t="s">
-        <v>1074</v>
+        <v>1125</v>
       </c>
       <c r="H465" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I465" s="31" t="s">
-        <v>1081</v>
+        <v>1135</v>
       </c>
       <c r="J465" s="31" t="s">
-        <v>1082</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="466" spans="1:10" ht="15.75">
@@ -21483,7 +21858,7 @@
         <v>883</v>
       </c>
       <c r="B466" s="31" t="s">
-        <v>1071</v>
+        <v>1137</v>
       </c>
       <c r="C466" s="31" t="s">
         <v>604</v>
@@ -21492,22 +21867,22 @@
         <v>605</v>
       </c>
       <c r="E466" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F466" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G466" s="31" t="s">
-        <v>1074</v>
+        <v>1125</v>
       </c>
       <c r="H466" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I466" s="31" t="s">
-        <v>1083</v>
+        <v>1138</v>
       </c>
       <c r="J466" s="31" t="s">
-        <v>1084</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="467" spans="1:10" ht="15.75">
@@ -21515,7 +21890,7 @@
         <v>883</v>
       </c>
       <c r="B467" s="31" t="s">
-        <v>1058</v>
+        <v>1140</v>
       </c>
       <c r="C467" s="31" t="s">
         <v>604</v>
@@ -21524,22 +21899,22 @@
         <v>605</v>
       </c>
       <c r="E467" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F467" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G467" s="31" t="s">
-        <v>1085</v>
+        <v>1141</v>
       </c>
       <c r="H467" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I467" s="31" t="s">
-        <v>1086</v>
+        <v>1142</v>
       </c>
       <c r="J467" s="31" t="s">
-        <v>1087</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="468" spans="1:10" ht="15.75">
@@ -21547,7 +21922,7 @@
         <v>883</v>
       </c>
       <c r="B468" s="31" t="s">
-        <v>1062</v>
+        <v>1144</v>
       </c>
       <c r="C468" s="31" t="s">
         <v>604</v>
@@ -21556,22 +21931,22 @@
         <v>605</v>
       </c>
       <c r="E468" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F468" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G468" s="31" t="s">
-        <v>1085</v>
+        <v>1141</v>
       </c>
       <c r="H468" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I468" s="31" t="s">
-        <v>1088</v>
+        <v>1145</v>
       </c>
       <c r="J468" s="31" t="s">
-        <v>1089</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="469" spans="1:10" ht="15.75">
@@ -21579,7 +21954,7 @@
         <v>883</v>
       </c>
       <c r="B469" s="31" t="s">
-        <v>1065</v>
+        <v>1147</v>
       </c>
       <c r="C469" s="31" t="s">
         <v>604</v>
@@ -21588,22 +21963,22 @@
         <v>605</v>
       </c>
       <c r="E469" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F469" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G469" s="31" t="s">
-        <v>1085</v>
+        <v>1141</v>
       </c>
       <c r="H469" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I469" s="31" t="s">
-        <v>1090</v>
+        <v>1148</v>
       </c>
       <c r="J469" s="31" t="s">
-        <v>1091</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="470" spans="1:10" ht="15.75">
@@ -21611,7 +21986,7 @@
         <v>883</v>
       </c>
       <c r="B470" s="31" t="s">
-        <v>1068</v>
+        <v>1150</v>
       </c>
       <c r="C470" s="31" t="s">
         <v>604</v>
@@ -21620,22 +21995,22 @@
         <v>605</v>
       </c>
       <c r="E470" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F470" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G470" s="31" t="s">
-        <v>1085</v>
+        <v>1141</v>
       </c>
       <c r="H470" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I470" s="31" t="s">
-        <v>1092</v>
+        <v>1151</v>
       </c>
       <c r="J470" s="31" t="s">
-        <v>1093</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="471" spans="1:10" ht="15.75">
@@ -21643,7 +22018,7 @@
         <v>883</v>
       </c>
       <c r="B471" s="31" t="s">
-        <v>1071</v>
+        <v>1153</v>
       </c>
       <c r="C471" s="31" t="s">
         <v>604</v>
@@ -21652,22 +22027,22 @@
         <v>605</v>
       </c>
       <c r="E471" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F471" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G471" s="31" t="s">
-        <v>1085</v>
+        <v>1141</v>
       </c>
       <c r="H471" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I471" s="31" t="s">
-        <v>1094</v>
+        <v>1154</v>
       </c>
       <c r="J471" s="31" t="s">
-        <v>1095</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="472" spans="1:10" ht="15.75">
@@ -21675,7 +22050,7 @@
         <v>883</v>
       </c>
       <c r="B472" s="31" t="s">
-        <v>1058</v>
+        <v>1156</v>
       </c>
       <c r="C472" s="31" t="s">
         <v>604</v>
@@ -21684,22 +22059,22 @@
         <v>605</v>
       </c>
       <c r="E472" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F472" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G472" s="31" t="s">
-        <v>1096</v>
+        <v>1157</v>
       </c>
       <c r="H472" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I472" s="31" t="s">
-        <v>1097</v>
+        <v>1158</v>
       </c>
       <c r="J472" s="31" t="s">
-        <v>1098</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="473" spans="1:10" ht="15.75">
@@ -21707,7 +22082,7 @@
         <v>883</v>
       </c>
       <c r="B473" s="31" t="s">
-        <v>1062</v>
+        <v>1160</v>
       </c>
       <c r="C473" s="31" t="s">
         <v>604</v>
@@ -21716,22 +22091,22 @@
         <v>605</v>
       </c>
       <c r="E473" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F473" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G473" s="31" t="s">
-        <v>1096</v>
+        <v>1157</v>
       </c>
       <c r="H473" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I473" s="31" t="s">
-        <v>1099</v>
+        <v>1161</v>
       </c>
       <c r="J473" s="31" t="s">
-        <v>1100</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="474" spans="1:10" ht="15.75">
@@ -21739,7 +22114,7 @@
         <v>883</v>
       </c>
       <c r="B474" s="31" t="s">
-        <v>1065</v>
+        <v>1163</v>
       </c>
       <c r="C474" s="31" t="s">
         <v>604</v>
@@ -21748,22 +22123,22 @@
         <v>605</v>
       </c>
       <c r="E474" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F474" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G474" s="31" t="s">
-        <v>1096</v>
+        <v>1157</v>
       </c>
       <c r="H474" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I474" s="31" t="s">
-        <v>1101</v>
+        <v>1164</v>
       </c>
       <c r="J474" s="31" t="s">
-        <v>1102</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="475" spans="1:10" ht="15.75">
@@ -21771,7 +22146,7 @@
         <v>883</v>
       </c>
       <c r="B475" s="31" t="s">
-        <v>1068</v>
+        <v>1166</v>
       </c>
       <c r="C475" s="31" t="s">
         <v>604</v>
@@ -21780,22 +22155,22 @@
         <v>605</v>
       </c>
       <c r="E475" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F475" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G475" s="31" t="s">
-        <v>1096</v>
+        <v>1157</v>
       </c>
       <c r="H475" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I475" s="31" t="s">
-        <v>1103</v>
+        <v>1167</v>
       </c>
       <c r="J475" s="31" t="s">
-        <v>1104</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="476" spans="1:10" ht="15.75">
@@ -21803,7 +22178,7 @@
         <v>883</v>
       </c>
       <c r="B476" s="31" t="s">
-        <v>1071</v>
+        <v>1169</v>
       </c>
       <c r="C476" s="31" t="s">
         <v>604</v>
@@ -21812,22 +22187,22 @@
         <v>605</v>
       </c>
       <c r="E476" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F476" s="31" t="s">
         <v>651</v>
       </c>
       <c r="G476" s="31" t="s">
-        <v>1096</v>
+        <v>1157</v>
       </c>
       <c r="H476" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I476" s="31" t="s">
-        <v>1105</v>
+        <v>1170</v>
       </c>
       <c r="J476" s="31" t="s">
-        <v>1106</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="477" spans="1:10" ht="15.75">
@@ -21835,7 +22210,7 @@
         <v>883</v>
       </c>
       <c r="B477" s="31" t="s">
-        <v>1107</v>
+        <v>1172</v>
       </c>
       <c r="C477" s="31" t="s">
         <v>604</v>
@@ -21844,22 +22219,22 @@
         <v>605</v>
       </c>
       <c r="E477" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F477" s="31" t="s">
-        <v>1108</v>
+        <v>1173</v>
       </c>
       <c r="G477" s="31" t="s">
-        <v>1109</v>
+        <v>1174</v>
       </c>
       <c r="H477" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I477" s="31" t="s">
-        <v>1110</v>
+        <v>1175</v>
       </c>
       <c r="J477" s="31" t="s">
-        <v>1111</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="478" spans="1:10" ht="15.75">
@@ -21867,7 +22242,7 @@
         <v>883</v>
       </c>
       <c r="B478" s="31" t="s">
-        <v>1112</v>
+        <v>1177</v>
       </c>
       <c r="C478" s="31" t="s">
         <v>604</v>
@@ -21876,22 +22251,22 @@
         <v>605</v>
       </c>
       <c r="E478" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F478" s="31" t="s">
-        <v>1108</v>
+        <v>1173</v>
       </c>
       <c r="G478" s="31" t="s">
-        <v>1109</v>
+        <v>1174</v>
       </c>
       <c r="H478" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I478" s="31" t="s">
-        <v>1113</v>
+        <v>1178</v>
       </c>
       <c r="J478" s="31" t="s">
-        <v>1114</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="479" spans="1:10" ht="15.75">
@@ -21899,7 +22274,7 @@
         <v>883</v>
       </c>
       <c r="B479" s="31" t="s">
-        <v>1115</v>
+        <v>1180</v>
       </c>
       <c r="C479" s="31" t="s">
         <v>604</v>
@@ -21908,22 +22283,22 @@
         <v>605</v>
       </c>
       <c r="E479" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F479" s="31" t="s">
-        <v>1108</v>
+        <v>1173</v>
       </c>
       <c r="G479" s="31" t="s">
-        <v>1109</v>
+        <v>1174</v>
       </c>
       <c r="H479" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I479" s="31" t="s">
-        <v>1116</v>
+        <v>1181</v>
       </c>
       <c r="J479" s="31" t="s">
-        <v>1117</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="480" spans="1:10" ht="15.75">
@@ -21931,7 +22306,7 @@
         <v>883</v>
       </c>
       <c r="B480" s="31" t="s">
-        <v>1118</v>
+        <v>1183</v>
       </c>
       <c r="C480" s="31" t="s">
         <v>604</v>
@@ -21940,22 +22315,22 @@
         <v>605</v>
       </c>
       <c r="E480" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F480" s="31" t="s">
-        <v>1108</v>
+        <v>1173</v>
       </c>
       <c r="G480" s="31" t="s">
-        <v>1109</v>
+        <v>1174</v>
       </c>
       <c r="H480" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I480" s="31" t="s">
-        <v>1119</v>
+        <v>1184</v>
       </c>
       <c r="J480" s="31" t="s">
-        <v>1120</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="481" spans="1:10" ht="15.75">
@@ -21963,7 +22338,7 @@
         <v>883</v>
       </c>
       <c r="B481" s="31" t="s">
-        <v>1121</v>
+        <v>1186</v>
       </c>
       <c r="C481" s="31" t="s">
         <v>604</v>
@@ -21972,22 +22347,22 @@
         <v>605</v>
       </c>
       <c r="E481" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F481" s="31" t="s">
-        <v>1108</v>
+        <v>1173</v>
       </c>
       <c r="G481" s="31" t="s">
-        <v>1109</v>
+        <v>1174</v>
       </c>
       <c r="H481" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I481" s="31" t="s">
-        <v>1122</v>
+        <v>1187</v>
       </c>
       <c r="J481" s="31" t="s">
-        <v>1123</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="482" spans="1:10" ht="15.75">
@@ -21995,7 +22370,7 @@
         <v>883</v>
       </c>
       <c r="B482" s="31" t="s">
-        <v>1107</v>
+        <v>1189</v>
       </c>
       <c r="C482" s="31" t="s">
         <v>604</v>
@@ -22004,22 +22379,22 @@
         <v>605</v>
       </c>
       <c r="E482" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F482" s="31" t="s">
-        <v>1108</v>
+        <v>1173</v>
       </c>
       <c r="G482" s="31" t="s">
-        <v>1124</v>
+        <v>1190</v>
       </c>
       <c r="H482" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I482" s="31" t="s">
-        <v>1125</v>
+        <v>1191</v>
       </c>
       <c r="J482" s="31" t="s">
-        <v>1126</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="483" spans="1:10" ht="15.75">
@@ -22027,7 +22402,7 @@
         <v>883</v>
       </c>
       <c r="B483" s="31" t="s">
-        <v>1112</v>
+        <v>1193</v>
       </c>
       <c r="C483" s="31" t="s">
         <v>604</v>
@@ -22036,22 +22411,22 @@
         <v>605</v>
       </c>
       <c r="E483" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F483" s="31" t="s">
-        <v>1108</v>
+        <v>1173</v>
       </c>
       <c r="G483" s="31" t="s">
-        <v>1124</v>
+        <v>1190</v>
       </c>
       <c r="H483" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I483" s="31" t="s">
-        <v>1127</v>
+        <v>1194</v>
       </c>
       <c r="J483" s="31" t="s">
-        <v>1128</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="484" spans="1:10" ht="15.75">
@@ -22059,7 +22434,7 @@
         <v>883</v>
       </c>
       <c r="B484" s="31" t="s">
-        <v>1115</v>
+        <v>1196</v>
       </c>
       <c r="C484" s="31" t="s">
         <v>604</v>
@@ -22068,22 +22443,22 @@
         <v>605</v>
       </c>
       <c r="E484" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F484" s="31" t="s">
-        <v>1108</v>
+        <v>1173</v>
       </c>
       <c r="G484" s="31" t="s">
-        <v>1124</v>
+        <v>1190</v>
       </c>
       <c r="H484" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I484" s="31" t="s">
-        <v>1129</v>
+        <v>1197</v>
       </c>
       <c r="J484" s="31" t="s">
-        <v>1130</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="485" spans="1:10" ht="15.75">
@@ -22091,7 +22466,7 @@
         <v>883</v>
       </c>
       <c r="B485" s="31" t="s">
-        <v>1118</v>
+        <v>1199</v>
       </c>
       <c r="C485" s="31" t="s">
         <v>604</v>
@@ -22100,22 +22475,22 @@
         <v>605</v>
       </c>
       <c r="E485" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F485" s="31" t="s">
-        <v>1108</v>
+        <v>1173</v>
       </c>
       <c r="G485" s="31" t="s">
-        <v>1124</v>
+        <v>1190</v>
       </c>
       <c r="H485" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I485" s="31" t="s">
-        <v>1131</v>
+        <v>1200</v>
       </c>
       <c r="J485" s="31" t="s">
-        <v>1132</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="486" spans="1:10" ht="15.75">
@@ -22123,7 +22498,7 @@
         <v>883</v>
       </c>
       <c r="B486" s="31" t="s">
-        <v>1121</v>
+        <v>1202</v>
       </c>
       <c r="C486" s="31" t="s">
         <v>604</v>
@@ -22132,22 +22507,22 @@
         <v>605</v>
       </c>
       <c r="E486" s="31" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="F486" s="31" t="s">
-        <v>1108</v>
+        <v>1173</v>
       </c>
       <c r="G486" s="31" t="s">
-        <v>1124</v>
+        <v>1190</v>
       </c>
       <c r="H486" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I486" s="31" t="s">
-        <v>1133</v>
+        <v>1203</v>
       </c>
       <c r="J486" s="31" t="s">
-        <v>1134</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="487" spans="1:10" ht="15.75">
@@ -22155,7 +22530,7 @@
         <v>883</v>
       </c>
       <c r="B487" s="31" t="s">
-        <v>1135</v>
+        <v>1205</v>
       </c>
       <c r="C487" s="31" t="s">
         <v>294</v>
@@ -22167,19 +22542,19 @@
         <v>296</v>
       </c>
       <c r="F487" s="31" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="G487" s="31" t="s">
-        <v>1137</v>
+        <v>1207</v>
       </c>
       <c r="H487" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I487" s="31" t="s">
-        <v>1138</v>
+        <v>1208</v>
       </c>
       <c r="J487" s="31" t="s">
-        <v>1139</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="488" spans="1:10" ht="15.75">
@@ -22187,7 +22562,7 @@
         <v>883</v>
       </c>
       <c r="B488" s="31" t="s">
-        <v>1140</v>
+        <v>1210</v>
       </c>
       <c r="C488" s="31" t="s">
         <v>294</v>
@@ -22199,19 +22574,19 @@
         <v>296</v>
       </c>
       <c r="F488" s="31" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="G488" s="31" t="s">
-        <v>1137</v>
+        <v>1207</v>
       </c>
       <c r="H488" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I488" s="31" t="s">
-        <v>1141</v>
+        <v>1211</v>
       </c>
       <c r="J488" s="31" t="s">
-        <v>1142</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="489" spans="1:10" ht="15.75">
@@ -22219,7 +22594,7 @@
         <v>883</v>
       </c>
       <c r="B489" s="31" t="s">
-        <v>1143</v>
+        <v>1213</v>
       </c>
       <c r="C489" s="31" t="s">
         <v>294</v>
@@ -22231,19 +22606,19 @@
         <v>296</v>
       </c>
       <c r="F489" s="31" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="G489" s="31" t="s">
-        <v>1137</v>
+        <v>1207</v>
       </c>
       <c r="H489" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I489" s="31" t="s">
-        <v>1144</v>
+        <v>1214</v>
       </c>
       <c r="J489" s="31" t="s">
-        <v>1145</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="490" spans="1:10" ht="15.75">
@@ -22251,7 +22626,7 @@
         <v>883</v>
       </c>
       <c r="B490" s="31" t="s">
-        <v>1146</v>
+        <v>1216</v>
       </c>
       <c r="C490" s="31" t="s">
         <v>294</v>
@@ -22263,19 +22638,19 @@
         <v>296</v>
       </c>
       <c r="F490" s="31" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="G490" s="31" t="s">
-        <v>1137</v>
+        <v>1207</v>
       </c>
       <c r="H490" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I490" s="31" t="s">
-        <v>1147</v>
+        <v>1217</v>
       </c>
       <c r="J490" s="31" t="s">
-        <v>1148</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="491" spans="1:10" ht="15.75">
@@ -22283,7 +22658,7 @@
         <v>883</v>
       </c>
       <c r="B491" s="31" t="s">
-        <v>1149</v>
+        <v>1219</v>
       </c>
       <c r="C491" s="31" t="s">
         <v>294</v>
@@ -22295,19 +22670,19 @@
         <v>296</v>
       </c>
       <c r="F491" s="31" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="G491" s="31" t="s">
-        <v>1137</v>
+        <v>1207</v>
       </c>
       <c r="H491" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I491" s="31" t="s">
-        <v>1150</v>
+        <v>1220</v>
       </c>
       <c r="J491" s="31" t="s">
-        <v>1151</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="492" spans="1:10" ht="15.75">
@@ -22315,7 +22690,7 @@
         <v>883</v>
       </c>
       <c r="B492" s="31" t="s">
-        <v>1135</v>
+        <v>1222</v>
       </c>
       <c r="C492" s="31" t="s">
         <v>294</v>
@@ -22327,19 +22702,19 @@
         <v>296</v>
       </c>
       <c r="F492" s="31" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="G492" s="31" t="s">
-        <v>1152</v>
+        <v>1223</v>
       </c>
       <c r="H492" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I492" s="31" t="s">
-        <v>1153</v>
+        <v>1224</v>
       </c>
       <c r="J492" s="31" t="s">
-        <v>1154</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="493" spans="1:10" ht="15.75">
@@ -22347,7 +22722,7 @@
         <v>883</v>
       </c>
       <c r="B493" s="31" t="s">
-        <v>1140</v>
+        <v>1226</v>
       </c>
       <c r="C493" s="31" t="s">
         <v>294</v>
@@ -22359,19 +22734,19 @@
         <v>296</v>
       </c>
       <c r="F493" s="31" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="G493" s="31" t="s">
-        <v>1152</v>
+        <v>1223</v>
       </c>
       <c r="H493" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I493" s="31" t="s">
-        <v>1155</v>
+        <v>1227</v>
       </c>
       <c r="J493" s="31" t="s">
-        <v>1156</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="494" spans="1:10" ht="15.75">
@@ -22379,7 +22754,7 @@
         <v>883</v>
       </c>
       <c r="B494" s="31" t="s">
-        <v>1143</v>
+        <v>1229</v>
       </c>
       <c r="C494" s="31" t="s">
         <v>294</v>
@@ -22391,19 +22766,19 @@
         <v>296</v>
       </c>
       <c r="F494" s="31" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="G494" s="31" t="s">
-        <v>1152</v>
+        <v>1223</v>
       </c>
       <c r="H494" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I494" s="31" t="s">
-        <v>1157</v>
+        <v>1230</v>
       </c>
       <c r="J494" s="31" t="s">
-        <v>1158</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="495" spans="1:10" ht="15.75">
@@ -22411,7 +22786,7 @@
         <v>883</v>
       </c>
       <c r="B495" s="31" t="s">
-        <v>1146</v>
+        <v>1232</v>
       </c>
       <c r="C495" s="31" t="s">
         <v>294</v>
@@ -22423,19 +22798,19 @@
         <v>296</v>
       </c>
       <c r="F495" s="31" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="G495" s="31" t="s">
-        <v>1152</v>
+        <v>1223</v>
       </c>
       <c r="H495" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I495" s="31" t="s">
-        <v>1159</v>
+        <v>1233</v>
       </c>
       <c r="J495" s="31" t="s">
-        <v>1160</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="496" spans="1:10" ht="15.75">
@@ -22443,7 +22818,7 @@
         <v>883</v>
       </c>
       <c r="B496" s="31" t="s">
-        <v>1149</v>
+        <v>1235</v>
       </c>
       <c r="C496" s="31" t="s">
         <v>294</v>
@@ -22455,19 +22830,19 @@
         <v>296</v>
       </c>
       <c r="F496" s="31" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="G496" s="31" t="s">
-        <v>1152</v>
+        <v>1223</v>
       </c>
       <c r="H496" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I496" s="31" t="s">
-        <v>1161</v>
+        <v>1236</v>
       </c>
       <c r="J496" s="31" t="s">
-        <v>1162</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="497" spans="1:10" ht="15.75">
@@ -22475,7 +22850,7 @@
         <v>883</v>
       </c>
       <c r="B497" s="31" t="s">
-        <v>1163</v>
+        <v>1238</v>
       </c>
       <c r="C497" s="31" t="s">
         <v>294</v>
@@ -22487,19 +22862,19 @@
         <v>296</v>
       </c>
       <c r="F497" s="31" t="s">
-        <v>1164</v>
+        <v>1239</v>
       </c>
       <c r="G497" s="31" t="s">
-        <v>1165</v>
+        <v>1240</v>
       </c>
       <c r="H497" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I497" s="31" t="s">
-        <v>1166</v>
+        <v>1241</v>
       </c>
       <c r="J497" s="31" t="s">
-        <v>1167</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="498" spans="1:10" ht="15.75">
@@ -22507,7 +22882,7 @@
         <v>883</v>
       </c>
       <c r="B498" s="31" t="s">
-        <v>1168</v>
+        <v>1243</v>
       </c>
       <c r="C498" s="31" t="s">
         <v>294</v>
@@ -22519,19 +22894,19 @@
         <v>296</v>
       </c>
       <c r="F498" s="31" t="s">
-        <v>1164</v>
+        <v>1239</v>
       </c>
       <c r="G498" s="31" t="s">
-        <v>1165</v>
+        <v>1240</v>
       </c>
       <c r="H498" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I498" s="31" t="s">
-        <v>1169</v>
+        <v>1244</v>
       </c>
       <c r="J498" s="31" t="s">
-        <v>1170</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="499" spans="1:10" ht="15.75">
@@ -22539,7 +22914,7 @@
         <v>883</v>
       </c>
       <c r="B499" s="31" t="s">
-        <v>1171</v>
+        <v>1246</v>
       </c>
       <c r="C499" s="31" t="s">
         <v>294</v>
@@ -22551,19 +22926,19 @@
         <v>296</v>
       </c>
       <c r="F499" s="31" t="s">
-        <v>1164</v>
+        <v>1239</v>
       </c>
       <c r="G499" s="31" t="s">
-        <v>1165</v>
+        <v>1240</v>
       </c>
       <c r="H499" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I499" s="31" t="s">
-        <v>1172</v>
+        <v>1247</v>
       </c>
       <c r="J499" s="31" t="s">
-        <v>1173</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="500" spans="1:10" ht="15.75">
@@ -22571,7 +22946,7 @@
         <v>883</v>
       </c>
       <c r="B500" s="31" t="s">
-        <v>1174</v>
+        <v>1249</v>
       </c>
       <c r="C500" s="31" t="s">
         <v>294</v>
@@ -22583,19 +22958,19 @@
         <v>296</v>
       </c>
       <c r="F500" s="31" t="s">
-        <v>1164</v>
+        <v>1239</v>
       </c>
       <c r="G500" s="31" t="s">
-        <v>1165</v>
+        <v>1240</v>
       </c>
       <c r="H500" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I500" s="31" t="s">
-        <v>1175</v>
+        <v>1250</v>
       </c>
       <c r="J500" s="31" t="s">
-        <v>1176</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="501" spans="1:10" ht="15.75">
@@ -22603,7 +22978,7 @@
         <v>883</v>
       </c>
       <c r="B501" s="31" t="s">
-        <v>1177</v>
+        <v>1252</v>
       </c>
       <c r="C501" s="31" t="s">
         <v>294</v>
@@ -22615,19 +22990,19 @@
         <v>296</v>
       </c>
       <c r="F501" s="31" t="s">
-        <v>1164</v>
+        <v>1239</v>
       </c>
       <c r="G501" s="31" t="s">
-        <v>1165</v>
+        <v>1240</v>
       </c>
       <c r="H501" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I501" s="31" t="s">
-        <v>1178</v>
+        <v>1253</v>
       </c>
       <c r="J501" s="31" t="s">
-        <v>1179</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="502" spans="1:10" ht="15.75">
@@ -22635,7 +23010,7 @@
         <v>883</v>
       </c>
       <c r="B502" s="31" t="s">
-        <v>1163</v>
+        <v>1255</v>
       </c>
       <c r="C502" s="31" t="s">
         <v>294</v>
@@ -22647,19 +23022,19 @@
         <v>296</v>
       </c>
       <c r="F502" s="31" t="s">
-        <v>1164</v>
+        <v>1239</v>
       </c>
       <c r="G502" s="31" t="s">
-        <v>1180</v>
+        <v>1256</v>
       </c>
       <c r="H502" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I502" s="31" t="s">
-        <v>1181</v>
+        <v>1257</v>
       </c>
       <c r="J502" s="31" t="s">
-        <v>1182</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="503" spans="1:10" ht="15.75">
@@ -22667,7 +23042,7 @@
         <v>883</v>
       </c>
       <c r="B503" s="31" t="s">
-        <v>1168</v>
+        <v>1259</v>
       </c>
       <c r="C503" s="31" t="s">
         <v>294</v>
@@ -22679,19 +23054,19 @@
         <v>296</v>
       </c>
       <c r="F503" s="31" t="s">
-        <v>1164</v>
+        <v>1239</v>
       </c>
       <c r="G503" s="31" t="s">
-        <v>1180</v>
+        <v>1256</v>
       </c>
       <c r="H503" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I503" s="31" t="s">
-        <v>1183</v>
+        <v>1260</v>
       </c>
       <c r="J503" s="31" t="s">
-        <v>1184</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="504" spans="1:10" ht="15.75">
@@ -22699,7 +23074,7 @@
         <v>883</v>
       </c>
       <c r="B504" s="31" t="s">
-        <v>1171</v>
+        <v>1262</v>
       </c>
       <c r="C504" s="31" t="s">
         <v>294</v>
@@ -22711,19 +23086,19 @@
         <v>296</v>
       </c>
       <c r="F504" s="31" t="s">
-        <v>1164</v>
+        <v>1239</v>
       </c>
       <c r="G504" s="31" t="s">
-        <v>1180</v>
+        <v>1256</v>
       </c>
       <c r="H504" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I504" s="31" t="s">
-        <v>1185</v>
+        <v>1263</v>
       </c>
       <c r="J504" s="31" t="s">
-        <v>1186</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="505" spans="1:10" ht="15.75">
@@ -22731,7 +23106,7 @@
         <v>883</v>
       </c>
       <c r="B505" s="31" t="s">
-        <v>1174</v>
+        <v>1265</v>
       </c>
       <c r="C505" s="31" t="s">
         <v>294</v>
@@ -22743,19 +23118,19 @@
         <v>296</v>
       </c>
       <c r="F505" s="31" t="s">
-        <v>1164</v>
+        <v>1239</v>
       </c>
       <c r="G505" s="31" t="s">
-        <v>1180</v>
+        <v>1256</v>
       </c>
       <c r="H505" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I505" s="31" t="s">
-        <v>1187</v>
+        <v>1266</v>
       </c>
       <c r="J505" s="31" t="s">
-        <v>1188</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="506" spans="1:10" ht="15.75">
@@ -22763,7 +23138,7 @@
         <v>883</v>
       </c>
       <c r="B506" s="31" t="s">
-        <v>1177</v>
+        <v>1268</v>
       </c>
       <c r="C506" s="31" t="s">
         <v>294</v>
@@ -22775,19 +23150,19 @@
         <v>296</v>
       </c>
       <c r="F506" s="31" t="s">
-        <v>1164</v>
+        <v>1239</v>
       </c>
       <c r="G506" s="31" t="s">
-        <v>1180</v>
+        <v>1256</v>
       </c>
       <c r="H506" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I506" s="31" t="s">
-        <v>1189</v>
+        <v>1269</v>
       </c>
       <c r="J506" s="31" t="s">
-        <v>1190</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="507" spans="1:10" ht="15.75">
@@ -22795,7 +23170,7 @@
         <v>883</v>
       </c>
       <c r="B507" s="31" t="s">
-        <v>1191</v>
+        <v>1271</v>
       </c>
       <c r="C507" s="31" t="s">
         <v>294</v>
@@ -22807,19 +23182,19 @@
         <v>296</v>
       </c>
       <c r="F507" s="31" t="s">
-        <v>1192</v>
+        <v>1272</v>
       </c>
       <c r="G507" s="31" t="s">
-        <v>1193</v>
+        <v>1273</v>
       </c>
       <c r="H507" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I507" s="31" t="s">
-        <v>1194</v>
+        <v>1274</v>
       </c>
       <c r="J507" s="31" t="s">
-        <v>1195</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="508" spans="1:10" ht="15.75">
@@ -22827,7 +23202,7 @@
         <v>883</v>
       </c>
       <c r="B508" s="31" t="s">
-        <v>1196</v>
+        <v>1276</v>
       </c>
       <c r="C508" s="31" t="s">
         <v>294</v>
@@ -22839,19 +23214,19 @@
         <v>296</v>
       </c>
       <c r="F508" s="31" t="s">
-        <v>1192</v>
+        <v>1272</v>
       </c>
       <c r="G508" s="31" t="s">
-        <v>1193</v>
+        <v>1273</v>
       </c>
       <c r="H508" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I508" s="31" t="s">
-        <v>1197</v>
+        <v>1277</v>
       </c>
       <c r="J508" s="31" t="s">
-        <v>1198</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="509" spans="1:10" ht="15.75">
@@ -22859,7 +23234,7 @@
         <v>883</v>
       </c>
       <c r="B509" s="31" t="s">
-        <v>1199</v>
+        <v>1279</v>
       </c>
       <c r="C509" s="31" t="s">
         <v>294</v>
@@ -22871,19 +23246,19 @@
         <v>296</v>
       </c>
       <c r="F509" s="31" t="s">
-        <v>1192</v>
+        <v>1272</v>
       </c>
       <c r="G509" s="31" t="s">
-        <v>1193</v>
+        <v>1273</v>
       </c>
       <c r="H509" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I509" s="31" t="s">
-        <v>1200</v>
+        <v>1280</v>
       </c>
       <c r="J509" s="31" t="s">
-        <v>1201</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="510" spans="1:10" ht="15.75">
@@ -22891,7 +23266,7 @@
         <v>883</v>
       </c>
       <c r="B510" s="31" t="s">
-        <v>1202</v>
+        <v>1282</v>
       </c>
       <c r="C510" s="31" t="s">
         <v>294</v>
@@ -22903,19 +23278,19 @@
         <v>296</v>
       </c>
       <c r="F510" s="31" t="s">
-        <v>1192</v>
+        <v>1272</v>
       </c>
       <c r="G510" s="31" t="s">
-        <v>1193</v>
+        <v>1273</v>
       </c>
       <c r="H510" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I510" s="31" t="s">
-        <v>1203</v>
+        <v>1283</v>
       </c>
       <c r="J510" s="31" t="s">
-        <v>1204</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="511" spans="1:10" ht="15.75">
@@ -22923,7 +23298,7 @@
         <v>883</v>
       </c>
       <c r="B511" s="31" t="s">
-        <v>1205</v>
+        <v>1285</v>
       </c>
       <c r="C511" s="31" t="s">
         <v>294</v>
@@ -22935,19 +23310,19 @@
         <v>296</v>
       </c>
       <c r="F511" s="31" t="s">
-        <v>1192</v>
+        <v>1272</v>
       </c>
       <c r="G511" s="31" t="s">
-        <v>1193</v>
+        <v>1273</v>
       </c>
       <c r="H511" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I511" s="31" t="s">
-        <v>1206</v>
+        <v>1286</v>
       </c>
       <c r="J511" s="31" t="s">
-        <v>1207</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="512" spans="1:10" ht="15.75">
@@ -22955,7 +23330,7 @@
         <v>883</v>
       </c>
       <c r="B512" s="31" t="s">
-        <v>1191</v>
+        <v>1288</v>
       </c>
       <c r="C512" s="31" t="s">
         <v>294</v>
@@ -22967,19 +23342,19 @@
         <v>296</v>
       </c>
       <c r="F512" s="31" t="s">
-        <v>1192</v>
+        <v>1272</v>
       </c>
       <c r="G512" s="31" t="s">
-        <v>1208</v>
+        <v>1289</v>
       </c>
       <c r="H512" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I512" s="31" t="s">
-        <v>1209</v>
+        <v>1290</v>
       </c>
       <c r="J512" s="31" t="s">
-        <v>1210</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="513" spans="1:10" ht="15.75">
@@ -22987,7 +23362,7 @@
         <v>883</v>
       </c>
       <c r="B513" s="31" t="s">
-        <v>1196</v>
+        <v>1292</v>
       </c>
       <c r="C513" s="31" t="s">
         <v>294</v>
@@ -22999,19 +23374,19 @@
         <v>296</v>
       </c>
       <c r="F513" s="31" t="s">
-        <v>1192</v>
+        <v>1272</v>
       </c>
       <c r="G513" s="31" t="s">
-        <v>1208</v>
+        <v>1289</v>
       </c>
       <c r="H513" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I513" s="31" t="s">
-        <v>1211</v>
+        <v>1293</v>
       </c>
       <c r="J513" s="31" t="s">
-        <v>1212</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="514" spans="1:10" ht="15.75">
@@ -23019,7 +23394,7 @@
         <v>883</v>
       </c>
       <c r="B514" s="31" t="s">
-        <v>1199</v>
+        <v>1295</v>
       </c>
       <c r="C514" s="31" t="s">
         <v>294</v>
@@ -23031,19 +23406,19 @@
         <v>296</v>
       </c>
       <c r="F514" s="31" t="s">
-        <v>1192</v>
+        <v>1272</v>
       </c>
       <c r="G514" s="31" t="s">
-        <v>1208</v>
+        <v>1289</v>
       </c>
       <c r="H514" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I514" s="31" t="s">
-        <v>1213</v>
+        <v>1296</v>
       </c>
       <c r="J514" s="31" t="s">
-        <v>1214</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="515" spans="1:10" ht="15.75">
@@ -23051,7 +23426,7 @@
         <v>883</v>
       </c>
       <c r="B515" s="31" t="s">
-        <v>1202</v>
+        <v>1298</v>
       </c>
       <c r="C515" s="31" t="s">
         <v>294</v>
@@ -23063,19 +23438,19 @@
         <v>296</v>
       </c>
       <c r="F515" s="31" t="s">
-        <v>1192</v>
+        <v>1272</v>
       </c>
       <c r="G515" s="31" t="s">
-        <v>1208</v>
+        <v>1289</v>
       </c>
       <c r="H515" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I515" s="31" t="s">
-        <v>1215</v>
+        <v>1299</v>
       </c>
       <c r="J515" s="31" t="s">
-        <v>1216</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="516" spans="1:10" ht="15.75">
@@ -23083,7 +23458,7 @@
         <v>883</v>
       </c>
       <c r="B516" s="31" t="s">
-        <v>1205</v>
+        <v>1301</v>
       </c>
       <c r="C516" s="31" t="s">
         <v>294</v>
@@ -23095,19 +23470,19 @@
         <v>296</v>
       </c>
       <c r="F516" s="31" t="s">
-        <v>1192</v>
+        <v>1272</v>
       </c>
       <c r="G516" s="31" t="s">
-        <v>1208</v>
+        <v>1289</v>
       </c>
       <c r="H516" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I516" s="31" t="s">
-        <v>1217</v>
+        <v>1302</v>
       </c>
       <c r="J516" s="31" t="s">
-        <v>1218</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="517" spans="1:10" ht="15.75">
@@ -23115,7 +23490,7 @@
         <v>883</v>
       </c>
       <c r="B517" s="31" t="s">
-        <v>1219</v>
+        <v>1304</v>
       </c>
       <c r="C517" s="31" t="s">
         <v>722</v>
@@ -23127,19 +23502,19 @@
         <v>724</v>
       </c>
       <c r="F517" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G517" s="31" t="s">
-        <v>1221</v>
+        <v>1306</v>
       </c>
       <c r="H517" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I517" s="31" t="s">
-        <v>1222</v>
+        <v>1307</v>
       </c>
       <c r="J517" s="31" t="s">
-        <v>1223</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="518" spans="1:10" ht="15.75">
@@ -23147,7 +23522,7 @@
         <v>883</v>
       </c>
       <c r="B518" s="31" t="s">
-        <v>1224</v>
+        <v>1309</v>
       </c>
       <c r="C518" s="31" t="s">
         <v>722</v>
@@ -23159,19 +23534,19 @@
         <v>724</v>
       </c>
       <c r="F518" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G518" s="31" t="s">
-        <v>1221</v>
+        <v>1306</v>
       </c>
       <c r="H518" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I518" s="31" t="s">
-        <v>1225</v>
+        <v>1310</v>
       </c>
       <c r="J518" s="31" t="s">
-        <v>1226</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="519" spans="1:10" ht="15.75">
@@ -23179,7 +23554,7 @@
         <v>883</v>
       </c>
       <c r="B519" s="31" t="s">
-        <v>1227</v>
+        <v>1312</v>
       </c>
       <c r="C519" s="31" t="s">
         <v>722</v>
@@ -23191,19 +23566,19 @@
         <v>724</v>
       </c>
       <c r="F519" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G519" s="31" t="s">
-        <v>1221</v>
+        <v>1306</v>
       </c>
       <c r="H519" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I519" s="31" t="s">
-        <v>1228</v>
+        <v>1313</v>
       </c>
       <c r="J519" s="31" t="s">
-        <v>1229</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="520" spans="1:10" ht="15.75">
@@ -23211,7 +23586,7 @@
         <v>883</v>
       </c>
       <c r="B520" s="31" t="s">
-        <v>1230</v>
+        <v>1315</v>
       </c>
       <c r="C520" s="31" t="s">
         <v>722</v>
@@ -23223,19 +23598,19 @@
         <v>724</v>
       </c>
       <c r="F520" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G520" s="31" t="s">
-        <v>1221</v>
+        <v>1306</v>
       </c>
       <c r="H520" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I520" s="31" t="s">
-        <v>1231</v>
+        <v>1316</v>
       </c>
       <c r="J520" s="31" t="s">
-        <v>1232</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="521" spans="1:10" ht="15.75">
@@ -23243,7 +23618,7 @@
         <v>883</v>
       </c>
       <c r="B521" s="31" t="s">
-        <v>1233</v>
+        <v>1318</v>
       </c>
       <c r="C521" s="31" t="s">
         <v>722</v>
@@ -23255,19 +23630,19 @@
         <v>724</v>
       </c>
       <c r="F521" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G521" s="31" t="s">
-        <v>1221</v>
+        <v>1306</v>
       </c>
       <c r="H521" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I521" s="31" t="s">
-        <v>1234</v>
+        <v>1319</v>
       </c>
       <c r="J521" s="31" t="s">
-        <v>1235</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="522" spans="1:10" ht="15.75">
@@ -23275,7 +23650,7 @@
         <v>883</v>
       </c>
       <c r="B522" s="31" t="s">
-        <v>1219</v>
+        <v>1321</v>
       </c>
       <c r="C522" s="31" t="s">
         <v>722</v>
@@ -23287,19 +23662,19 @@
         <v>724</v>
       </c>
       <c r="F522" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G522" s="31" t="s">
-        <v>1236</v>
+        <v>1322</v>
       </c>
       <c r="H522" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I522" s="31" t="s">
-        <v>1237</v>
+        <v>1323</v>
       </c>
       <c r="J522" s="31" t="s">
-        <v>1238</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="523" spans="1:10" ht="15.75">
@@ -23307,7 +23682,7 @@
         <v>883</v>
       </c>
       <c r="B523" s="31" t="s">
-        <v>1224</v>
+        <v>1325</v>
       </c>
       <c r="C523" s="31" t="s">
         <v>722</v>
@@ -23319,19 +23694,19 @@
         <v>724</v>
       </c>
       <c r="F523" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G523" s="31" t="s">
-        <v>1236</v>
+        <v>1322</v>
       </c>
       <c r="H523" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I523" s="31" t="s">
-        <v>1239</v>
+        <v>1326</v>
       </c>
       <c r="J523" s="31" t="s">
-        <v>1240</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="524" spans="1:10" ht="15.75">
@@ -23339,7 +23714,7 @@
         <v>883</v>
       </c>
       <c r="B524" s="31" t="s">
-        <v>1227</v>
+        <v>1328</v>
       </c>
       <c r="C524" s="31" t="s">
         <v>722</v>
@@ -23351,19 +23726,19 @@
         <v>724</v>
       </c>
       <c r="F524" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G524" s="31" t="s">
-        <v>1236</v>
+        <v>1322</v>
       </c>
       <c r="H524" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I524" s="31" t="s">
-        <v>1241</v>
+        <v>1329</v>
       </c>
       <c r="J524" s="31" t="s">
-        <v>1242</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="525" spans="1:10" ht="15.75">
@@ -23371,7 +23746,7 @@
         <v>883</v>
       </c>
       <c r="B525" s="31" t="s">
-        <v>1230</v>
+        <v>1331</v>
       </c>
       <c r="C525" s="31" t="s">
         <v>722</v>
@@ -23383,19 +23758,19 @@
         <v>724</v>
       </c>
       <c r="F525" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G525" s="31" t="s">
-        <v>1236</v>
+        <v>1322</v>
       </c>
       <c r="H525" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I525" s="31" t="s">
-        <v>1243</v>
+        <v>1332</v>
       </c>
       <c r="J525" s="31" t="s">
-        <v>1244</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="526" spans="1:10" ht="15.75">
@@ -23403,7 +23778,7 @@
         <v>883</v>
       </c>
       <c r="B526" s="31" t="s">
-        <v>1233</v>
+        <v>1334</v>
       </c>
       <c r="C526" s="31" t="s">
         <v>722</v>
@@ -23415,19 +23790,19 @@
         <v>724</v>
       </c>
       <c r="F526" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G526" s="31" t="s">
-        <v>1236</v>
+        <v>1322</v>
       </c>
       <c r="H526" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I526" s="31" t="s">
-        <v>1245</v>
+        <v>1335</v>
       </c>
       <c r="J526" s="31" t="s">
-        <v>1246</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="527" spans="1:10" ht="15.75">
@@ -23435,7 +23810,7 @@
         <v>883</v>
       </c>
       <c r="B527" s="31" t="s">
-        <v>1219</v>
+        <v>1337</v>
       </c>
       <c r="C527" s="31" t="s">
         <v>722</v>
@@ -23447,19 +23822,19 @@
         <v>724</v>
       </c>
       <c r="F527" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G527" s="31" t="s">
-        <v>1247</v>
+        <v>1338</v>
       </c>
       <c r="H527" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I527" s="31" t="s">
-        <v>1248</v>
+        <v>1339</v>
       </c>
       <c r="J527" s="31" t="s">
-        <v>1249</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="528" spans="1:10" ht="15.75">
@@ -23467,7 +23842,7 @@
         <v>883</v>
       </c>
       <c r="B528" s="31" t="s">
-        <v>1224</v>
+        <v>1341</v>
       </c>
       <c r="C528" s="31" t="s">
         <v>722</v>
@@ -23479,19 +23854,19 @@
         <v>724</v>
       </c>
       <c r="F528" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G528" s="31" t="s">
-        <v>1247</v>
+        <v>1338</v>
       </c>
       <c r="H528" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I528" s="31" t="s">
-        <v>1250</v>
+        <v>1342</v>
       </c>
       <c r="J528" s="31" t="s">
-        <v>1251</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="529" spans="1:10" ht="15.75">
@@ -23499,7 +23874,7 @@
         <v>883</v>
       </c>
       <c r="B529" s="31" t="s">
-        <v>1227</v>
+        <v>1344</v>
       </c>
       <c r="C529" s="31" t="s">
         <v>722</v>
@@ -23511,19 +23886,19 @@
         <v>724</v>
       </c>
       <c r="F529" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G529" s="31" t="s">
-        <v>1247</v>
+        <v>1338</v>
       </c>
       <c r="H529" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I529" s="31" t="s">
-        <v>1252</v>
+        <v>1345</v>
       </c>
       <c r="J529" s="31" t="s">
-        <v>1253</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="530" spans="1:10" ht="15.75">
@@ -23531,7 +23906,7 @@
         <v>883</v>
       </c>
       <c r="B530" s="31" t="s">
-        <v>1230</v>
+        <v>1347</v>
       </c>
       <c r="C530" s="31" t="s">
         <v>722</v>
@@ -23543,19 +23918,19 @@
         <v>724</v>
       </c>
       <c r="F530" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G530" s="31" t="s">
-        <v>1247</v>
+        <v>1338</v>
       </c>
       <c r="H530" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I530" s="31" t="s">
-        <v>1254</v>
+        <v>1348</v>
       </c>
       <c r="J530" s="31" t="s">
-        <v>1255</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="531" spans="1:10" ht="15.75">
@@ -23563,7 +23938,7 @@
         <v>883</v>
       </c>
       <c r="B531" s="31" t="s">
-        <v>1233</v>
+        <v>1350</v>
       </c>
       <c r="C531" s="31" t="s">
         <v>722</v>
@@ -23575,19 +23950,19 @@
         <v>724</v>
       </c>
       <c r="F531" s="31" t="s">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="G531" s="31" t="s">
-        <v>1247</v>
+        <v>1338</v>
       </c>
       <c r="H531" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I531" s="31" t="s">
-        <v>1256</v>
+        <v>1351</v>
       </c>
       <c r="J531" s="31" t="s">
-        <v>1257</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="532" spans="1:10" ht="15.75">
@@ -23595,7 +23970,7 @@
         <v>883</v>
       </c>
       <c r="B532" s="31" t="s">
-        <v>1258</v>
+        <v>1353</v>
       </c>
       <c r="C532" s="31" t="s">
         <v>722</v>
@@ -23607,19 +23982,19 @@
         <v>724</v>
       </c>
       <c r="F532" s="31" t="s">
-        <v>1259</v>
+        <v>1354</v>
       </c>
       <c r="G532" s="31" t="s">
-        <v>1260</v>
+        <v>1355</v>
       </c>
       <c r="H532" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I532" s="31" t="s">
-        <v>1261</v>
+        <v>1356</v>
       </c>
       <c r="J532" s="31" t="s">
-        <v>1262</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="533" spans="1:10" ht="15.75">
@@ -23627,7 +24002,7 @@
         <v>883</v>
       </c>
       <c r="B533" s="31" t="s">
-        <v>1263</v>
+        <v>1358</v>
       </c>
       <c r="C533" s="31" t="s">
         <v>722</v>
@@ -23639,19 +24014,19 @@
         <v>724</v>
       </c>
       <c r="F533" s="31" t="s">
-        <v>1259</v>
+        <v>1354</v>
       </c>
       <c r="G533" s="31" t="s">
-        <v>1260</v>
+        <v>1355</v>
       </c>
       <c r="H533" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I533" s="31" t="s">
-        <v>1264</v>
+        <v>1359</v>
       </c>
       <c r="J533" s="31" t="s">
-        <v>1265</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="534" spans="1:10" ht="15.75">
@@ -23659,7 +24034,7 @@
         <v>883</v>
       </c>
       <c r="B534" s="31" t="s">
-        <v>1266</v>
+        <v>1361</v>
       </c>
       <c r="C534" s="31" t="s">
         <v>722</v>
@@ -23671,19 +24046,19 @@
         <v>724</v>
       </c>
       <c r="F534" s="31" t="s">
-        <v>1259</v>
+        <v>1354</v>
       </c>
       <c r="G534" s="31" t="s">
-        <v>1260</v>
+        <v>1355</v>
       </c>
       <c r="H534" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I534" s="31" t="s">
-        <v>1267</v>
+        <v>1362</v>
       </c>
       <c r="J534" s="31" t="s">
-        <v>1268</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="535" spans="1:10" ht="15.75">
@@ -23691,7 +24066,7 @@
         <v>883</v>
       </c>
       <c r="B535" s="31" t="s">
-        <v>1269</v>
+        <v>1364</v>
       </c>
       <c r="C535" s="31" t="s">
         <v>722</v>
@@ -23703,19 +24078,19 @@
         <v>724</v>
       </c>
       <c r="F535" s="31" t="s">
-        <v>1259</v>
+        <v>1354</v>
       </c>
       <c r="G535" s="31" t="s">
-        <v>1260</v>
+        <v>1355</v>
       </c>
       <c r="H535" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I535" s="31" t="s">
-        <v>1270</v>
+        <v>1365</v>
       </c>
       <c r="J535" s="31" t="s">
-        <v>1271</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="536" spans="1:10" ht="15.75">
@@ -23723,7 +24098,7 @@
         <v>883</v>
       </c>
       <c r="B536" s="31" t="s">
-        <v>1272</v>
+        <v>1367</v>
       </c>
       <c r="C536" s="31" t="s">
         <v>722</v>
@@ -23735,19 +24110,19 @@
         <v>724</v>
       </c>
       <c r="F536" s="31" t="s">
-        <v>1259</v>
+        <v>1354</v>
       </c>
       <c r="G536" s="31" t="s">
-        <v>1260</v>
+        <v>1355</v>
       </c>
       <c r="H536" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I536" s="31" t="s">
-        <v>1273</v>
+        <v>1368</v>
       </c>
       <c r="J536" s="31" t="s">
-        <v>1274</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="537" spans="1:10" ht="15.75">
@@ -23755,7 +24130,7 @@
         <v>883</v>
       </c>
       <c r="B537" s="31" t="s">
-        <v>1258</v>
+        <v>1370</v>
       </c>
       <c r="C537" s="31" t="s">
         <v>722</v>
@@ -23767,19 +24142,19 @@
         <v>724</v>
       </c>
       <c r="F537" s="31" t="s">
-        <v>1259</v>
+        <v>1354</v>
       </c>
       <c r="G537" s="31" t="s">
-        <v>1275</v>
+        <v>1371</v>
       </c>
       <c r="H537" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I537" s="31" t="s">
-        <v>1276</v>
+        <v>1372</v>
       </c>
       <c r="J537" s="31" t="s">
-        <v>1277</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="538" spans="1:10" ht="15.75">
@@ -23787,7 +24162,7 @@
         <v>883</v>
       </c>
       <c r="B538" s="31" t="s">
-        <v>1263</v>
+        <v>1374</v>
       </c>
       <c r="C538" s="31" t="s">
         <v>722</v>
@@ -23799,19 +24174,19 @@
         <v>724</v>
       </c>
       <c r="F538" s="31" t="s">
-        <v>1259</v>
+        <v>1354</v>
       </c>
       <c r="G538" s="31" t="s">
-        <v>1275</v>
+        <v>1371</v>
       </c>
       <c r="H538" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I538" s="31" t="s">
-        <v>1278</v>
+        <v>1375</v>
       </c>
       <c r="J538" s="31" t="s">
-        <v>1279</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="539" spans="1:10" ht="15.75">
@@ -23819,7 +24194,7 @@
         <v>883</v>
       </c>
       <c r="B539" s="31" t="s">
-        <v>1266</v>
+        <v>1377</v>
       </c>
       <c r="C539" s="31" t="s">
         <v>722</v>
@@ -23831,19 +24206,19 @@
         <v>724</v>
       </c>
       <c r="F539" s="31" t="s">
-        <v>1259</v>
+        <v>1354</v>
       </c>
       <c r="G539" s="31" t="s">
-        <v>1275</v>
+        <v>1371</v>
       </c>
       <c r="H539" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I539" s="31" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="J539" s="31" t="s">
-        <v>1281</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="540" spans="1:10" ht="15.75">
@@ -23851,7 +24226,7 @@
         <v>883</v>
       </c>
       <c r="B540" s="31" t="s">
-        <v>1269</v>
+        <v>1380</v>
       </c>
       <c r="C540" s="31" t="s">
         <v>722</v>
@@ -23863,19 +24238,19 @@
         <v>724</v>
       </c>
       <c r="F540" s="31" t="s">
-        <v>1259</v>
+        <v>1354</v>
       </c>
       <c r="G540" s="31" t="s">
-        <v>1275</v>
+        <v>1371</v>
       </c>
       <c r="H540" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I540" s="31" t="s">
-        <v>1282</v>
+        <v>1381</v>
       </c>
       <c r="J540" s="31" t="s">
-        <v>1283</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="541" spans="1:10" ht="15.75">
@@ -23883,7 +24258,7 @@
         <v>883</v>
       </c>
       <c r="B541" s="31" t="s">
-        <v>1272</v>
+        <v>1383</v>
       </c>
       <c r="C541" s="31" t="s">
         <v>722</v>
@@ -23895,19 +24270,19 @@
         <v>724</v>
       </c>
       <c r="F541" s="31" t="s">
-        <v>1259</v>
+        <v>1354</v>
       </c>
       <c r="G541" s="31" t="s">
-        <v>1275</v>
+        <v>1371</v>
       </c>
       <c r="H541" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I541" s="31" t="s">
-        <v>1284</v>
+        <v>1384</v>
       </c>
       <c r="J541" s="31" t="s">
-        <v>1285</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="542" spans="1:10" ht="15.75">
@@ -23915,7 +24290,7 @@
         <v>883</v>
       </c>
       <c r="B542" s="31" t="s">
-        <v>1286</v>
+        <v>1386</v>
       </c>
       <c r="C542" s="31" t="s">
         <v>832</v>
@@ -23927,19 +24302,19 @@
         <v>834</v>
       </c>
       <c r="F542" s="31" t="s">
-        <v>1287</v>
+        <v>1387</v>
       </c>
       <c r="G542" s="31" t="s">
-        <v>1288</v>
+        <v>1388</v>
       </c>
       <c r="H542" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I542" s="31" t="s">
-        <v>1289</v>
+        <v>1389</v>
       </c>
       <c r="J542" s="31" t="s">
-        <v>1290</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="543" spans="1:10" ht="15.75">
@@ -23947,7 +24322,7 @@
         <v>883</v>
       </c>
       <c r="B543" s="31" t="s">
-        <v>1291</v>
+        <v>1391</v>
       </c>
       <c r="C543" s="31" t="s">
         <v>832</v>
@@ -23959,19 +24334,19 @@
         <v>834</v>
       </c>
       <c r="F543" s="31" t="s">
-        <v>1287</v>
+        <v>1387</v>
       </c>
       <c r="G543" s="31" t="s">
-        <v>1288</v>
+        <v>1388</v>
       </c>
       <c r="H543" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I543" s="31" t="s">
-        <v>1292</v>
+        <v>1392</v>
       </c>
       <c r="J543" s="31" t="s">
-        <v>1293</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="544" spans="1:10" ht="15.75">
@@ -23979,7 +24354,7 @@
         <v>883</v>
       </c>
       <c r="B544" s="31" t="s">
-        <v>1294</v>
+        <v>1394</v>
       </c>
       <c r="C544" s="31" t="s">
         <v>832</v>
@@ -23991,19 +24366,19 @@
         <v>834</v>
       </c>
       <c r="F544" s="31" t="s">
-        <v>1287</v>
+        <v>1387</v>
       </c>
       <c r="G544" s="31" t="s">
-        <v>1288</v>
+        <v>1388</v>
       </c>
       <c r="H544" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I544" s="31" t="s">
-        <v>1295</v>
+        <v>1395</v>
       </c>
       <c r="J544" s="31" t="s">
-        <v>1296</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="545" spans="1:10" ht="15.75">
@@ -24011,7 +24386,7 @@
         <v>883</v>
       </c>
       <c r="B545" s="31" t="s">
-        <v>1297</v>
+        <v>1397</v>
       </c>
       <c r="C545" s="31" t="s">
         <v>832</v>
@@ -24023,19 +24398,19 @@
         <v>834</v>
       </c>
       <c r="F545" s="31" t="s">
-        <v>1287</v>
+        <v>1387</v>
       </c>
       <c r="G545" s="31" t="s">
-        <v>1288</v>
+        <v>1388</v>
       </c>
       <c r="H545" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I545" s="31" t="s">
-        <v>1298</v>
+        <v>1398</v>
       </c>
       <c r="J545" s="31" t="s">
-        <v>1299</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="546" spans="1:10" ht="15.75">
@@ -24043,7 +24418,7 @@
         <v>883</v>
       </c>
       <c r="B546" s="31" t="s">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="C546" s="31" t="s">
         <v>832</v>
@@ -24055,19 +24430,19 @@
         <v>834</v>
       </c>
       <c r="F546" s="31" t="s">
-        <v>1287</v>
+        <v>1387</v>
       </c>
       <c r="G546" s="31" t="s">
-        <v>1288</v>
+        <v>1388</v>
       </c>
       <c r="H546" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I546" s="31" t="s">
-        <v>1301</v>
+        <v>1401</v>
       </c>
       <c r="J546" s="31" t="s">
-        <v>1302</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="547" spans="1:10" ht="15.75">
@@ -24075,7 +24450,7 @@
         <v>883</v>
       </c>
       <c r="B547" s="31" t="s">
-        <v>1286</v>
+        <v>1403</v>
       </c>
       <c r="C547" s="31" t="s">
         <v>832</v>
@@ -24087,19 +24462,19 @@
         <v>834</v>
       </c>
       <c r="F547" s="31" t="s">
-        <v>1287</v>
+        <v>1387</v>
       </c>
       <c r="G547" s="31" t="s">
-        <v>1303</v>
+        <v>1404</v>
       </c>
       <c r="H547" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I547" s="31" t="s">
-        <v>1304</v>
+        <v>1405</v>
       </c>
       <c r="J547" s="31" t="s">
-        <v>1305</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="548" spans="1:10" ht="15.75">
@@ -24107,7 +24482,7 @@
         <v>883</v>
       </c>
       <c r="B548" s="31" t="s">
-        <v>1291</v>
+        <v>1407</v>
       </c>
       <c r="C548" s="31" t="s">
         <v>832</v>
@@ -24119,19 +24494,19 @@
         <v>834</v>
       </c>
       <c r="F548" s="31" t="s">
-        <v>1287</v>
+        <v>1387</v>
       </c>
       <c r="G548" s="31" t="s">
-        <v>1303</v>
+        <v>1404</v>
       </c>
       <c r="H548" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I548" s="31" t="s">
-        <v>1306</v>
+        <v>1408</v>
       </c>
       <c r="J548" s="31" t="s">
-        <v>1307</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="549" spans="1:10" ht="15.75">
@@ -24139,7 +24514,7 @@
         <v>883</v>
       </c>
       <c r="B549" s="31" t="s">
-        <v>1294</v>
+        <v>1410</v>
       </c>
       <c r="C549" s="31" t="s">
         <v>832</v>
@@ -24151,19 +24526,19 @@
         <v>834</v>
       </c>
       <c r="F549" s="31" t="s">
-        <v>1287</v>
+        <v>1387</v>
       </c>
       <c r="G549" s="31" t="s">
-        <v>1303</v>
+        <v>1404</v>
       </c>
       <c r="H549" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I549" s="31" t="s">
-        <v>1308</v>
+        <v>1411</v>
       </c>
       <c r="J549" s="31" t="s">
-        <v>1309</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="550" spans="1:10" ht="15.75">
@@ -24171,7 +24546,7 @@
         <v>883</v>
       </c>
       <c r="B550" s="31" t="s">
-        <v>1297</v>
+        <v>1413</v>
       </c>
       <c r="C550" s="31" t="s">
         <v>832</v>
@@ -24183,19 +24558,19 @@
         <v>834</v>
       </c>
       <c r="F550" s="31" t="s">
-        <v>1287</v>
+        <v>1387</v>
       </c>
       <c r="G550" s="31" t="s">
-        <v>1303</v>
+        <v>1404</v>
       </c>
       <c r="H550" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I550" s="31" t="s">
-        <v>1310</v>
+        <v>1414</v>
       </c>
       <c r="J550" s="31" t="s">
-        <v>1311</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="551" spans="1:10" ht="15.75">
@@ -24203,7 +24578,7 @@
         <v>883</v>
       </c>
       <c r="B551" s="31" t="s">
-        <v>1300</v>
+        <v>1416</v>
       </c>
       <c r="C551" s="31" t="s">
         <v>832</v>
@@ -24215,19 +24590,19 @@
         <v>834</v>
       </c>
       <c r="F551" s="31" t="s">
-        <v>1287</v>
+        <v>1387</v>
       </c>
       <c r="G551" s="31" t="s">
-        <v>1303</v>
+        <v>1404</v>
       </c>
       <c r="H551" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I551" s="31" t="s">
-        <v>1312</v>
+        <v>1417</v>
       </c>
       <c r="J551" s="31" t="s">
-        <v>1313</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="552" spans="1:10" ht="15.75">
@@ -24235,7 +24610,7 @@
         <v>883</v>
       </c>
       <c r="B552" s="31" t="s">
-        <v>1314</v>
+        <v>1419</v>
       </c>
       <c r="C552" s="31" t="s">
         <v>832</v>
@@ -24247,19 +24622,19 @@
         <v>834</v>
       </c>
       <c r="F552" s="31" t="s">
-        <v>1315</v>
+        <v>1420</v>
       </c>
       <c r="G552" s="31" t="s">
-        <v>1316</v>
+        <v>1421</v>
       </c>
       <c r="H552" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I552" s="31" t="s">
-        <v>1317</v>
+        <v>1422</v>
       </c>
       <c r="J552" s="31" t="s">
-        <v>1318</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="553" spans="1:10" ht="15.75">
@@ -24267,7 +24642,7 @@
         <v>883</v>
       </c>
       <c r="B553" s="31" t="s">
-        <v>1319</v>
+        <v>1424</v>
       </c>
       <c r="C553" s="31" t="s">
         <v>832</v>
@@ -24279,19 +24654,19 @@
         <v>834</v>
       </c>
       <c r="F553" s="31" t="s">
-        <v>1315</v>
+        <v>1420</v>
       </c>
       <c r="G553" s="31" t="s">
-        <v>1316</v>
+        <v>1421</v>
       </c>
       <c r="H553" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I553" s="31" t="s">
-        <v>1320</v>
+        <v>1425</v>
       </c>
       <c r="J553" s="31" t="s">
-        <v>1321</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="554" spans="1:10" ht="15.75">
@@ -24299,7 +24674,7 @@
         <v>883</v>
       </c>
       <c r="B554" s="31" t="s">
-        <v>1322</v>
+        <v>1427</v>
       </c>
       <c r="C554" s="31" t="s">
         <v>832</v>
@@ -24311,19 +24686,19 @@
         <v>834</v>
       </c>
       <c r="F554" s="31" t="s">
-        <v>1315</v>
+        <v>1420</v>
       </c>
       <c r="G554" s="31" t="s">
-        <v>1316</v>
+        <v>1421</v>
       </c>
       <c r="H554" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I554" s="31" t="s">
-        <v>1323</v>
+        <v>1428</v>
       </c>
       <c r="J554" s="31" t="s">
-        <v>1324</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="555" spans="1:10" ht="15.75">
@@ -24331,7 +24706,7 @@
         <v>883</v>
       </c>
       <c r="B555" s="31" t="s">
-        <v>1325</v>
+        <v>1430</v>
       </c>
       <c r="C555" s="31" t="s">
         <v>832</v>
@@ -24343,19 +24718,19 @@
         <v>834</v>
       </c>
       <c r="F555" s="31" t="s">
-        <v>1315</v>
+        <v>1420</v>
       </c>
       <c r="G555" s="31" t="s">
-        <v>1316</v>
+        <v>1421</v>
       </c>
       <c r="H555" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I555" s="31" t="s">
-        <v>1326</v>
+        <v>1431</v>
       </c>
       <c r="J555" s="31" t="s">
-        <v>1327</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="556" spans="1:10" ht="15.75">
@@ -24363,7 +24738,7 @@
         <v>883</v>
       </c>
       <c r="B556" s="31" t="s">
-        <v>1328</v>
+        <v>1433</v>
       </c>
       <c r="C556" s="31" t="s">
         <v>832</v>
@@ -24375,19 +24750,19 @@
         <v>834</v>
       </c>
       <c r="F556" s="31" t="s">
-        <v>1315</v>
+        <v>1420</v>
       </c>
       <c r="G556" s="31" t="s">
-        <v>1316</v>
+        <v>1421</v>
       </c>
       <c r="H556" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I556" s="31" t="s">
-        <v>1329</v>
+        <v>1434</v>
       </c>
       <c r="J556" s="31" t="s">
-        <v>1330</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="557" spans="1:10" ht="15.75">
@@ -24395,7 +24770,7 @@
         <v>883</v>
       </c>
       <c r="B557" s="31" t="s">
-        <v>1314</v>
+        <v>1436</v>
       </c>
       <c r="C557" s="31" t="s">
         <v>832</v>
@@ -24407,19 +24782,19 @@
         <v>834</v>
       </c>
       <c r="F557" s="31" t="s">
-        <v>1315</v>
+        <v>1420</v>
       </c>
       <c r="G557" s="31" t="s">
-        <v>1331</v>
+        <v>1437</v>
       </c>
       <c r="H557" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I557" s="31" t="s">
-        <v>1332</v>
+        <v>1438</v>
       </c>
       <c r="J557" s="31" t="s">
-        <v>1333</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="558" spans="1:10" ht="15.75">
@@ -24427,7 +24802,7 @@
         <v>883</v>
       </c>
       <c r="B558" s="31" t="s">
-        <v>1319</v>
+        <v>1440</v>
       </c>
       <c r="C558" s="31" t="s">
         <v>832</v>
@@ -24439,19 +24814,19 @@
         <v>834</v>
       </c>
       <c r="F558" s="31" t="s">
-        <v>1315</v>
+        <v>1420</v>
       </c>
       <c r="G558" s="31" t="s">
-        <v>1331</v>
+        <v>1437</v>
       </c>
       <c r="H558" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I558" s="31" t="s">
-        <v>1334</v>
+        <v>1441</v>
       </c>
       <c r="J558" s="31" t="s">
-        <v>1335</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="559" spans="1:10" ht="15.75">
@@ -24459,7 +24834,7 @@
         <v>883</v>
       </c>
       <c r="B559" s="31" t="s">
-        <v>1322</v>
+        <v>1443</v>
       </c>
       <c r="C559" s="31" t="s">
         <v>832</v>
@@ -24471,19 +24846,19 @@
         <v>834</v>
       </c>
       <c r="F559" s="31" t="s">
-        <v>1315</v>
+        <v>1420</v>
       </c>
       <c r="G559" s="31" t="s">
-        <v>1331</v>
+        <v>1437</v>
       </c>
       <c r="H559" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I559" s="31" t="s">
-        <v>1336</v>
+        <v>1444</v>
       </c>
       <c r="J559" s="31" t="s">
-        <v>1337</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="560" spans="1:10" ht="15.75">
@@ -24491,7 +24866,7 @@
         <v>883</v>
       </c>
       <c r="B560" s="31" t="s">
-        <v>1325</v>
+        <v>1446</v>
       </c>
       <c r="C560" s="31" t="s">
         <v>832</v>
@@ -24503,19 +24878,19 @@
         <v>834</v>
       </c>
       <c r="F560" s="31" t="s">
-        <v>1315</v>
+        <v>1420</v>
       </c>
       <c r="G560" s="31" t="s">
-        <v>1331</v>
+        <v>1437</v>
       </c>
       <c r="H560" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I560" s="31" t="s">
-        <v>1338</v>
+        <v>1447</v>
       </c>
       <c r="J560" s="31" t="s">
-        <v>1339</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="561" spans="1:10" ht="15.75">
@@ -24523,7 +24898,7 @@
         <v>883</v>
       </c>
       <c r="B561" s="31" t="s">
-        <v>1328</v>
+        <v>1449</v>
       </c>
       <c r="C561" s="31" t="s">
         <v>832</v>
@@ -24535,19 +24910,19 @@
         <v>834</v>
       </c>
       <c r="F561" s="31" t="s">
-        <v>1315</v>
+        <v>1420</v>
       </c>
       <c r="G561" s="31" t="s">
-        <v>1331</v>
+        <v>1437</v>
       </c>
       <c r="H561" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I561" s="31" t="s">
-        <v>1340</v>
+        <v>1450</v>
       </c>
       <c r="J561" s="31" t="s">
-        <v>1341</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="562" spans="1:10" ht="15.75">
@@ -24555,7 +24930,7 @@
         <v>883</v>
       </c>
       <c r="B562" s="31" t="s">
-        <v>1342</v>
+        <v>1452</v>
       </c>
       <c r="C562" s="31" t="s">
         <v>832</v>
@@ -24567,19 +24942,19 @@
         <v>834</v>
       </c>
       <c r="F562" s="31" t="s">
-        <v>1343</v>
+        <v>1453</v>
       </c>
       <c r="G562" s="31" t="s">
-        <v>1344</v>
+        <v>1454</v>
       </c>
       <c r="H562" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I562" s="31" t="s">
-        <v>1345</v>
+        <v>1455</v>
       </c>
       <c r="J562" s="31" t="s">
-        <v>1346</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="563" spans="1:10" ht="15.75">
@@ -24587,7 +24962,7 @@
         <v>883</v>
       </c>
       <c r="B563" s="31" t="s">
-        <v>1347</v>
+        <v>1457</v>
       </c>
       <c r="C563" s="31" t="s">
         <v>832</v>
@@ -24599,19 +24974,19 @@
         <v>834</v>
       </c>
       <c r="F563" s="31" t="s">
-        <v>1343</v>
+        <v>1453</v>
       </c>
       <c r="G563" s="31" t="s">
-        <v>1344</v>
+        <v>1454</v>
       </c>
       <c r="H563" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I563" s="31" t="s">
-        <v>1348</v>
+        <v>1458</v>
       </c>
       <c r="J563" s="31" t="s">
-        <v>1349</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="564" spans="1:10" ht="15.75">
@@ -24619,7 +24994,7 @@
         <v>883</v>
       </c>
       <c r="B564" s="31" t="s">
-        <v>1350</v>
+        <v>1460</v>
       </c>
       <c r="C564" s="31" t="s">
         <v>832</v>
@@ -24631,19 +25006,19 @@
         <v>834</v>
       </c>
       <c r="F564" s="31" t="s">
-        <v>1343</v>
+        <v>1453</v>
       </c>
       <c r="G564" s="31" t="s">
-        <v>1344</v>
+        <v>1454</v>
       </c>
       <c r="H564" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I564" s="31" t="s">
-        <v>1351</v>
+        <v>1461</v>
       </c>
       <c r="J564" s="31" t="s">
-        <v>1352</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="565" spans="1:10" ht="15.75">
@@ -24651,7 +25026,7 @@
         <v>883</v>
       </c>
       <c r="B565" s="31" t="s">
-        <v>1353</v>
+        <v>1463</v>
       </c>
       <c r="C565" s="31" t="s">
         <v>832</v>
@@ -24663,19 +25038,19 @@
         <v>834</v>
       </c>
       <c r="F565" s="31" t="s">
-        <v>1343</v>
+        <v>1453</v>
       </c>
       <c r="G565" s="31" t="s">
-        <v>1344</v>
+        <v>1454</v>
       </c>
       <c r="H565" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I565" s="31" t="s">
-        <v>1354</v>
+        <v>1464</v>
       </c>
       <c r="J565" s="31" t="s">
-        <v>1355</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="566" spans="1:10" ht="15.75">
@@ -24683,7 +25058,7 @@
         <v>883</v>
       </c>
       <c r="B566" s="31" t="s">
-        <v>1356</v>
+        <v>1466</v>
       </c>
       <c r="C566" s="31" t="s">
         <v>832</v>
@@ -24695,19 +25070,19 @@
         <v>834</v>
       </c>
       <c r="F566" s="31" t="s">
-        <v>1343</v>
+        <v>1453</v>
       </c>
       <c r="G566" s="31" t="s">
-        <v>1344</v>
+        <v>1454</v>
       </c>
       <c r="H566" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I566" s="31" t="s">
-        <v>1357</v>
+        <v>1467</v>
       </c>
       <c r="J566" s="31" t="s">
-        <v>1358</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="567" spans="1:10" ht="15.75">
@@ -24715,7 +25090,7 @@
         <v>883</v>
       </c>
       <c r="B567" s="31" t="s">
-        <v>1342</v>
+        <v>1469</v>
       </c>
       <c r="C567" s="31" t="s">
         <v>832</v>
@@ -24727,19 +25102,19 @@
         <v>834</v>
       </c>
       <c r="F567" s="31" t="s">
-        <v>1343</v>
+        <v>1453</v>
       </c>
       <c r="G567" s="31" t="s">
-        <v>1359</v>
+        <v>1470</v>
       </c>
       <c r="H567" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I567" s="31" t="s">
-        <v>1360</v>
+        <v>1471</v>
       </c>
       <c r="J567" s="31" t="s">
-        <v>1361</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="568" spans="1:10" ht="15.75">
@@ -24747,7 +25122,7 @@
         <v>883</v>
       </c>
       <c r="B568" s="31" t="s">
-        <v>1347</v>
+        <v>1473</v>
       </c>
       <c r="C568" s="31" t="s">
         <v>832</v>
@@ -24759,19 +25134,19 @@
         <v>834</v>
       </c>
       <c r="F568" s="31" t="s">
-        <v>1343</v>
+        <v>1453</v>
       </c>
       <c r="G568" s="31" t="s">
-        <v>1359</v>
+        <v>1470</v>
       </c>
       <c r="H568" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I568" s="31" t="s">
-        <v>1362</v>
+        <v>1474</v>
       </c>
       <c r="J568" s="31" t="s">
-        <v>1363</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="569" spans="1:10" ht="15.75">
@@ -24779,7 +25154,7 @@
         <v>883</v>
       </c>
       <c r="B569" s="31" t="s">
-        <v>1350</v>
+        <v>1476</v>
       </c>
       <c r="C569" s="31" t="s">
         <v>832</v>
@@ -24791,19 +25166,19 @@
         <v>834</v>
       </c>
       <c r="F569" s="31" t="s">
-        <v>1343</v>
+        <v>1453</v>
       </c>
       <c r="G569" s="31" t="s">
-        <v>1359</v>
+        <v>1470</v>
       </c>
       <c r="H569" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I569" s="31" t="s">
-        <v>1364</v>
+        <v>1477</v>
       </c>
       <c r="J569" s="31" t="s">
-        <v>1365</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="570" spans="1:10" ht="15.75">
@@ -24811,7 +25186,7 @@
         <v>883</v>
       </c>
       <c r="B570" s="31" t="s">
-        <v>1353</v>
+        <v>1479</v>
       </c>
       <c r="C570" s="31" t="s">
         <v>832</v>
@@ -24823,19 +25198,19 @@
         <v>834</v>
       </c>
       <c r="F570" s="31" t="s">
-        <v>1343</v>
+        <v>1453</v>
       </c>
       <c r="G570" s="31" t="s">
-        <v>1359</v>
+        <v>1470</v>
       </c>
       <c r="H570" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I570" s="31" t="s">
-        <v>1366</v>
+        <v>1480</v>
       </c>
       <c r="J570" s="31" t="s">
-        <v>1367</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="571" spans="1:10" ht="15.75">
@@ -24843,7 +25218,7 @@
         <v>883</v>
       </c>
       <c r="B571" s="31" t="s">
-        <v>1356</v>
+        <v>1482</v>
       </c>
       <c r="C571" s="31" t="s">
         <v>832</v>
@@ -24855,19 +25230,19 @@
         <v>834</v>
       </c>
       <c r="F571" s="31" t="s">
-        <v>1343</v>
+        <v>1453</v>
       </c>
       <c r="G571" s="31" t="s">
-        <v>1359</v>
+        <v>1470</v>
       </c>
       <c r="H571" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I571" s="31" t="s">
-        <v>1368</v>
+        <v>1483</v>
       </c>
       <c r="J571" s="31" t="s">
-        <v>1369</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="572" spans="1:10" ht="15.75">
@@ -24875,7 +25250,7 @@
         <v>883</v>
       </c>
       <c r="B572" s="31" t="s">
-        <v>1370</v>
+        <v>1485</v>
       </c>
       <c r="C572" s="31" t="s">
         <v>444</v>
@@ -24887,19 +25262,19 @@
         <v>446</v>
       </c>
       <c r="F572" s="31" t="s">
-        <v>1371</v>
+        <v>1486</v>
       </c>
       <c r="G572" s="31" t="s">
-        <v>1372</v>
+        <v>1487</v>
       </c>
       <c r="H572" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I572" s="31" t="s">
-        <v>1373</v>
+        <v>1488</v>
       </c>
       <c r="J572" s="31" t="s">
-        <v>1374</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="573" spans="1:10" ht="15.75">
@@ -24907,7 +25282,7 @@
         <v>883</v>
       </c>
       <c r="B573" s="31" t="s">
-        <v>1375</v>
+        <v>1490</v>
       </c>
       <c r="C573" s="31" t="s">
         <v>444</v>
@@ -24919,19 +25294,19 @@
         <v>446</v>
       </c>
       <c r="F573" s="31" t="s">
-        <v>1371</v>
+        <v>1486</v>
       </c>
       <c r="G573" s="31" t="s">
-        <v>1372</v>
+        <v>1487</v>
       </c>
       <c r="H573" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I573" s="31" t="s">
-        <v>1376</v>
+        <v>1491</v>
       </c>
       <c r="J573" s="31" t="s">
-        <v>1377</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="574" spans="1:10" ht="15.75">
@@ -24939,7 +25314,7 @@
         <v>883</v>
       </c>
       <c r="B574" s="31" t="s">
-        <v>1378</v>
+        <v>1493</v>
       </c>
       <c r="C574" s="31" t="s">
         <v>444</v>
@@ -24951,19 +25326,19 @@
         <v>446</v>
       </c>
       <c r="F574" s="31" t="s">
-        <v>1371</v>
+        <v>1486</v>
       </c>
       <c r="G574" s="31" t="s">
-        <v>1372</v>
+        <v>1487</v>
       </c>
       <c r="H574" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I574" s="31" t="s">
-        <v>1379</v>
+        <v>1494</v>
       </c>
       <c r="J574" s="31" t="s">
-        <v>1380</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="575" spans="1:10" ht="15.75">
@@ -24971,7 +25346,7 @@
         <v>883</v>
       </c>
       <c r="B575" s="31" t="s">
-        <v>1381</v>
+        <v>1496</v>
       </c>
       <c r="C575" s="31" t="s">
         <v>444</v>
@@ -24983,19 +25358,19 @@
         <v>446</v>
       </c>
       <c r="F575" s="31" t="s">
-        <v>1371</v>
+        <v>1486</v>
       </c>
       <c r="G575" s="31" t="s">
-        <v>1372</v>
+        <v>1487</v>
       </c>
       <c r="H575" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I575" s="31" t="s">
-        <v>1382</v>
+        <v>1497</v>
       </c>
       <c r="J575" s="31" t="s">
-        <v>1383</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="576" spans="1:10" ht="15.75">
@@ -25003,7 +25378,7 @@
         <v>883</v>
       </c>
       <c r="B576" s="31" t="s">
-        <v>1384</v>
+        <v>1499</v>
       </c>
       <c r="C576" s="31" t="s">
         <v>444</v>
@@ -25015,19 +25390,19 @@
         <v>446</v>
       </c>
       <c r="F576" s="31" t="s">
-        <v>1371</v>
+        <v>1486</v>
       </c>
       <c r="G576" s="31" t="s">
-        <v>1372</v>
+        <v>1487</v>
       </c>
       <c r="H576" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I576" s="31" t="s">
-        <v>1385</v>
+        <v>1500</v>
       </c>
       <c r="J576" s="31" t="s">
-        <v>1386</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="577" spans="1:10" ht="15.75">
@@ -25035,7 +25410,7 @@
         <v>883</v>
       </c>
       <c r="B577" s="31" t="s">
-        <v>1370</v>
+        <v>1502</v>
       </c>
       <c r="C577" s="31" t="s">
         <v>444</v>
@@ -25047,19 +25422,19 @@
         <v>446</v>
       </c>
       <c r="F577" s="31" t="s">
-        <v>1371</v>
+        <v>1486</v>
       </c>
       <c r="G577" s="31" t="s">
-        <v>1387</v>
+        <v>1503</v>
       </c>
       <c r="H577" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I577" s="31" t="s">
-        <v>1388</v>
+        <v>1504</v>
       </c>
       <c r="J577" s="31" t="s">
-        <v>1389</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="578" spans="1:10" ht="15.75">
@@ -25067,7 +25442,7 @@
         <v>883</v>
       </c>
       <c r="B578" s="31" t="s">
-        <v>1375</v>
+        <v>1506</v>
       </c>
       <c r="C578" s="31" t="s">
         <v>444</v>
@@ -25079,19 +25454,19 @@
         <v>446</v>
       </c>
       <c r="F578" s="31" t="s">
-        <v>1371</v>
+        <v>1486</v>
       </c>
       <c r="G578" s="31" t="s">
-        <v>1387</v>
+        <v>1503</v>
       </c>
       <c r="H578" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I578" s="31" t="s">
-        <v>1390</v>
+        <v>1507</v>
       </c>
       <c r="J578" s="31" t="s">
-        <v>1391</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="579" spans="1:10" ht="15.75">
@@ -25099,7 +25474,7 @@
         <v>883</v>
       </c>
       <c r="B579" s="31" t="s">
-        <v>1378</v>
+        <v>1509</v>
       </c>
       <c r="C579" s="31" t="s">
         <v>444</v>
@@ -25111,19 +25486,19 @@
         <v>446</v>
       </c>
       <c r="F579" s="31" t="s">
-        <v>1371</v>
+        <v>1486</v>
       </c>
       <c r="G579" s="31" t="s">
-        <v>1387</v>
+        <v>1503</v>
       </c>
       <c r="H579" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I579" s="31" t="s">
-        <v>1392</v>
+        <v>1510</v>
       </c>
       <c r="J579" s="31" t="s">
-        <v>1393</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="580" spans="1:10" ht="15.75">
@@ -25131,7 +25506,7 @@
         <v>883</v>
       </c>
       <c r="B580" s="31" t="s">
-        <v>1381</v>
+        <v>1512</v>
       </c>
       <c r="C580" s="31" t="s">
         <v>444</v>
@@ -25143,19 +25518,19 @@
         <v>446</v>
       </c>
       <c r="F580" s="31" t="s">
-        <v>1371</v>
+        <v>1486</v>
       </c>
       <c r="G580" s="31" t="s">
-        <v>1387</v>
+        <v>1503</v>
       </c>
       <c r="H580" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I580" s="31" t="s">
-        <v>1394</v>
+        <v>1513</v>
       </c>
       <c r="J580" s="31" t="s">
-        <v>1395</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="581" spans="1:10" ht="15.75">
@@ -25163,7 +25538,7 @@
         <v>883</v>
       </c>
       <c r="B581" s="31" t="s">
-        <v>1384</v>
+        <v>1515</v>
       </c>
       <c r="C581" s="31" t="s">
         <v>444</v>
@@ -25175,19 +25550,19 @@
         <v>446</v>
       </c>
       <c r="F581" s="31" t="s">
-        <v>1371</v>
+        <v>1486</v>
       </c>
       <c r="G581" s="31" t="s">
-        <v>1387</v>
+        <v>1503</v>
       </c>
       <c r="H581" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I581" s="31" t="s">
-        <v>1396</v>
+        <v>1516</v>
       </c>
       <c r="J581" s="31" t="s">
-        <v>1397</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="582" spans="1:10" ht="15.75">
@@ -25195,7 +25570,7 @@
         <v>883</v>
       </c>
       <c r="B582" s="31" t="s">
-        <v>1398</v>
+        <v>1518</v>
       </c>
       <c r="C582" s="31" t="s">
         <v>444</v>
@@ -25207,19 +25582,19 @@
         <v>446</v>
       </c>
       <c r="F582" s="31" t="s">
-        <v>1399</v>
+        <v>1519</v>
       </c>
       <c r="G582" s="31" t="s">
-        <v>1400</v>
+        <v>1520</v>
       </c>
       <c r="H582" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I582" s="31" t="s">
-        <v>1401</v>
+        <v>1521</v>
       </c>
       <c r="J582" s="31" t="s">
-        <v>1402</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="583" spans="1:10" ht="15.75">
@@ -25227,7 +25602,7 @@
         <v>883</v>
       </c>
       <c r="B583" s="31" t="s">
-        <v>1403</v>
+        <v>1523</v>
       </c>
       <c r="C583" s="31" t="s">
         <v>444</v>
@@ -25239,19 +25614,19 @@
         <v>446</v>
       </c>
       <c r="F583" s="31" t="s">
-        <v>1399</v>
+        <v>1519</v>
       </c>
       <c r="G583" s="31" t="s">
-        <v>1400</v>
+        <v>1520</v>
       </c>
       <c r="H583" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I583" s="31" t="s">
-        <v>1404</v>
+        <v>1524</v>
       </c>
       <c r="J583" s="31" t="s">
-        <v>1405</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="584" spans="1:10" ht="15.75">
@@ -25259,7 +25634,7 @@
         <v>883</v>
       </c>
       <c r="B584" s="31" t="s">
-        <v>1406</v>
+        <v>1526</v>
       </c>
       <c r="C584" s="31" t="s">
         <v>444</v>
@@ -25271,19 +25646,19 @@
         <v>446</v>
       </c>
       <c r="F584" s="31" t="s">
-        <v>1399</v>
+        <v>1519</v>
       </c>
       <c r="G584" s="31" t="s">
-        <v>1400</v>
+        <v>1520</v>
       </c>
       <c r="H584" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I584" s="31" t="s">
-        <v>1407</v>
+        <v>1527</v>
       </c>
       <c r="J584" s="31" t="s">
-        <v>1408</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="585" spans="1:10" ht="15.75">
@@ -25291,7 +25666,7 @@
         <v>883</v>
       </c>
       <c r="B585" s="31" t="s">
-        <v>1409</v>
+        <v>1529</v>
       </c>
       <c r="C585" s="31" t="s">
         <v>444</v>
@@ -25303,19 +25678,19 @@
         <v>446</v>
       </c>
       <c r="F585" s="31" t="s">
-        <v>1399</v>
+        <v>1519</v>
       </c>
       <c r="G585" s="31" t="s">
-        <v>1400</v>
+        <v>1520</v>
       </c>
       <c r="H585" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I585" s="31" t="s">
-        <v>1410</v>
+        <v>1530</v>
       </c>
       <c r="J585" s="31" t="s">
-        <v>1411</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="586" spans="1:10" ht="15.75">
@@ -25323,7 +25698,7 @@
         <v>883</v>
       </c>
       <c r="B586" s="31" t="s">
-        <v>1412</v>
+        <v>1532</v>
       </c>
       <c r="C586" s="31" t="s">
         <v>444</v>
@@ -25335,19 +25710,19 @@
         <v>446</v>
       </c>
       <c r="F586" s="31" t="s">
-        <v>1399</v>
+        <v>1519</v>
       </c>
       <c r="G586" s="31" t="s">
-        <v>1400</v>
+        <v>1520</v>
       </c>
       <c r="H586" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I586" s="31" t="s">
-        <v>1413</v>
+        <v>1533</v>
       </c>
       <c r="J586" s="31" t="s">
-        <v>1414</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="587" spans="1:10" ht="15.75">
@@ -25355,7 +25730,7 @@
         <v>883</v>
       </c>
       <c r="B587" s="31" t="s">
-        <v>1398</v>
+        <v>1535</v>
       </c>
       <c r="C587" s="31" t="s">
         <v>444</v>
@@ -25367,19 +25742,19 @@
         <v>446</v>
       </c>
       <c r="F587" s="31" t="s">
-        <v>1399</v>
+        <v>1519</v>
       </c>
       <c r="G587" s="31" t="s">
-        <v>1415</v>
+        <v>1536</v>
       </c>
       <c r="H587" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I587" s="31" t="s">
-        <v>1416</v>
+        <v>1537</v>
       </c>
       <c r="J587" s="31" t="s">
-        <v>1417</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="588" spans="1:10" ht="15.75">
@@ -25387,7 +25762,7 @@
         <v>883</v>
       </c>
       <c r="B588" s="31" t="s">
-        <v>1403</v>
+        <v>1539</v>
       </c>
       <c r="C588" s="31" t="s">
         <v>444</v>
@@ -25399,19 +25774,19 @@
         <v>446</v>
       </c>
       <c r="F588" s="31" t="s">
-        <v>1399</v>
+        <v>1519</v>
       </c>
       <c r="G588" s="31" t="s">
-        <v>1415</v>
+        <v>1536</v>
       </c>
       <c r="H588" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I588" s="31" t="s">
-        <v>1418</v>
+        <v>1540</v>
       </c>
       <c r="J588" s="31" t="s">
-        <v>1419</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="589" spans="1:10" ht="15.75">
@@ -25419,7 +25794,7 @@
         <v>883</v>
       </c>
       <c r="B589" s="31" t="s">
-        <v>1406</v>
+        <v>1542</v>
       </c>
       <c r="C589" s="31" t="s">
         <v>444</v>
@@ -25431,19 +25806,19 @@
         <v>446</v>
       </c>
       <c r="F589" s="31" t="s">
-        <v>1399</v>
+        <v>1519</v>
       </c>
       <c r="G589" s="31" t="s">
-        <v>1415</v>
+        <v>1536</v>
       </c>
       <c r="H589" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I589" s="31" t="s">
-        <v>1420</v>
+        <v>1543</v>
       </c>
       <c r="J589" s="31" t="s">
-        <v>1421</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="590" spans="1:10" ht="15.75">
@@ -25451,7 +25826,7 @@
         <v>883</v>
       </c>
       <c r="B590" s="31" t="s">
-        <v>1409</v>
+        <v>1545</v>
       </c>
       <c r="C590" s="31" t="s">
         <v>444</v>
@@ -25463,19 +25838,19 @@
         <v>446</v>
       </c>
       <c r="F590" s="31" t="s">
-        <v>1399</v>
+        <v>1519</v>
       </c>
       <c r="G590" s="31" t="s">
-        <v>1415</v>
+        <v>1536</v>
       </c>
       <c r="H590" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I590" s="31" t="s">
-        <v>1422</v>
+        <v>1546</v>
       </c>
       <c r="J590" s="31" t="s">
-        <v>1423</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="591" spans="1:10" ht="15.75">
@@ -25483,7 +25858,7 @@
         <v>883</v>
       </c>
       <c r="B591" s="31" t="s">
-        <v>1412</v>
+        <v>1548</v>
       </c>
       <c r="C591" s="31" t="s">
         <v>444</v>
@@ -25495,19 +25870,19 @@
         <v>446</v>
       </c>
       <c r="F591" s="31" t="s">
-        <v>1399</v>
+        <v>1519</v>
       </c>
       <c r="G591" s="31" t="s">
-        <v>1415</v>
+        <v>1536</v>
       </c>
       <c r="H591" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I591" s="31" t="s">
-        <v>1424</v>
+        <v>1549</v>
       </c>
       <c r="J591" s="31" t="s">
-        <v>1425</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="592" spans="1:10" ht="15.75">
@@ -25515,7 +25890,7 @@
         <v>883</v>
       </c>
       <c r="B592" s="31" t="s">
-        <v>1426</v>
+        <v>1551</v>
       </c>
       <c r="C592" s="31" t="s">
         <v>444</v>
@@ -25527,19 +25902,19 @@
         <v>446</v>
       </c>
       <c r="F592" s="31" t="s">
-        <v>1427</v>
+        <v>1552</v>
       </c>
       <c r="G592" s="31" t="s">
-        <v>1428</v>
+        <v>1553</v>
       </c>
       <c r="H592" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I592" s="31" t="s">
-        <v>1429</v>
+        <v>1554</v>
       </c>
       <c r="J592" s="31" t="s">
-        <v>1430</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="593" spans="1:10" ht="15.75">
@@ -25547,7 +25922,7 @@
         <v>883</v>
       </c>
       <c r="B593" s="31" t="s">
-        <v>1431</v>
+        <v>1556</v>
       </c>
       <c r="C593" s="31" t="s">
         <v>444</v>
@@ -25559,19 +25934,19 @@
         <v>446</v>
       </c>
       <c r="F593" s="31" t="s">
-        <v>1427</v>
+        <v>1552</v>
       </c>
       <c r="G593" s="31" t="s">
-        <v>1428</v>
+        <v>1553</v>
       </c>
       <c r="H593" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I593" s="31" t="s">
-        <v>1432</v>
+        <v>1557</v>
       </c>
       <c r="J593" s="31" t="s">
-        <v>1433</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="594" spans="1:10" ht="15.75">
@@ -25579,7 +25954,7 @@
         <v>883</v>
       </c>
       <c r="B594" s="31" t="s">
-        <v>1434</v>
+        <v>1559</v>
       </c>
       <c r="C594" s="31" t="s">
         <v>444</v>
@@ -25591,19 +25966,19 @@
         <v>446</v>
       </c>
       <c r="F594" s="31" t="s">
-        <v>1427</v>
+        <v>1552</v>
       </c>
       <c r="G594" s="31" t="s">
-        <v>1428</v>
+        <v>1553</v>
       </c>
       <c r="H594" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I594" s="31" t="s">
-        <v>1435</v>
+        <v>1560</v>
       </c>
       <c r="J594" s="31" t="s">
-        <v>1436</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="595" spans="1:10" ht="15.75">
@@ -25611,7 +25986,7 @@
         <v>883</v>
       </c>
       <c r="B595" s="31" t="s">
-        <v>1437</v>
+        <v>1562</v>
       </c>
       <c r="C595" s="31" t="s">
         <v>444</v>
@@ -25623,19 +25998,19 @@
         <v>446</v>
       </c>
       <c r="F595" s="31" t="s">
-        <v>1427</v>
+        <v>1552</v>
       </c>
       <c r="G595" s="31" t="s">
-        <v>1428</v>
+        <v>1553</v>
       </c>
       <c r="H595" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I595" s="31" t="s">
-        <v>1438</v>
+        <v>1563</v>
       </c>
       <c r="J595" s="31" t="s">
-        <v>1439</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="596" spans="1:10" ht="15.75">
@@ -25643,7 +26018,7 @@
         <v>883</v>
       </c>
       <c r="B596" s="31" t="s">
-        <v>1440</v>
+        <v>1565</v>
       </c>
       <c r="C596" s="31" t="s">
         <v>444</v>
@@ -25655,19 +26030,19 @@
         <v>446</v>
       </c>
       <c r="F596" s="31" t="s">
-        <v>1427</v>
+        <v>1552</v>
       </c>
       <c r="G596" s="31" t="s">
-        <v>1428</v>
+        <v>1553</v>
       </c>
       <c r="H596" s="31" t="s">
         <v>28</v>
       </c>
       <c r="I596" s="31" t="s">
-        <v>1441</v>
+        <v>1566</v>
       </c>
       <c r="J596" s="31" t="s">
-        <v>1442</v>
+        <v>1567</v>
       </c>
     </row>
   </sheetData>
